--- a/GORRITI/Mayo/GORRITI-MAYO.xlsx
+++ b/GORRITI/Mayo/GORRITI-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039A54B7-4E6F-497B-A2B3-FFB4B7F7D2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3F058-0F1F-47DF-A4B4-815F960E7F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$144</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="250">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -754,6 +754,27 @@
   </si>
   <si>
     <t>Metrogas Plan de pagos cuota 3 de 4 - Cliente nro. 020495697900</t>
+  </si>
+  <si>
+    <t>Gonzalez Maximiliano - reparaciones con yeso, endudo y trabajo de pintura en comedor y balo del 12A</t>
+  </si>
+  <si>
+    <t>Transf 23/05</t>
+  </si>
+  <si>
+    <t>Transf 22/05</t>
+  </si>
+  <si>
+    <t>ruIZ DIEGO ARIEL</t>
+  </si>
+  <si>
+    <t>Vaciamiento de pozo en cocherw, sala de bomba y bauleras por colapso de agua de napa ganada por caudal - El dia 16/05 al 17/05 en guardia se asiste con bombas propias y personal hasta su vaciamiento total</t>
+  </si>
+  <si>
+    <t>Transf 21/05</t>
+  </si>
+  <si>
+    <t>Instalacion de bomba de achique CUBIC 07 nueva</t>
   </si>
 </sst>
 </file>
@@ -1752,6 +1773,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1769,6 +1802,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1841,24 +1880,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2225,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2311,49 +2332,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="212" t="s">
+      <c r="B9" s="222" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="212"/>
+      <c r="C9" s="222"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="222"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="212"/>
-      <c r="C11" s="212"/>
+      <c r="B11" s="222"/>
+      <c r="C11" s="222"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="211" t="s">
+      <c r="A14" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
+      <c r="B14" s="221"/>
+      <c r="C14" s="221"/>
+      <c r="D14" s="221"/>
+      <c r="E14" s="221"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
+      <c r="A15" s="221"/>
+      <c r="B15" s="221"/>
+      <c r="C15" s="221"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="211"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
+      <c r="A16" s="221"/>
+      <c r="B16" s="221"/>
+      <c r="C16" s="221"/>
+      <c r="D16" s="221"/>
+      <c r="E16" s="221"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="211"/>
-      <c r="B17" s="211"/>
-      <c r="C17" s="211"/>
-      <c r="D17" s="211"/>
-      <c r="E17" s="211"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="221"/>
+      <c r="C17" s="221"/>
+      <c r="D17" s="221"/>
+      <c r="E17" s="221"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2545,28 +2566,28 @@
       <c r="E39" s="178"/>
     </row>
     <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="236" t="s">
+      <c r="A40" s="217" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="237"/>
+      <c r="B40" s="218"/>
       <c r="C40" s="55"/>
-      <c r="D40" s="234">
+      <c r="D40" s="204">
         <v>56000</v>
       </c>
-      <c r="E40" s="235" t="s">
+      <c r="E40" s="205" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="236" t="s">
+      <c r="A41" s="217" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="237"/>
+      <c r="B41" s="218"/>
       <c r="C41" s="55"/>
-      <c r="D41" s="234">
+      <c r="D41" s="204">
         <v>230000</v>
       </c>
-      <c r="E41" s="235" t="s">
+      <c r="E41" s="205" t="s">
         <v>203</v>
       </c>
       <c r="H41" s="168" t="s">
@@ -2595,10 +2616,10 @@
       <c r="E43" s="182"/>
     </row>
     <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="203" t="s">
+      <c r="A44" s="211" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="204"/>
+      <c r="B44" s="212"/>
       <c r="C44" s="57"/>
       <c r="D44" s="183">
         <v>120974</v>
@@ -2608,8 +2629,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="203"/>
-      <c r="B45" s="204"/>
+      <c r="A45" s="211"/>
+      <c r="B45" s="212"/>
       <c r="C45" s="57"/>
       <c r="D45" s="185"/>
       <c r="E45" s="184"/>
@@ -2641,7 +2662,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="55"/>
-      <c r="D48" s="240">
+      <c r="D48" s="208">
         <v>1644550.83</v>
       </c>
       <c r="E48" s="188" t="s">
@@ -2657,7 +2678,7 @@
         <v>38</v>
       </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="238">
+      <c r="D49" s="206">
         <v>129055.15</v>
       </c>
       <c r="E49" s="190" t="s">
@@ -2673,7 +2694,7 @@
         <v>68</v>
       </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="238">
+      <c r="D50" s="206">
         <v>234412.98</v>
       </c>
       <c r="E50" s="190" t="str">
@@ -2690,7 +2711,7 @@
         <v>37</v>
       </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="238">
+      <c r="D51" s="206">
         <v>14339.47</v>
       </c>
       <c r="E51" s="191" t="str">
@@ -2725,10 +2746,10 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="238">
+      <c r="D54" s="206">
         <v>814908.33</v>
       </c>
-      <c r="E54" s="239" t="s">
+      <c r="E54" s="207" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2738,7 +2759,7 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="238">
+      <c r="D55" s="206">
         <v>24398.76</v>
       </c>
       <c r="E55" s="193" t="str">
@@ -2752,7 +2773,7 @@
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="238">
+      <c r="D56" s="206">
         <v>15117.56</v>
       </c>
       <c r="E56" s="193" t="str">
@@ -2766,10 +2787,10 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="238">
+      <c r="D57" s="206">
         <v>11961.98</v>
       </c>
-      <c r="E57" s="239" t="s">
+      <c r="E57" s="207" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2779,7 +2800,7 @@
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="241">
+      <c r="D58" s="209">
         <f>5015.88+9656.96</f>
         <v>14672.84</v>
       </c>
@@ -2793,10 +2814,10 @@
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="241">
+      <c r="D59" s="209">
         <v>571923.57999999996</v>
       </c>
-      <c r="E59" s="242" t="s">
+      <c r="E59" s="210" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2814,12 +2835,12 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="203" t="s">
+      <c r="A61" s="211" t="s">
         <v>171</v>
       </c>
-      <c r="B61" s="204"/>
+      <c r="B61" s="212"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="238">
+      <c r="D61" s="206">
         <v>2302294.3199999998</v>
       </c>
       <c r="E61" s="193" t="s">
@@ -2827,11 +2848,11 @@
       </c>
     </row>
     <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="203"/>
-      <c r="B62" s="204"/>
+      <c r="A62" s="211"/>
+      <c r="B62" s="212"/>
       <c r="C62" s="166"/>
-      <c r="D62" s="209"/>
-      <c r="E62" s="210"/>
+      <c r="D62" s="219"/>
+      <c r="E62" s="220"/>
     </row>
     <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="s">
@@ -2854,76 +2875,76 @@
       <c r="D64" s="179"/>
       <c r="E64" s="195"/>
     </row>
-    <row r="65" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="236" t="s">
+    <row r="65" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="217" t="s">
         <v>214</v>
       </c>
-      <c r="B65" s="237"/>
+      <c r="B65" s="218"/>
       <c r="C65" s="58"/>
-      <c r="D65" s="238">
+      <c r="D65" s="206">
         <v>72600</v>
       </c>
       <c r="E65" s="126" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="236" t="s">
+    <row r="66" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="217" t="s">
         <v>214</v>
       </c>
-      <c r="B66" s="237"/>
+      <c r="B66" s="218"/>
       <c r="C66" s="58"/>
-      <c r="D66" s="238">
+      <c r="D66" s="206">
         <v>38000</v>
       </c>
       <c r="E66" s="126" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="236" t="s">
+    <row r="67" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="217" t="s">
         <v>214</v>
       </c>
-      <c r="B67" s="237"/>
+      <c r="B67" s="218"/>
       <c r="C67" s="58"/>
-      <c r="D67" s="238">
+      <c r="D67" s="206">
         <v>360000</v>
       </c>
       <c r="E67" s="126" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>202</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="238">
+      <c r="D68" s="206">
         <v>52000</v>
       </c>
       <c r="E68" s="196" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>234</v>
       </c>
       <c r="B69" s="167"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="238">
+      <c r="D69" s="206">
         <v>120000</v>
       </c>
       <c r="E69" s="194" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="203" t="s">
+    <row r="70" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="211" t="s">
         <v>223</v>
       </c>
-      <c r="B70" s="204"/>
+      <c r="B70" s="212"/>
       <c r="C70" s="5"/>
       <c r="D70" s="189">
         <v>338800</v>
@@ -2935,595 +2956,648 @@
         <v>241</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="205" t="s">
+    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="217" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="218"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="206">
+        <v>260000</v>
+      </c>
+      <c r="E71" s="203" t="s">
+        <v>245</v>
+      </c>
+      <c r="H71" s="168"/>
+    </row>
+    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="213" t="s">
         <v>240</v>
       </c>
-      <c r="B71" s="206"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="238">
+      <c r="B72" s="214"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="206">
         <v>120000</v>
       </c>
-      <c r="E71" s="194" t="s">
+      <c r="E72" s="194" t="s">
         <v>211</v>
       </c>
-      <c r="H71" s="168" t="s">
+      <c r="H72" s="168" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="205" t="s">
+    <row r="73" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="213" t="s">
         <v>235</v>
       </c>
-      <c r="B72" s="206"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="152">
-        <v>305000</v>
-      </c>
-      <c r="E72" s="194" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="205" t="s">
-        <v>237</v>
-      </c>
-      <c r="B73" s="206"/>
+      <c r="B73" s="214"/>
       <c r="C73" s="5"/>
       <c r="D73" s="152">
-        <v>45000</v>
-      </c>
-      <c r="E73" s="233" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="205" t="s">
-        <v>238</v>
-      </c>
-      <c r="B74" s="206"/>
+        <v>305000</v>
+      </c>
+      <c r="E73" s="194" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="213" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" s="214"/>
       <c r="C74" s="5"/>
       <c r="D74" s="152">
-        <v>130000</v>
-      </c>
-      <c r="E74" s="233" t="s">
+        <v>45000</v>
+      </c>
+      <c r="E74" s="203" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="205" t="s">
-        <v>227</v>
-      </c>
-      <c r="B75" s="206"/>
+    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="213" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75" s="214"/>
       <c r="C75" s="5"/>
       <c r="D75" s="152">
-        <v>210000</v>
-      </c>
-      <c r="E75" s="233" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="205" t="s">
-        <v>226</v>
-      </c>
-      <c r="B76" s="206"/>
+        <v>130000</v>
+      </c>
+      <c r="E75" s="203" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="213" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="214"/>
       <c r="C76" s="5"/>
       <c r="D76" s="152">
-        <v>115000</v>
-      </c>
-      <c r="E76" s="233" t="s">
+        <v>210000</v>
+      </c>
+      <c r="E76" s="203" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="201" t="s">
-        <v>232</v>
-      </c>
-      <c r="B77" s="202"/>
+    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="213" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" s="214"/>
       <c r="C77" s="5"/>
       <c r="D77" s="152">
-        <v>12000</v>
-      </c>
-      <c r="E77" s="233" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="205" t="s">
-        <v>224</v>
-      </c>
-      <c r="B78" s="206"/>
+        <v>115000</v>
+      </c>
+      <c r="E77" s="203" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="213" t="s">
+        <v>243</v>
+      </c>
+      <c r="B78" s="214"/>
       <c r="C78" s="5"/>
       <c r="D78" s="152">
+        <v>360000</v>
+      </c>
+      <c r="E78" s="203" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="213" t="s">
+        <v>247</v>
+      </c>
+      <c r="B79" s="214"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="152">
+        <v>770000</v>
+      </c>
+      <c r="E79" s="203" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="201" t="s">
+        <v>249</v>
+      </c>
+      <c r="B80" s="202"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="152">
+        <v>120000</v>
+      </c>
+      <c r="E80" s="203" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="201" t="s">
+        <v>232</v>
+      </c>
+      <c r="B81" s="202"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="152">
+        <v>12000</v>
+      </c>
+      <c r="E81" s="203" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="213" t="s">
+        <v>224</v>
+      </c>
+      <c r="B82" s="214"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="152">
         <f>1600+6400</f>
         <v>8000</v>
       </c>
-      <c r="E78" s="194" t="s">
+      <c r="E82" s="194" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="203" t="s">
+    <row r="83" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="211" t="s">
         <v>210</v>
       </c>
-      <c r="B79" s="204"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="124">
+      <c r="B83" s="212"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="124">
         <v>146900</v>
       </c>
-      <c r="E79" s="197" t="s">
+      <c r="E83" s="197" t="s">
         <v>209</v>
       </c>
-      <c r="I79" s="203"/>
-      <c r="J79" s="204"/>
-    </row>
-    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="30" t="s">
+      <c r="I83" s="211"/>
+      <c r="J83" s="212"/>
+    </row>
+    <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="198">
-        <f>SUM(D65:D79)</f>
-        <v>2073300</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="37" t="s">
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="198">
+        <f>SUM(D65:D83)</f>
+        <v>3583300</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B81" s="71"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="175"/>
-      <c r="E81" s="195"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+      <c r="B85" s="71"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="175"/>
+      <c r="E85" s="195"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="189">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="189">
         <f>37181.67+5673.24+21952.02+27190.88+9051.16+45454.76</f>
         <v>146503.73000000001</v>
       </c>
-      <c r="E82" s="199"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
+      <c r="E86" s="199"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="189">
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="189">
         <v>46383.47</v>
       </c>
-      <c r="E83" s="126"/>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="54" t="s">
+      <c r="E87" s="126"/>
+    </row>
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="54"/>
-      <c r="C84" s="54"/>
-      <c r="D84" s="127"/>
-      <c r="E84" s="121">
-        <f>SUM(D82:D83)</f>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="127"/>
+      <c r="E88" s="121">
+        <f>SUM(D86:D87)</f>
         <v>192887.2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="120"/>
-      <c r="E85" s="128"/>
-    </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="32" t="s">
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="120"/>
+      <c r="E89" s="128"/>
+    </row>
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="129"/>
-      <c r="E86" s="130">
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="129"/>
+      <c r="E90" s="130">
         <v>1468681.28</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="1"/>
-      <c r="D87" s="131"/>
-      <c r="E87" s="132"/>
-      <c r="F87" s="46"/>
-    </row>
-    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="1"/>
+      <c r="D91" s="131"/>
+      <c r="E91" s="132"/>
+      <c r="F91" s="46"/>
+    </row>
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B88" s="10"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="133"/>
-      <c r="E88" s="134">
-        <f>(SUM(E31:E86))</f>
-        <v>12184624.789999997</v>
-      </c>
-      <c r="F88" s="163"/>
-      <c r="G88" s="46"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D89" s="131"/>
-      <c r="E89" s="131"/>
-    </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D90" s="131"/>
-      <c r="E90" s="131"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="11" t="s">
+      <c r="B92" s="10"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="133"/>
+      <c r="E92" s="134">
+        <f>(SUM(E31:E90))</f>
+        <v>13694624.789999997</v>
+      </c>
+      <c r="F92" s="163"/>
+      <c r="G92" s="46"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D93" s="131"/>
+      <c r="E93" s="131"/>
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="131"/>
+      <c r="E94" s="131"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B91" s="12"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="135"/>
-      <c r="E91" s="136"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="203"/>
-      <c r="B92" s="204"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="152"/>
-      <c r="E92" s="122"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="203"/>
-      <c r="B93" s="204"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="124"/>
-      <c r="E93" s="122"/>
-    </row>
-    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="205"/>
-      <c r="B94" s="206"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="124"/>
-      <c r="E94" s="122"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="123"/>
-      <c r="B95" s="125"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="124"/>
-      <c r="E95" s="122"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="52"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61">
-        <f>SUM(D92:D95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="32" t="s">
+      <c r="B95" s="12"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="135"/>
+      <c r="E95" s="136"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="211"/>
+      <c r="B96" s="212"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="152"/>
+      <c r="E96" s="122"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="211"/>
+      <c r="B97" s="212"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="124"/>
+      <c r="E97" s="122"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="213"/>
+      <c r="B98" s="214"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="122"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="123"/>
+      <c r="B99" s="125"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="122"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="52"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61">
+        <f>SUM(D96:D99)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B99" s="32"/>
-      <c r="C99" s="32"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="119"/>
-    </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="33"/>
+      <c r="E103" s="119"/>
+    </row>
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B101" s="10"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="72">
-        <f>E96+E99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="116" t="s">
+      <c r="B105" s="10"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="72">
+        <f>E100+E103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="B103" s="117">
-        <f>E88</f>
-        <v>12184624.789999997</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="116" t="s">
+      <c r="B107" s="117">
+        <f>E92</f>
+        <v>13694624.789999997</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="B104" s="117">
-        <f>E88-E86</f>
-        <v>10715943.509999998</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="116" t="s">
+      <c r="B108" s="117">
+        <f>E92-E90</f>
+        <v>12225943.509999998</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="B105" s="117">
-        <f>E101-E99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="116" t="s">
+      <c r="B109" s="117">
+        <f>E105-E103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="B106" s="117">
-        <f>E101</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="207"/>
-      <c r="B109" s="207"/>
-      <c r="C109" s="207"/>
-      <c r="D109" s="207"/>
-      <c r="E109" s="207"/>
-    </row>
-    <row r="110" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="207"/>
-      <c r="B110" s="207"/>
-      <c r="C110" s="207"/>
-      <c r="D110" s="207"/>
-      <c r="E110" s="207"/>
-    </row>
-    <row r="111" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="207"/>
-      <c r="B111" s="207"/>
-      <c r="C111" s="207"/>
-      <c r="D111" s="207"/>
-      <c r="E111" s="207"/>
-    </row>
-    <row r="113" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="23" t="s">
+      <c r="B110" s="117">
+        <f>E105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="215"/>
+      <c r="B113" s="215"/>
+      <c r="C113" s="215"/>
+      <c r="D113" s="215"/>
+      <c r="E113" s="215"/>
+    </row>
+    <row r="114" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="215"/>
+      <c r="B114" s="215"/>
+      <c r="C114" s="215"/>
+      <c r="D114" s="215"/>
+      <c r="E114" s="215"/>
+    </row>
+    <row r="115" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="215"/>
+      <c r="B115" s="215"/>
+      <c r="C115" s="215"/>
+      <c r="D115" s="215"/>
+      <c r="E115" s="215"/>
+    </row>
+    <row r="117" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B113" s="148"/>
-      <c r="C113" s="24"/>
-    </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="35"/>
-      <c r="B114" s="62">
-        <v>0</v>
-      </c>
-      <c r="C114" s="26"/>
-    </row>
-    <row r="115" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="25" t="s">
+      <c r="B117" s="148"/>
+      <c r="C117" s="24"/>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="35"/>
+      <c r="B118" s="62">
+        <v>0</v>
+      </c>
+      <c r="C118" s="26"/>
+    </row>
+    <row r="119" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="42">
+      <c r="B119" s="42">
         <f>PRORRATEO!I81</f>
         <v>11284159.269999998</v>
       </c>
-      <c r="C115" s="24"/>
-    </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="25"/>
-      <c r="B116" s="42">
-        <v>0</v>
-      </c>
-      <c r="C116" s="24"/>
-    </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="25" t="s">
+      <c r="C119" s="24"/>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="25"/>
+      <c r="B120" s="42">
+        <v>0</v>
+      </c>
+      <c r="C120" s="24"/>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B117" s="126">
-        <f>B139</f>
-        <v>0</v>
-      </c>
-      <c r="C117" s="24"/>
-    </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="28"/>
-      <c r="B118" s="50"/>
-      <c r="C118" s="24"/>
-    </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="142" t="s">
+      <c r="B121" s="126">
+        <f>B143</f>
+        <v>0</v>
+      </c>
+      <c r="C121" s="24"/>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="28"/>
+      <c r="B122" s="50"/>
+      <c r="C122" s="24"/>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="B119" s="50"/>
-      <c r="C119" s="24"/>
-    </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="41" t="s">
+      <c r="B123" s="50"/>
+      <c r="C123" s="24"/>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B120" s="50">
-        <f>-B104</f>
-        <v>-10715943.509999998</v>
-      </c>
-      <c r="C120" s="24"/>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="28" t="s">
+      <c r="B124" s="50">
+        <f>-B108</f>
+        <v>-12225943.509999998</v>
+      </c>
+      <c r="C124" s="24"/>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B121" s="50">
-        <f>-(B105)</f>
-        <v>0</v>
-      </c>
-      <c r="C121" s="24"/>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="34" t="s">
+      <c r="B125" s="50">
+        <f>-(B109)</f>
+        <v>0</v>
+      </c>
+      <c r="C125" s="24"/>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B122" s="62">
-        <f>SUM(B114:B121)</f>
-        <v>568215.75999999978</v>
-      </c>
-      <c r="C122" s="27"/>
-      <c r="D122" s="46"/>
-    </row>
-    <row r="123" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="43"/>
-      <c r="C123" s="27"/>
-      <c r="D123" s="46"/>
-      <c r="E123" s="149"/>
-      <c r="F123" s="150"/>
-    </row>
-    <row r="124" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="44"/>
-      <c r="C124" s="27"/>
-    </row>
-    <row r="125" spans="1:6" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125"/>
-      <c r="B125" s="43"/>
-      <c r="C125" s="39"/>
-    </row>
-    <row r="126" spans="1:6" s="40" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="154" t="s">
+      <c r="B126" s="62">
+        <f>SUM(B118:B125)</f>
+        <v>-941784.24000000022</v>
+      </c>
+      <c r="C126" s="27"/>
+      <c r="D126" s="46"/>
+    </row>
+    <row r="127" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="43"/>
+      <c r="C127" s="27"/>
+      <c r="D127" s="46"/>
+      <c r="E127" s="149"/>
+      <c r="F127" s="150"/>
+    </row>
+    <row r="128" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="44"/>
+      <c r="C128" s="27"/>
+    </row>
+    <row r="129" spans="1:13" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="39"/>
+    </row>
+    <row r="130" spans="1:13" s="40" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="154" t="s">
         <v>190</v>
       </c>
-      <c r="B126" s="155">
+      <c r="B130" s="155">
         <v>66313.089999996126</v>
       </c>
-      <c r="C126" s="39"/>
-      <c r="D126" s="49"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="57" t="s">
+      <c r="C130" s="39"/>
+      <c r="D130" s="49"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="B127" s="159">
-        <f>-B104</f>
-        <v>-10715943.509999998</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="57" t="s">
+      <c r="B131" s="159">
+        <f>-B108</f>
+        <v>-12225943.509999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="B128" s="159">
-        <f>-B105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="57" t="s">
+      <c r="B132" s="159">
+        <f>-B109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="B129" s="160">
+      <c r="B133" s="160">
         <f>PRORRATEO!I81</f>
         <v>11284159.269999998</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A130" s="57"/>
-      <c r="B130" s="160"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A131" s="161" t="s">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="57"/>
+      <c r="B134" s="160"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="161" t="s">
         <v>199</v>
       </c>
-      <c r="B131" s="162">
+      <c r="B135" s="162">
         <f>-(11743+7875)</f>
         <v>-19618</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="157" t="s">
+    <row r="136" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="157" t="s">
         <v>184</v>
       </c>
-      <c r="B132" s="158">
-        <f>SUM(B126:C131)</f>
-        <v>614910.8499999959</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A133" s="156"/>
-      <c r="B133" s="156"/>
-    </row>
-    <row r="134" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="208" t="s">
+      <c r="B136" s="158">
+        <f>SUM(B130:C135)</f>
+        <v>-895089.1500000041</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="156"/>
+      <c r="B137" s="156"/>
+    </row>
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B135" s="208"/>
-      <c r="C135" s="208"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="208"/>
-      <c r="B136" s="208"/>
-      <c r="C136" s="208"/>
-    </row>
-    <row r="137" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="139"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="38">
+      <c r="B139" s="216"/>
+      <c r="C139" s="216"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140" s="216"/>
+      <c r="B140" s="216"/>
+      <c r="C140" s="216"/>
+    </row>
+    <row r="141" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="139"/>
+      <c r="B141" s="38"/>
+      <c r="C141" s="38">
         <v>40000</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="139"/>
-      <c r="B138" s="141"/>
-      <c r="C138" s="137"/>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
+    <row r="142" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="139"/>
+      <c r="B142" s="141"/>
+      <c r="C142" s="137"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B139" s="140">
-        <f>SUM(B137:B138)</f>
-        <v>0</v>
-      </c>
-      <c r="C139" s="48"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M140" s="8"/>
-    </row>
-    <row r="141" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="207"/>
-      <c r="B141" s="207"/>
-      <c r="C141" s="207"/>
-      <c r="D141" s="207"/>
-      <c r="E141" s="207"/>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A142" s="207"/>
-      <c r="B142" s="207"/>
-      <c r="C142" s="207"/>
-      <c r="D142" s="207"/>
-      <c r="E142" s="207"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A143" s="207"/>
-      <c r="B143" s="207"/>
-      <c r="C143" s="207"/>
-      <c r="D143" s="207"/>
-      <c r="E143" s="207"/>
+      <c r="B143" s="140">
+        <f>SUM(B141:B142)</f>
+        <v>0</v>
+      </c>
+      <c r="C143" s="48"/>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A144" s="207"/>
-      <c r="B144" s="207"/>
-      <c r="C144" s="207"/>
-      <c r="D144" s="207"/>
-      <c r="E144" s="207"/>
+      <c r="M144" s="8"/>
+    </row>
+    <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="215"/>
+      <c r="B145" s="215"/>
+      <c r="C145" s="215"/>
+      <c r="D145" s="215"/>
+      <c r="E145" s="215"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="215"/>
+      <c r="B146" s="215"/>
+      <c r="C146" s="215"/>
+      <c r="D146" s="215"/>
+      <c r="E146" s="215"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="215"/>
+      <c r="B147" s="215"/>
+      <c r="C147" s="215"/>
+      <c r="D147" s="215"/>
+      <c r="E147" s="215"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="215"/>
+      <c r="B148" s="215"/>
+      <c r="C148" s="215"/>
+      <c r="D148" s="215"/>
+      <c r="E148" s="215"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="31">
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="D62:E62"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="B9:C11"/>
@@ -3536,20 +3610,23 @@
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A145:E148"/>
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A113:E115"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A141:E144"/>
-    <mergeCell ref="A135:C136"/>
-    <mergeCell ref="A109:E111"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3592,16 +3669,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="220"/>
-      <c r="P1" s="220"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="230"/>
+      <c r="P1" s="230"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3626,11 +3703,11 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="230">
+      <c r="P2" s="240">
         <v>11376831.439999999</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3654,82 +3731,82 @@
       <c r="R3" s="63"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="215" t="s">
+      <c r="A4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="227" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="143"/>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="213" t="s">
+      <c r="E4" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="213" t="s">
+      <c r="F4" s="223" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="213" t="s">
+      <c r="G4" s="223" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="231" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="223" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="223" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="225" t="s">
+      <c r="K4" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="221" t="s">
+      <c r="L4" s="231" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="221" t="s">
+      <c r="M4" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="221" t="s">
+      <c r="N4" s="231" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="228" t="s">
+      <c r="O4" s="238" t="s">
         <v>63</v>
       </c>
       <c r="P4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="223" t="s">
+      <c r="Q4" s="233" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="231" t="s">
+      <c r="R4" s="241" t="s">
         <v>61</v>
       </c>
       <c r="U4" s="46"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="216"/>
-      <c r="B5" s="218"/>
+      <c r="A5" s="226"/>
+      <c r="B5" s="228"/>
       <c r="C5" s="144"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="222"/>
-      <c r="M5" s="227"/>
-      <c r="N5" s="222"/>
-      <c r="O5" s="229"/>
+      <c r="D5" s="229"/>
+      <c r="E5" s="229"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="232"/>
+      <c r="M5" s="237"/>
+      <c r="N5" s="232"/>
+      <c r="O5" s="239"/>
       <c r="P5" s="64" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q5" s="224"/>
-      <c r="R5" s="232"/>
+      <c r="Q5" s="234"/>
+      <c r="R5" s="242"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -8325,91 +8402,91 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="207" t="str">
+      <c r="E84" s="215" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="207"/>
-      <c r="G84" s="207"/>
-      <c r="H84" s="207"/>
-      <c r="I84" s="207"/>
-      <c r="J84" s="207"/>
-      <c r="K84" s="207"/>
-      <c r="L84" s="207"/>
-      <c r="M84" s="207"/>
-      <c r="N84" s="207"/>
-      <c r="O84" s="207"/>
-      <c r="P84" s="207"/>
+      <c r="F84" s="215"/>
+      <c r="G84" s="215"/>
+      <c r="H84" s="215"/>
+      <c r="I84" s="215"/>
+      <c r="J84" s="215"/>
+      <c r="K84" s="215"/>
+      <c r="L84" s="215"/>
+      <c r="M84" s="215"/>
+      <c r="N84" s="215"/>
+      <c r="O84" s="215"/>
+      <c r="P84" s="215"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E85" s="207"/>
-      <c r="F85" s="207"/>
-      <c r="G85" s="207"/>
-      <c r="H85" s="207"/>
-      <c r="I85" s="207"/>
-      <c r="J85" s="207"/>
-      <c r="K85" s="207"/>
-      <c r="L85" s="207"/>
-      <c r="M85" s="207"/>
-      <c r="N85" s="207"/>
-      <c r="O85" s="207"/>
-      <c r="P85" s="207"/>
+      <c r="E85" s="215"/>
+      <c r="F85" s="215"/>
+      <c r="G85" s="215"/>
+      <c r="H85" s="215"/>
+      <c r="I85" s="215"/>
+      <c r="J85" s="215"/>
+      <c r="K85" s="215"/>
+      <c r="L85" s="215"/>
+      <c r="M85" s="215"/>
+      <c r="N85" s="215"/>
+      <c r="O85" s="215"/>
+      <c r="P85" s="215"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E86" s="207"/>
-      <c r="F86" s="207"/>
-      <c r="G86" s="207"/>
-      <c r="H86" s="207"/>
-      <c r="I86" s="207"/>
-      <c r="J86" s="207"/>
-      <c r="K86" s="207"/>
-      <c r="L86" s="207"/>
-      <c r="M86" s="207"/>
-      <c r="N86" s="207"/>
-      <c r="O86" s="207"/>
-      <c r="P86" s="207"/>
+      <c r="E86" s="215"/>
+      <c r="F86" s="215"/>
+      <c r="G86" s="215"/>
+      <c r="H86" s="215"/>
+      <c r="I86" s="215"/>
+      <c r="J86" s="215"/>
+      <c r="K86" s="215"/>
+      <c r="L86" s="215"/>
+      <c r="M86" s="215"/>
+      <c r="N86" s="215"/>
+      <c r="O86" s="215"/>
+      <c r="P86" s="215"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="207"/>
-      <c r="F87" s="207"/>
-      <c r="G87" s="207"/>
-      <c r="H87" s="207"/>
-      <c r="I87" s="207"/>
-      <c r="J87" s="207"/>
-      <c r="K87" s="207"/>
-      <c r="L87" s="207"/>
-      <c r="M87" s="207"/>
-      <c r="N87" s="207"/>
-      <c r="O87" s="207"/>
-      <c r="P87" s="207"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="215"/>
+      <c r="G87" s="215"/>
+      <c r="H87" s="215"/>
+      <c r="I87" s="215"/>
+      <c r="J87" s="215"/>
+      <c r="K87" s="215"/>
+      <c r="L87" s="215"/>
+      <c r="M87" s="215"/>
+      <c r="N87" s="215"/>
+      <c r="O87" s="215"/>
+      <c r="P87" s="215"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E88" s="207"/>
-      <c r="F88" s="207"/>
-      <c r="G88" s="207"/>
-      <c r="H88" s="207"/>
-      <c r="I88" s="207"/>
-      <c r="J88" s="207"/>
-      <c r="K88" s="207"/>
-      <c r="L88" s="207"/>
-      <c r="M88" s="207"/>
-      <c r="N88" s="207"/>
-      <c r="O88" s="207"/>
-      <c r="P88" s="207"/>
+      <c r="E88" s="215"/>
+      <c r="F88" s="215"/>
+      <c r="G88" s="215"/>
+      <c r="H88" s="215"/>
+      <c r="I88" s="215"/>
+      <c r="J88" s="215"/>
+      <c r="K88" s="215"/>
+      <c r="L88" s="215"/>
+      <c r="M88" s="215"/>
+      <c r="N88" s="215"/>
+      <c r="O88" s="215"/>
+      <c r="P88" s="215"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="207"/>
-      <c r="F89" s="207"/>
-      <c r="G89" s="207"/>
-      <c r="H89" s="207"/>
-      <c r="I89" s="207"/>
-      <c r="J89" s="207"/>
-      <c r="K89" s="207"/>
-      <c r="L89" s="207"/>
-      <c r="M89" s="207"/>
-      <c r="N89" s="207"/>
-      <c r="O89" s="207"/>
-      <c r="P89" s="207"/>
+      <c r="E89" s="215"/>
+      <c r="F89" s="215"/>
+      <c r="G89" s="215"/>
+      <c r="H89" s="215"/>
+      <c r="I89" s="215"/>
+      <c r="J89" s="215"/>
+      <c r="K89" s="215"/>
+      <c r="L89" s="215"/>
+      <c r="M89" s="215"/>
+      <c r="N89" s="215"/>
+      <c r="O89" s="215"/>
+      <c r="P89" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/GORRITI/Mayo/GORRITI-MAYO.xlsx
+++ b/GORRITI/Mayo/GORRITI-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3F058-0F1F-47DF-A4B4-815F960E7F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155E890-66BD-4492-8A0F-9D122BACB4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$145</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="251">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -775,6 +775,9 @@
   </si>
   <si>
     <t>Instalacion de bomba de achique CUBIC 07 nueva</t>
+  </si>
+  <si>
+    <t>Transf 26/05</t>
   </si>
 </sst>
 </file>
@@ -1785,28 +1788,16 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1821,25 +1812,16 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1856,6 +1838,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1880,6 +1868,21 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2246,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2332,49 +2335,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="222" t="s">
+      <c r="B9" s="218" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="222"/>
+      <c r="C9" s="218"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="222"/>
-      <c r="C10" s="222"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="222"/>
-      <c r="C11" s="222"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="218"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="221" t="s">
+      <c r="A14" s="217" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="221"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="221"/>
-      <c r="B15" s="221"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
-      <c r="E15" s="221"/>
+      <c r="A15" s="217"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="217"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="221"/>
-      <c r="B16" s="221"/>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
-      <c r="E16" s="221"/>
+      <c r="A16" s="217"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="217"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="221"/>
-      <c r="B17" s="221"/>
-      <c r="C17" s="221"/>
-      <c r="D17" s="221"/>
-      <c r="E17" s="221"/>
+      <c r="A17" s="217"/>
+      <c r="B17" s="217"/>
+      <c r="C17" s="217"/>
+      <c r="D17" s="217"/>
+      <c r="E17" s="217"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2566,10 +2569,10 @@
       <c r="E39" s="178"/>
     </row>
     <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="217" t="s">
+      <c r="A40" s="211" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="218"/>
+      <c r="B40" s="212"/>
       <c r="C40" s="55"/>
       <c r="D40" s="204">
         <v>56000</v>
@@ -2579,10 +2582,10 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="217" t="s">
+      <c r="A41" s="211" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="218"/>
+      <c r="B41" s="212"/>
       <c r="C41" s="55"/>
       <c r="D41" s="204">
         <v>230000</v>
@@ -2616,10 +2619,10 @@
       <c r="E43" s="182"/>
     </row>
     <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="211" t="s">
+      <c r="A44" s="213" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="212"/>
+      <c r="B44" s="214"/>
       <c r="C44" s="57"/>
       <c r="D44" s="183">
         <v>120974</v>
@@ -2629,8 +2632,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="211"/>
-      <c r="B45" s="212"/>
+      <c r="A45" s="213"/>
+      <c r="B45" s="214"/>
       <c r="C45" s="57"/>
       <c r="D45" s="185"/>
       <c r="E45" s="184"/>
@@ -2835,10 +2838,10 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="211" t="s">
+      <c r="A61" s="213" t="s">
         <v>171</v>
       </c>
-      <c r="B61" s="212"/>
+      <c r="B61" s="214"/>
       <c r="C61" s="5"/>
       <c r="D61" s="206">
         <v>2302294.3199999998</v>
@@ -2848,11 +2851,11 @@
       </c>
     </row>
     <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="211"/>
-      <c r="B62" s="212"/>
+      <c r="A62" s="213"/>
+      <c r="B62" s="214"/>
       <c r="C62" s="166"/>
-      <c r="D62" s="219"/>
-      <c r="E62" s="220"/>
+      <c r="D62" s="215"/>
+      <c r="E62" s="216"/>
     </row>
     <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="s">
@@ -2876,10 +2879,10 @@
       <c r="E64" s="195"/>
     </row>
     <row r="65" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="217" t="s">
+      <c r="A65" s="211" t="s">
         <v>214</v>
       </c>
-      <c r="B65" s="218"/>
+      <c r="B65" s="212"/>
       <c r="C65" s="58"/>
       <c r="D65" s="206">
         <v>72600</v>
@@ -2889,10 +2892,10 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="217" t="s">
+      <c r="A66" s="211" t="s">
         <v>214</v>
       </c>
-      <c r="B66" s="218"/>
+      <c r="B66" s="212"/>
       <c r="C66" s="58"/>
       <c r="D66" s="206">
         <v>38000</v>
@@ -2902,10 +2905,10 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="217" t="s">
+      <c r="A67" s="211" t="s">
         <v>214</v>
       </c>
-      <c r="B67" s="218"/>
+      <c r="B67" s="212"/>
       <c r="C67" s="58"/>
       <c r="D67" s="206">
         <v>360000</v>
@@ -2920,7 +2923,7 @@
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="206">
+      <c r="D68" s="209">
         <v>52000</v>
       </c>
       <c r="E68" s="196" t="s">
@@ -2929,675 +2932,703 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="B69" s="167"/>
       <c r="C69" s="5"/>
       <c r="D69" s="206">
+        <v>53500</v>
+      </c>
+      <c r="E69" s="196" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" s="167"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="206">
         <v>120000</v>
       </c>
-      <c r="E69" s="194" t="s">
+      <c r="E70" s="194" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="211" t="s">
+    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="213" t="s">
         <v>223</v>
       </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="189">
+      <c r="B71" s="214"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="189">
         <v>338800</v>
       </c>
-      <c r="E70" s="196" t="s">
+      <c r="E71" s="196" t="s">
         <v>197</v>
       </c>
-      <c r="H70" s="168" t="s">
+      <c r="H71" s="168" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="217" t="s">
+    <row r="72" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="211" t="s">
         <v>246</v>
       </c>
-      <c r="B71" s="218"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="206">
-        <v>260000</v>
-      </c>
-      <c r="E71" s="203" t="s">
-        <v>245</v>
-      </c>
-      <c r="H71" s="168"/>
-    </row>
-    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="213" t="s">
-        <v>240</v>
-      </c>
-      <c r="B72" s="214"/>
+      <c r="B72" s="212"/>
       <c r="C72" s="5"/>
       <c r="D72" s="206">
+        <v>260000</v>
+      </c>
+      <c r="E72" s="203" t="s">
+        <v>245</v>
+      </c>
+      <c r="H72" s="168"/>
+    </row>
+    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="219" t="s">
+        <v>240</v>
+      </c>
+      <c r="B73" s="220"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="206">
         <v>120000</v>
       </c>
-      <c r="E72" s="194" t="s">
+      <c r="E73" s="194" t="s">
         <v>211</v>
       </c>
-      <c r="H72" s="168" t="s">
+      <c r="H73" s="168" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="213" t="s">
+    <row r="74" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="219" t="s">
         <v>235</v>
       </c>
-      <c r="B73" s="214"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="152">
-        <v>305000</v>
-      </c>
-      <c r="E73" s="194" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="213" t="s">
-        <v>237</v>
-      </c>
-      <c r="B74" s="214"/>
+      <c r="B74" s="220"/>
       <c r="C74" s="5"/>
       <c r="D74" s="152">
-        <v>45000</v>
-      </c>
-      <c r="E74" s="203" t="s">
-        <v>213</v>
+        <v>305000</v>
+      </c>
+      <c r="E74" s="194" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="213" t="s">
-        <v>238</v>
-      </c>
-      <c r="B75" s="214"/>
+      <c r="A75" s="219" t="s">
+        <v>237</v>
+      </c>
+      <c r="B75" s="220"/>
       <c r="C75" s="5"/>
       <c r="D75" s="152">
-        <v>130000</v>
+        <v>45000</v>
       </c>
       <c r="E75" s="203" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="213" t="s">
-        <v>227</v>
-      </c>
-      <c r="B76" s="214"/>
+      <c r="A76" s="219" t="s">
+        <v>238</v>
+      </c>
+      <c r="B76" s="220"/>
       <c r="C76" s="5"/>
       <c r="D76" s="152">
-        <v>210000</v>
+        <v>130000</v>
       </c>
       <c r="E76" s="203" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="213" t="s">
-        <v>226</v>
-      </c>
-      <c r="B77" s="214"/>
+      <c r="A77" s="219" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" s="220"/>
       <c r="C77" s="5"/>
       <c r="D77" s="152">
-        <v>115000</v>
+        <v>210000</v>
       </c>
       <c r="E77" s="203" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="213" t="s">
-        <v>243</v>
-      </c>
-      <c r="B78" s="214"/>
+      <c r="A78" s="219" t="s">
+        <v>226</v>
+      </c>
+      <c r="B78" s="220"/>
       <c r="C78" s="5"/>
       <c r="D78" s="152">
-        <v>360000</v>
+        <v>115000</v>
       </c>
       <c r="E78" s="203" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="213" t="s">
-        <v>247</v>
-      </c>
-      <c r="B79" s="214"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="219" t="s">
+        <v>243</v>
+      </c>
+      <c r="B79" s="220"/>
       <c r="C79" s="5"/>
       <c r="D79" s="152">
-        <v>770000</v>
+        <v>360000</v>
       </c>
       <c r="E79" s="203" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="201" t="s">
-        <v>249</v>
-      </c>
-      <c r="B80" s="202"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="219" t="s">
+        <v>247</v>
+      </c>
+      <c r="B80" s="220"/>
       <c r="C80" s="5"/>
       <c r="D80" s="152">
-        <v>120000</v>
+        <v>770000</v>
       </c>
       <c r="E80" s="203" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="201" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B81" s="202"/>
       <c r="C81" s="5"/>
       <c r="D81" s="152">
-        <v>12000</v>
+        <v>120000</v>
       </c>
       <c r="E81" s="203" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="213" t="s">
-        <v>224</v>
-      </c>
-      <c r="B82" s="214"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="201" t="s">
+        <v>232</v>
+      </c>
+      <c r="B82" s="202"/>
       <c r="C82" s="5"/>
       <c r="D82" s="152">
+        <v>12000</v>
+      </c>
+      <c r="E82" s="203" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B83" s="220"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="152">
         <f>1600+6400</f>
         <v>8000</v>
       </c>
-      <c r="E82" s="194" t="s">
+      <c r="E83" s="194" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="211" t="s">
+    <row r="84" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="213" t="s">
         <v>210</v>
       </c>
-      <c r="B83" s="212"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="124">
+      <c r="B84" s="214"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="124">
         <v>146900</v>
       </c>
-      <c r="E83" s="197" t="s">
+      <c r="E84" s="197" t="s">
         <v>209</v>
       </c>
-      <c r="I83" s="211"/>
-      <c r="J83" s="212"/>
-    </row>
-    <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="30" t="s">
+      <c r="I84" s="213"/>
+      <c r="J84" s="214"/>
+    </row>
+    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B84" s="37"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="198">
-        <f>SUM(D65:D83)</f>
-        <v>3583300</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="37" t="s">
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="198">
+        <f>SUM(D65:D84)</f>
+        <v>3636800</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B85" s="71"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="175"/>
-      <c r="E85" s="195"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="189">
-        <f>37181.67+5673.24+21952.02+27190.88+9051.16+45454.76</f>
-        <v>146503.73000000001</v>
-      </c>
-      <c r="E86" s="199"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="175"/>
+      <c r="E86" s="195"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="189">
+        <f>37181.67+5673.24+21952.02+27190.88+9051.16+45454.76</f>
+        <v>146503.73000000001</v>
+      </c>
+      <c r="E87" s="199"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="189">
         <v>46383.47</v>
       </c>
-      <c r="E87" s="126"/>
-    </row>
-    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="54" t="s">
+      <c r="E88" s="126"/>
+    </row>
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="54"/>
-      <c r="C88" s="54"/>
-      <c r="D88" s="127"/>
-      <c r="E88" s="121">
-        <f>SUM(D86:D87)</f>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="127"/>
+      <c r="E89" s="121">
+        <f>SUM(D87:D88)</f>
         <v>192887.2</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="120"/>
-      <c r="E89" s="128"/>
-    </row>
     <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="32" t="s">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="120"/>
+      <c r="E90" s="128"/>
+    </row>
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B90" s="32"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="129"/>
-      <c r="E90" s="130">
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="129"/>
+      <c r="E91" s="130">
         <v>1468681.28</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1"/>
-      <c r="D91" s="131"/>
-      <c r="E91" s="132"/>
-      <c r="F91" s="46"/>
-    </row>
     <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="1"/>
+      <c r="D92" s="131"/>
+      <c r="E92" s="132"/>
+      <c r="F92" s="46"/>
+    </row>
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="133"/>
-      <c r="E92" s="134">
-        <f>(SUM(E31:E90))</f>
-        <v>13694624.789999997</v>
-      </c>
-      <c r="F92" s="163"/>
-      <c r="G92" s="46"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D93" s="131"/>
-      <c r="E93" s="131"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="10"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="133"/>
+      <c r="E93" s="134">
+        <f>(SUM(E31:E91))</f>
+        <v>13748124.789999997</v>
+      </c>
+      <c r="F93" s="163"/>
+      <c r="G93" s="46"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D94" s="131"/>
       <c r="E94" s="131"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="11" t="s">
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D95" s="131"/>
+      <c r="E95" s="131"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B95" s="12"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="135"/>
-      <c r="E95" s="136"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="211"/>
-      <c r="B96" s="212"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="152"/>
-      <c r="E96" s="122"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="135"/>
+      <c r="E96" s="136"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="211"/>
-      <c r="B97" s="212"/>
+      <c r="A97" s="213"/>
+      <c r="B97" s="214"/>
       <c r="C97" s="5"/>
-      <c r="D97" s="124"/>
+      <c r="D97" s="152"/>
       <c r="E97" s="122"/>
     </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="213"/>
       <c r="B98" s="214"/>
       <c r="C98" s="5"/>
       <c r="D98" s="124"/>
       <c r="E98" s="122"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="123"/>
-      <c r="B99" s="125"/>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="219"/>
+      <c r="B99" s="220"/>
       <c r="C99" s="5"/>
       <c r="D99" s="124"/>
       <c r="E99" s="122"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="52"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61">
-        <f>SUM(D96:D99)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="32" t="s">
+      <c r="A100" s="123"/>
+      <c r="B100" s="125"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="124"/>
+      <c r="E100" s="122"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="52"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61">
+        <f>SUM(D97:D100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B103" s="32"/>
-      <c r="C103" s="32"/>
-      <c r="D103" s="33"/>
-      <c r="E103" s="119"/>
-    </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="3" t="s">
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="119"/>
+    </row>
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B105" s="10"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="72">
-        <f>E100+E103</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="116" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" s="117">
-        <f>E92</f>
-        <v>13694624.789999997</v>
-      </c>
-    </row>
+      <c r="B106" s="10"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="72">
+        <f>E101+E104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B108" s="117">
-        <f>E92-E90</f>
-        <v>12225943.509999998</v>
+        <f>E93</f>
+        <v>13748124.789999997</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="116" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B109" s="117">
-        <f>E105-E103</f>
-        <v>0</v>
+        <f>E93-E91</f>
+        <v>12279443.509999998</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" s="117">
+        <f>E106-E104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="117">
-        <f>E105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="215"/>
-      <c r="B113" s="215"/>
-      <c r="C113" s="215"/>
-      <c r="D113" s="215"/>
-      <c r="E113" s="215"/>
-    </row>
-    <row r="114" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="215"/>
-      <c r="B114" s="215"/>
-      <c r="C114" s="215"/>
-      <c r="D114" s="215"/>
-      <c r="E114" s="215"/>
-    </row>
-    <row r="115" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="215"/>
-      <c r="B115" s="215"/>
-      <c r="C115" s="215"/>
-      <c r="D115" s="215"/>
-      <c r="E115" s="215"/>
-    </row>
-    <row r="117" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="23" t="s">
+      <c r="B111" s="117">
+        <f>E106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="221"/>
+      <c r="B114" s="221"/>
+      <c r="C114" s="221"/>
+      <c r="D114" s="221"/>
+      <c r="E114" s="221"/>
+    </row>
+    <row r="115" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="221"/>
+      <c r="B115" s="221"/>
+      <c r="C115" s="221"/>
+      <c r="D115" s="221"/>
+      <c r="E115" s="221"/>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="221"/>
+      <c r="B116" s="221"/>
+      <c r="C116" s="221"/>
+      <c r="D116" s="221"/>
+      <c r="E116" s="221"/>
+    </row>
+    <row r="118" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B117" s="148"/>
-      <c r="C117" s="24"/>
-    </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="35"/>
-      <c r="B118" s="62">
-        <v>0</v>
-      </c>
-      <c r="C118" s="26"/>
-    </row>
-    <row r="119" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="25" t="s">
+      <c r="B118" s="148"/>
+      <c r="C118" s="24"/>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="35"/>
+      <c r="B119" s="62">
+        <v>0</v>
+      </c>
+      <c r="C119" s="26"/>
+    </row>
+    <row r="120" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="42">
+      <c r="B120" s="42">
         <f>PRORRATEO!I81</f>
         <v>11284159.269999998</v>
       </c>
-      <c r="C119" s="24"/>
-    </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="25"/>
-      <c r="B120" s="42">
-        <v>0</v>
-      </c>
       <c r="C120" s="24"/>
     </row>
     <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="25" t="s">
+      <c r="A121" s="25"/>
+      <c r="B121" s="42">
+        <v>0</v>
+      </c>
+      <c r="C121" s="24"/>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B121" s="126">
-        <f>B143</f>
-        <v>0</v>
-      </c>
-      <c r="C121" s="24"/>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="28"/>
-      <c r="B122" s="50"/>
+      <c r="B122" s="126">
+        <f>B144</f>
+        <v>0</v>
+      </c>
       <c r="C122" s="24"/>
     </row>
     <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="142" t="s">
-        <v>172</v>
-      </c>
+      <c r="A123" s="28"/>
       <c r="B123" s="50"/>
       <c r="C123" s="24"/>
     </row>
     <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="41" t="s">
+      <c r="A124" s="142" t="s">
+        <v>172</v>
+      </c>
+      <c r="B124" s="50"/>
+      <c r="C124" s="24"/>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B124" s="50">
-        <f>-B108</f>
-        <v>-12225943.509999998</v>
-      </c>
-      <c r="C124" s="24"/>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="28" t="s">
+      <c r="B125" s="50">
+        <f>-B109</f>
+        <v>-12279443.509999998</v>
+      </c>
+      <c r="C125" s="24"/>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B125" s="50">
-        <f>-(B109)</f>
-        <v>0</v>
-      </c>
-      <c r="C125" s="24"/>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="34" t="s">
+      <c r="B126" s="50">
+        <f>-(B110)</f>
+        <v>0</v>
+      </c>
+      <c r="C126" s="24"/>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B126" s="62">
-        <f>SUM(B118:B125)</f>
-        <v>-941784.24000000022</v>
-      </c>
-      <c r="C126" s="27"/>
-      <c r="D126" s="46"/>
-    </row>
-    <row r="127" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="43"/>
+      <c r="B127" s="62">
+        <f>SUM(B119:B126)</f>
+        <v>-995284.24000000022</v>
+      </c>
       <c r="C127" s="27"/>
       <c r="D127" s="46"/>
-      <c r="E127" s="149"/>
-      <c r="F127" s="150"/>
-    </row>
-    <row r="128" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="44"/>
+    </row>
+    <row r="128" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="43"/>
       <c r="C128" s="27"/>
-    </row>
-    <row r="129" spans="1:13" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129"/>
-      <c r="B129" s="43"/>
-      <c r="C129" s="39"/>
-    </row>
-    <row r="130" spans="1:13" s="40" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="154" t="s">
+      <c r="D128" s="46"/>
+      <c r="E128" s="149"/>
+      <c r="F128" s="150"/>
+    </row>
+    <row r="129" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="44"/>
+      <c r="C129" s="27"/>
+    </row>
+    <row r="130" spans="1:4" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="39"/>
+    </row>
+    <row r="131" spans="1:4" s="40" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="154" t="s">
         <v>190</v>
       </c>
-      <c r="B130" s="155">
+      <c r="B131" s="155">
         <v>66313.089999996126</v>
       </c>
-      <c r="C130" s="39"/>
-      <c r="D130" s="49"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A131" s="57" t="s">
+      <c r="C131" s="39"/>
+      <c r="D131" s="49"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="57" t="s">
         <v>193</v>
-      </c>
-      <c r="B131" s="159">
-        <f>-B108</f>
-        <v>-12225943.509999998</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132" s="57" t="s">
-        <v>194</v>
       </c>
       <c r="B132" s="159">
         <f>-B109</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+        <v>-12279443.509999998</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="B133" s="159">
+        <f>-B110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="B133" s="160">
+      <c r="B134" s="160">
         <f>PRORRATEO!I81</f>
         <v>11284159.269999998</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A134" s="57"/>
-      <c r="B134" s="160"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="161" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="57"/>
+      <c r="B135" s="160"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="161" t="s">
         <v>199</v>
       </c>
-      <c r="B135" s="162">
+      <c r="B136" s="162">
         <f>-(11743+7875)</f>
         <v>-19618</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="157" t="s">
+    <row r="137" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="157" t="s">
         <v>184</v>
       </c>
-      <c r="B136" s="158">
-        <f>SUM(B130:C135)</f>
-        <v>-895089.1500000041</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="156"/>
-      <c r="B137" s="156"/>
-    </row>
-    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="216" t="s">
+      <c r="B137" s="158">
+        <f>SUM(B131:C136)</f>
+        <v>-948589.1500000041</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="156"/>
+      <c r="B138" s="156"/>
+    </row>
+    <row r="139" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="222" t="s">
         <v>55</v>
       </c>
-      <c r="B139" s="216"/>
-      <c r="C139" s="216"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="216"/>
-      <c r="B140" s="216"/>
-      <c r="C140" s="216"/>
-    </row>
-    <row r="141" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="139"/>
-      <c r="B141" s="38"/>
-      <c r="C141" s="38">
+      <c r="B140" s="222"/>
+      <c r="C140" s="222"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="222"/>
+      <c r="B141" s="222"/>
+      <c r="C141" s="222"/>
+    </row>
+    <row r="142" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="139"/>
+      <c r="B142" s="38"/>
+      <c r="C142" s="38">
         <v>40000</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="139"/>
-      <c r="B142" s="141"/>
-      <c r="C142" s="137"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A143" s="47" t="s">
+    <row r="143" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="139"/>
+      <c r="B143" s="141"/>
+      <c r="C143" s="137"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B143" s="140">
-        <f>SUM(B141:B142)</f>
-        <v>0</v>
-      </c>
-      <c r="C143" s="48"/>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M144" s="8"/>
-    </row>
-    <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="215"/>
-      <c r="B145" s="215"/>
-      <c r="C145" s="215"/>
-      <c r="D145" s="215"/>
-      <c r="E145" s="215"/>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="215"/>
-      <c r="B146" s="215"/>
-      <c r="C146" s="215"/>
-      <c r="D146" s="215"/>
-      <c r="E146" s="215"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="215"/>
-      <c r="B147" s="215"/>
-      <c r="C147" s="215"/>
-      <c r="D147" s="215"/>
-      <c r="E147" s="215"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="215"/>
-      <c r="B148" s="215"/>
-      <c r="C148" s="215"/>
-      <c r="D148" s="215"/>
-      <c r="E148" s="215"/>
+      <c r="B144" s="140">
+        <f>SUM(B142:B143)</f>
+        <v>0</v>
+      </c>
+      <c r="C144" s="48"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M145" s="8"/>
+    </row>
+    <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="221"/>
+      <c r="B146" s="221"/>
+      <c r="C146" s="221"/>
+      <c r="D146" s="221"/>
+      <c r="E146" s="221"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A147" s="221"/>
+      <c r="B147" s="221"/>
+      <c r="C147" s="221"/>
+      <c r="D147" s="221"/>
+      <c r="E147" s="221"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A148" s="221"/>
+      <c r="B148" s="221"/>
+      <c r="C148" s="221"/>
+      <c r="D148" s="221"/>
+      <c r="E148" s="221"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A149" s="221"/>
+      <c r="B149" s="221"/>
+      <c r="C149" s="221"/>
+      <c r="D149" s="221"/>
+      <c r="E149" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A146:E149"/>
+    <mergeCell ref="A140:C141"/>
+    <mergeCell ref="A114:E116"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
     <mergeCell ref="D62:E62"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="B9:C11"/>
@@ -3607,26 +3638,11 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A145:E148"/>
-    <mergeCell ref="A139:C140"/>
-    <mergeCell ref="A113:E115"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3669,16 +3685,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="230"/>
-      <c r="M1" s="230"/>
-      <c r="N1" s="230"/>
-      <c r="O1" s="230"/>
-      <c r="P1" s="230"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3703,11 +3719,11 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="240">
+      <c r="P2" s="235">
         <v>11376831.439999999</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3731,82 +3747,82 @@
       <c r="R3" s="63"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="225" t="s">
+      <c r="A4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="241" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="143"/>
-      <c r="D4" s="223" t="s">
+      <c r="D4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="228" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="223" t="s">
+      <c r="F4" s="228" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="223" t="s">
+      <c r="G4" s="228" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="231" t="s">
+      <c r="H4" s="224" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="228" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="228" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="235" t="s">
+      <c r="K4" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="224" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="231" t="s">
+      <c r="N4" s="224" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="238" t="s">
+      <c r="O4" s="233" t="s">
         <v>63</v>
       </c>
       <c r="P4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="233" t="s">
+      <c r="Q4" s="226" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="241" t="s">
+      <c r="R4" s="236" t="s">
         <v>61</v>
       </c>
       <c r="U4" s="46"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="226"/>
-      <c r="B5" s="228"/>
+      <c r="A5" s="240"/>
+      <c r="B5" s="242"/>
       <c r="C5" s="144"/>
       <c r="D5" s="229"/>
       <c r="E5" s="229"/>
-      <c r="F5" s="224"/>
+      <c r="F5" s="238"/>
       <c r="G5" s="229"/>
-      <c r="H5" s="232"/>
+      <c r="H5" s="225"/>
       <c r="I5" s="229"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="232"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="232"/>
-      <c r="O5" s="239"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="225"/>
+      <c r="M5" s="232"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="234"/>
       <c r="P5" s="64" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q5" s="234"/>
-      <c r="R5" s="242"/>
+      <c r="Q5" s="227"/>
+      <c r="R5" s="237"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -8402,94 +8418,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="215" t="str">
+      <c r="E84" s="221" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="215"/>
-      <c r="G84" s="215"/>
-      <c r="H84" s="215"/>
-      <c r="I84" s="215"/>
-      <c r="J84" s="215"/>
-      <c r="K84" s="215"/>
-      <c r="L84" s="215"/>
-      <c r="M84" s="215"/>
-      <c r="N84" s="215"/>
-      <c r="O84" s="215"/>
-      <c r="P84" s="215"/>
+      <c r="F84" s="221"/>
+      <c r="G84" s="221"/>
+      <c r="H84" s="221"/>
+      <c r="I84" s="221"/>
+      <c r="J84" s="221"/>
+      <c r="K84" s="221"/>
+      <c r="L84" s="221"/>
+      <c r="M84" s="221"/>
+      <c r="N84" s="221"/>
+      <c r="O84" s="221"/>
+      <c r="P84" s="221"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E85" s="215"/>
-      <c r="F85" s="215"/>
-      <c r="G85" s="215"/>
-      <c r="H85" s="215"/>
-      <c r="I85" s="215"/>
-      <c r="J85" s="215"/>
-      <c r="K85" s="215"/>
-      <c r="L85" s="215"/>
-      <c r="M85" s="215"/>
-      <c r="N85" s="215"/>
-      <c r="O85" s="215"/>
-      <c r="P85" s="215"/>
+      <c r="E85" s="221"/>
+      <c r="F85" s="221"/>
+      <c r="G85" s="221"/>
+      <c r="H85" s="221"/>
+      <c r="I85" s="221"/>
+      <c r="J85" s="221"/>
+      <c r="K85" s="221"/>
+      <c r="L85" s="221"/>
+      <c r="M85" s="221"/>
+      <c r="N85" s="221"/>
+      <c r="O85" s="221"/>
+      <c r="P85" s="221"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E86" s="215"/>
-      <c r="F86" s="215"/>
-      <c r="G86" s="215"/>
-      <c r="H86" s="215"/>
-      <c r="I86" s="215"/>
-      <c r="J86" s="215"/>
-      <c r="K86" s="215"/>
-      <c r="L86" s="215"/>
-      <c r="M86" s="215"/>
-      <c r="N86" s="215"/>
-      <c r="O86" s="215"/>
-      <c r="P86" s="215"/>
+      <c r="E86" s="221"/>
+      <c r="F86" s="221"/>
+      <c r="G86" s="221"/>
+      <c r="H86" s="221"/>
+      <c r="I86" s="221"/>
+      <c r="J86" s="221"/>
+      <c r="K86" s="221"/>
+      <c r="L86" s="221"/>
+      <c r="M86" s="221"/>
+      <c r="N86" s="221"/>
+      <c r="O86" s="221"/>
+      <c r="P86" s="221"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="215"/>
-      <c r="F87" s="215"/>
-      <c r="G87" s="215"/>
-      <c r="H87" s="215"/>
-      <c r="I87" s="215"/>
-      <c r="J87" s="215"/>
-      <c r="K87" s="215"/>
-      <c r="L87" s="215"/>
-      <c r="M87" s="215"/>
-      <c r="N87" s="215"/>
-      <c r="O87" s="215"/>
-      <c r="P87" s="215"/>
+      <c r="E87" s="221"/>
+      <c r="F87" s="221"/>
+      <c r="G87" s="221"/>
+      <c r="H87" s="221"/>
+      <c r="I87" s="221"/>
+      <c r="J87" s="221"/>
+      <c r="K87" s="221"/>
+      <c r="L87" s="221"/>
+      <c r="M87" s="221"/>
+      <c r="N87" s="221"/>
+      <c r="O87" s="221"/>
+      <c r="P87" s="221"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E88" s="215"/>
-      <c r="F88" s="215"/>
-      <c r="G88" s="215"/>
-      <c r="H88" s="215"/>
-      <c r="I88" s="215"/>
-      <c r="J88" s="215"/>
-      <c r="K88" s="215"/>
-      <c r="L88" s="215"/>
-      <c r="M88" s="215"/>
-      <c r="N88" s="215"/>
-      <c r="O88" s="215"/>
-      <c r="P88" s="215"/>
+      <c r="E88" s="221"/>
+      <c r="F88" s="221"/>
+      <c r="G88" s="221"/>
+      <c r="H88" s="221"/>
+      <c r="I88" s="221"/>
+      <c r="J88" s="221"/>
+      <c r="K88" s="221"/>
+      <c r="L88" s="221"/>
+      <c r="M88" s="221"/>
+      <c r="N88" s="221"/>
+      <c r="O88" s="221"/>
+      <c r="P88" s="221"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="215"/>
-      <c r="F89" s="215"/>
-      <c r="G89" s="215"/>
-      <c r="H89" s="215"/>
-      <c r="I89" s="215"/>
-      <c r="J89" s="215"/>
-      <c r="K89" s="215"/>
-      <c r="L89" s="215"/>
-      <c r="M89" s="215"/>
-      <c r="N89" s="215"/>
-      <c r="O89" s="215"/>
-      <c r="P89" s="215"/>
+      <c r="E89" s="221"/>
+      <c r="F89" s="221"/>
+      <c r="G89" s="221"/>
+      <c r="H89" s="221"/>
+      <c r="I89" s="221"/>
+      <c r="J89" s="221"/>
+      <c r="K89" s="221"/>
+      <c r="L89" s="221"/>
+      <c r="M89" s="221"/>
+      <c r="N89" s="221"/>
+      <c r="O89" s="221"/>
+      <c r="P89" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="H4:H5"/>
@@ -8501,14 +8525,6 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="R4:R5"/>
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/GORRITI/Mayo/GORRITI-MAYO.xlsx
+++ b/GORRITI/Mayo/GORRITI-MAYO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155E890-66BD-4492-8A0F-9D122BACB4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A86D8D6-5DC9-4BF4-A245-A61732C051ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$147</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="255">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -480,9 +480,6 @@
     <t>MANDELLI MARIA</t>
   </si>
   <si>
-    <t>Analía</t>
-  </si>
-  <si>
     <t>BRITEZ M.</t>
   </si>
   <si>
@@ -597,9 +594,6 @@
     <t>ESTA ES WANDA VERON</t>
   </si>
   <si>
-    <t>SALDO EN BANCO ANTERIOR REAL</t>
-  </si>
-  <si>
     <t>BELEN CIACCIARELLI</t>
   </si>
   <si>
@@ -618,9 +612,6 @@
     <t>PUED ETRANSFERIR DESDE GALI NELLY MABEL</t>
   </si>
   <si>
-    <t>Transf 19/03</t>
-  </si>
-  <si>
     <t>Gastos ordinarios:</t>
   </si>
   <si>
@@ -636,51 +627,15 @@
     <t>Fumigacion Viturro Alberto</t>
   </si>
   <si>
-    <t>Transf 08/04</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
-    <t>PMC 08/04</t>
-  </si>
-  <si>
-    <t>PMC 04/04</t>
-  </si>
-  <si>
     <t>Metrogas - Cliente nro. 020495697900</t>
   </si>
   <si>
-    <t>Debito 10/04</t>
-  </si>
-  <si>
-    <t>Tranfs 14/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPL articulos de limpieza </t>
-  </si>
-  <si>
-    <t>Transf 16/04</t>
-  </si>
-  <si>
-    <t>Transf 22/04</t>
-  </si>
-  <si>
     <t>Transf 05/05</t>
   </si>
   <si>
-    <t xml:space="preserve">Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton </t>
-  </si>
-  <si>
-    <t>Transf 30/04</t>
-  </si>
-  <si>
     <t>LUIS SAAVEDRA FERNANDO ESPINO</t>
   </si>
   <si>
-    <t>MANTENIMIENTO DE CUENTA</t>
-  </si>
-  <si>
     <t>Luciana</t>
   </si>
   <si>
@@ -696,9 +651,6 @@
     <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES ABRIL - SE DEBE MAYO</t>
   </si>
   <si>
-    <t>Servicio de mantenimiento grupo electrogeno y porton de Septiembre 2024 a ABRIL 2025</t>
-  </si>
-  <si>
     <t>Clean home - Bolsas de consorcio</t>
   </si>
   <si>
@@ -711,9 +663,6 @@
     <t>Doartero materiales y mano de obra reparacion caño de gas 10A</t>
   </si>
   <si>
-    <t>EN ABRIL TENDRIAN QUE AUMENTAR, Y EN MAYO DEBEMOS PAGAR ABRIL Y DEBER MAYO</t>
-  </si>
-  <si>
     <t>Transf 07/05</t>
   </si>
   <si>
@@ -723,15 +672,9 @@
     <t>Transf 11/05</t>
   </si>
   <si>
-    <t>Impresiones</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ascensores Lema mantenimiento abril de 2 ascensores </t>
-  </si>
-  <si>
     <t>Destapaciones italoamericanas de cañerias deague de cocina y lavadero - mantenimiento de cañerias, repaso de ramales, columnas del 1er piso y sus dos salidas cloacales - Abono febrero, marzo y abril</t>
   </si>
   <si>
@@ -747,30 +690,18 @@
     <t>HAY DOS COMPROBANTES DE 210.000$ A DOARTERO QUE NOSE SI CORRESPONDEN A GASTOS YA PUESTOS O NO</t>
   </si>
   <si>
-    <t>Congett Mirta Graciela</t>
-  </si>
-  <si>
     <t>TRANSFERENCIAS A PATRIZIO DIEGO ROBERTO QUE NOSE A QUE GASTO CORRESPONDE</t>
   </si>
   <si>
     <t>Metrogas Plan de pagos cuota 3 de 4 - Cliente nro. 020495697900</t>
   </si>
   <si>
-    <t>Gonzalez Maximiliano - reparaciones con yeso, endudo y trabajo de pintura en comedor y balo del 12A</t>
-  </si>
-  <si>
     <t>Transf 23/05</t>
   </si>
   <si>
     <t>Transf 22/05</t>
   </si>
   <si>
-    <t>ruIZ DIEGO ARIEL</t>
-  </si>
-  <si>
-    <t>Vaciamiento de pozo en cocherw, sala de bomba y bauleras por colapso de agua de napa ganada por caudal - El dia 16/05 al 17/05 en guardia se asiste con bombas propias y personal hasta su vaciamiento total</t>
-  </si>
-  <si>
     <t>Transf 21/05</t>
   </si>
   <si>
@@ -778,6 +709,87 @@
   </si>
   <si>
     <t>Transf 26/05</t>
+  </si>
+  <si>
+    <t>Transf parcial 30/5</t>
+  </si>
+  <si>
+    <t>PMC 08/05</t>
+  </si>
+  <si>
+    <t>Debito 09/05</t>
+  </si>
+  <si>
+    <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton ABRIL Y MAYO</t>
+  </si>
+  <si>
+    <t>Castellano Alejandro - Trabajos realizados en grupo electrogeno según presupuesto - Cuota 1 adelanto que por emergencia de agua se postergo hasta principios del mes entrante</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t>Gonzalez Maximiliano - reparaciones con yeso, endudo y trabajo de pintura en comedor y baño del 12A</t>
+  </si>
+  <si>
+    <t>Castellano Alejandro - Resto de deuda año 2024/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascensores Lema mantenimiento </t>
+  </si>
+  <si>
+    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES ABRIL Y MAYO</t>
+  </si>
+  <si>
+    <t>Tranfs 13/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destapacion particular 6B italoamericana </t>
+  </si>
+  <si>
+    <t>Compra de bomba de achique CUBIC 07 Rotorpum nueva</t>
+  </si>
+  <si>
+    <t>Transf 19/05</t>
+  </si>
+  <si>
+    <t>Destapaciones italoamericano servicio abono febrero, marzo y abril</t>
+  </si>
+  <si>
+    <t>Toto calefaccion - Reparacion y cambio de varilla detectora de chispa del quemador y bujia que es la cjispa del encendido -  Mano de obra</t>
+  </si>
+  <si>
+    <t>Kromacolor - Compra de materiales (pintura, sellador, etc) reparacion techos 12A</t>
+  </si>
+  <si>
+    <t>Transf 12/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresiones de planos </t>
+  </si>
+  <si>
+    <t>PMC 14/04</t>
+  </si>
+  <si>
+    <t>Analía Ayelen Camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencia sin identificar 06/05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALDO ANTERIOR </t>
+  </si>
+  <si>
+    <t>Ingresos sin identificar</t>
+  </si>
+  <si>
+    <t>MANTENIMIENTO DE CUENTA - NO SE DEBITO</t>
+  </si>
+  <si>
+    <t>Vaciamiento de pozo en cocherA, sala de bomba y bauleras por colapso de agua de napa ganada por caudal - El dia 16/05 al 17/05 en guardia se asiste con bombas propias y personal hasta su vaciamiento total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE PRORRATEA UN MONTO MENOS A EL GASTO REAL EFECTUADO ($12.841.476,05) </t>
   </si>
 </sst>
 </file>
@@ -785,13 +797,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -991,7 +1003,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1480,11 +1492,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1492,7 +1504,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1507,9 +1519,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1525,7 +1537,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1535,40 +1547,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1583,7 +1595,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1591,18 +1603,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1615,27 +1627,27 @@
     <xf numFmtId="2" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1646,41 +1658,41 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1695,33 +1707,33 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1732,85 +1744,68 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="24" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="24" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1822,6 +1817,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1839,12 +1873,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1860,7 +1888,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1869,20 +1897,11 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2249,28 +2268,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M151"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="31"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="73" t="s">
         <v>118</v>
@@ -2279,7 +2298,7 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="75" t="s">
         <v>50</v>
@@ -2288,7 +2307,7 @@
       <c r="D3" s="75"/>
       <c r="E3" s="76"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
       <c r="B4" s="115" t="s">
         <v>116</v>
@@ -2299,7 +2318,7 @@
       </c>
       <c r="E4" s="76"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>0</v>
       </c>
@@ -2310,12 +2329,12 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>71</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="75" t="s">
@@ -2323,7 +2342,7 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>72</v>
       </c>
@@ -2334,57 +2353,57 @@
       </c>
       <c r="E7" s="21"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="218" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="218"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="218"/>
-      <c r="C10" s="218"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="218"/>
-      <c r="C11" s="218"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="217" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="219" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="219"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="219"/>
+      <c r="C10" s="219"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="219"/>
+      <c r="C11" s="219"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="218" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
-      <c r="B15" s="217"/>
-      <c r="C15" s="217"/>
-      <c r="D15" s="217"/>
-      <c r="E15" s="217"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="217"/>
-      <c r="B16" s="217"/>
-      <c r="C16" s="217"/>
-      <c r="D16" s="217"/>
-      <c r="E16" s="217"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="217"/>
-      <c r="B17" s="217"/>
-      <c r="C17" s="217"/>
-      <c r="D17" s="217"/>
-      <c r="E17" s="217"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="218"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="218"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="218"/>
+      <c r="B17" s="218"/>
+      <c r="C17" s="218"/>
+      <c r="D17" s="218"/>
+      <c r="E17" s="218"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2393,7 +2412,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
         <v>57</v>
       </c>
@@ -2402,34 +2421,34 @@
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
     </row>
-    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="170">
         <v>1227647</v>
       </c>
-      <c r="E23" s="120" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="164" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="170"/>
       <c r="E24" s="120"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="170"/>
       <c r="E25" s="120"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>58</v>
       </c>
@@ -2440,7 +2459,7 @@
       </c>
       <c r="E26" s="120"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2448,7 +2467,7 @@
       <c r="E27" s="120"/>
       <c r="G27" s="22"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="60" t="s">
         <v>59</v>
       </c>
@@ -2461,44 +2480,44 @@
       <c r="E28" s="172"/>
       <c r="G28" s="22">
         <f>D28+D37</f>
-        <v>2244127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2303751</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="170">
-        <v>1016480</v>
-      </c>
-      <c r="E29" s="120" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>1076104</v>
+      </c>
+      <c r="E29" s="164" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="170"/>
       <c r="E30" s="120"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="170"/>
       <c r="E31" s="120"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="173"/>
       <c r="E32" s="120"/>
     </row>
-    <row r="33" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>66</v>
       </c>
@@ -2507,7 +2526,7 @@
       <c r="D33" s="173"/>
       <c r="E33" s="120"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
@@ -2516,7 +2535,7 @@
       <c r="D34" s="173"/>
       <c r="E34" s="120"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>60</v>
       </c>
@@ -2527,14 +2546,14 @@
       </c>
       <c r="E35" s="120"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="173"/>
       <c r="E36" s="120"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="60" t="s">
         <v>59</v>
       </c>
@@ -2542,11 +2561,11 @@
       <c r="C37" s="60"/>
       <c r="D37" s="174">
         <f>SUM(D29:D36)</f>
-        <v>1016480</v>
+        <v>1076104</v>
       </c>
       <c r="E37" s="172"/>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="30" t="s">
         <v>1</v>
       </c>
@@ -2555,11 +2574,11 @@
       <c r="D38" s="175"/>
       <c r="E38" s="176">
         <f>D28+D37</f>
-        <v>2244127</v>
+        <v>2303751</v>
       </c>
       <c r="F38" s="22"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
         <v>39</v>
       </c>
@@ -2568,36 +2587,35 @@
       <c r="D39" s="177"/>
       <c r="E39" s="178"/>
     </row>
-    <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="211" t="s">
-        <v>222</v>
-      </c>
-      <c r="B40" s="212"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="204">
-        <v>56000</v>
-      </c>
-      <c r="E40" s="205" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="211" t="s">
-        <v>222</v>
-      </c>
-      <c r="B41" s="212"/>
+    <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="220" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="221"/>
+      <c r="C40" s="205"/>
+      <c r="D40" s="170">
+        <f>2*56000</f>
+        <v>112000</v>
+      </c>
+      <c r="E40" s="204" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="212" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="213"/>
       <c r="C41" s="55"/>
-      <c r="D41" s="204">
-        <v>230000</v>
-      </c>
-      <c r="E41" s="205" t="s">
-        <v>203</v>
-      </c>
-      <c r="H41" s="168" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D41" s="170">
+        <v>249000</v>
+      </c>
+      <c r="E41" s="204" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="147"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
         <v>33</v>
       </c>
@@ -2606,10 +2624,10 @@
       <c r="D42" s="179"/>
       <c r="E42" s="180">
         <f>SUM(D40:D41)</f>
-        <v>286000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>361000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="37" t="s">
         <v>54</v>
       </c>
@@ -2618,27 +2636,27 @@
       <c r="D43" s="181"/>
       <c r="E43" s="182"/>
     </row>
-    <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="213" t="s">
-        <v>169</v>
-      </c>
-      <c r="B44" s="214"/>
+    <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="210" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="211"/>
       <c r="C44" s="57"/>
       <c r="D44" s="183">
-        <v>120974</v>
+        <v>120977</v>
       </c>
       <c r="E44" s="184" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="213"/>
-      <c r="B45" s="214"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="210"/>
+      <c r="B45" s="211"/>
       <c r="C45" s="57"/>
       <c r="D45" s="185"/>
       <c r="E45" s="184"/>
     </row>
-    <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="30" t="s">
         <v>2</v>
       </c>
@@ -2647,10 +2665,10 @@
       <c r="D46" s="179"/>
       <c r="E46" s="121">
         <f>SUM(D44:D45)</f>
-        <v>120974</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>120977</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="37" t="s">
         <v>34</v>
       </c>
@@ -2659,36 +2677,36 @@
       <c r="D47" s="186"/>
       <c r="E47" s="187"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="55"/>
-      <c r="D48" s="208">
+      <c r="D48" s="209">
         <v>1644550.83</v>
       </c>
       <c r="E48" s="188" t="s">
+        <v>229</v>
+      </c>
+      <c r="G48" s="147"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="G48" s="147"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="206">
+      <c r="D49" s="189">
         <v>129055.15</v>
       </c>
       <c r="E49" s="190" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="str">
         <f>A49</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2697,15 +2715,15 @@
         <v>68</v>
       </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="206">
+      <c r="D50" s="189">
         <v>234412.98</v>
       </c>
       <c r="E50" s="190" t="str">
         <f>E49</f>
-        <v>Debito 14/04</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>Debito 12/05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="str">
         <f>A50</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2714,15 +2732,15 @@
         <v>37</v>
       </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="206">
+      <c r="D51" s="189">
         <v>14339.47</v>
       </c>
       <c r="E51" s="191" t="str">
         <f>E50</f>
-        <v>Debito 14/04</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 12/05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="30" t="s">
         <v>3</v>
       </c>
@@ -2734,7 +2752,7 @@
         <v>2022358.43</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
         <v>36</v>
       </c>
@@ -2743,26 +2761,26 @@
       <c r="D53" s="186"/>
       <c r="E53" s="187"/>
     </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="206">
+      <c r="D54" s="189">
         <v>814908.33</v>
       </c>
-      <c r="E54" s="207" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E54" s="202" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="206">
+      <c r="D55" s="189">
         <v>24398.76</v>
       </c>
       <c r="E55" s="193" t="str">
@@ -2770,13 +2788,13 @@
         <v>Transf 07/05</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="206">
+      <c r="D56" s="189">
         <v>15117.56</v>
       </c>
       <c r="E56" s="193" t="str">
@@ -2784,80 +2802,79 @@
         <v>Transf 07/05</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="206">
+      <c r="D57" s="189">
         <v>11961.98</v>
       </c>
-      <c r="E57" s="207" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E57" s="202" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="209">
-        <f>5015.88+9656.96</f>
-        <v>14672.84</v>
+      <c r="D58" s="189">
+        <v>9656.9599999999991</v>
       </c>
       <c r="E58" s="193" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="209">
-        <v>571923.57999999996</v>
-      </c>
-      <c r="E59" s="210" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D59" s="189">
+        <v>571919</v>
+      </c>
+      <c r="E59" s="193" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="189">
-        <v>21019.51</v>
+        <v>22050.01</v>
       </c>
       <c r="E60" s="194" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="213" t="s">
-        <v>171</v>
-      </c>
-      <c r="B61" s="214"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="210" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="211"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="206">
+      <c r="D61" s="189">
         <v>2302294.3199999998</v>
       </c>
       <c r="E61" s="193" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="213"/>
-      <c r="B62" s="214"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="210"/>
+      <c r="B62" s="211"/>
       <c r="C62" s="166"/>
-      <c r="D62" s="215"/>
-      <c r="E62" s="216"/>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D62" s="216"/>
+      <c r="E62" s="217"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
         <v>4</v>
       </c>
@@ -2866,10 +2883,10 @@
       <c r="D63" s="179"/>
       <c r="E63" s="121">
         <f>SUM(D54:D62)</f>
-        <v>3776296.88</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3772306.92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="37" t="s">
         <v>35</v>
       </c>
@@ -2878,757 +2895,769 @@
       <c r="D64" s="179"/>
       <c r="E64" s="195"/>
     </row>
-    <row r="65" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="211" t="s">
+    <row r="65" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="212" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="213"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="189">
+        <f>72600+360000</f>
+        <v>432600</v>
+      </c>
+      <c r="E65" s="126" t="s">
         <v>214</v>
       </c>
-      <c r="B65" s="212"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="206">
-        <v>72600</v>
-      </c>
-      <c r="E65" s="126" t="s">
+    </row>
+    <row r="66" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="212" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="211" t="s">
-        <v>214</v>
-      </c>
-      <c r="B66" s="212"/>
+      <c r="B66" s="213"/>
       <c r="C66" s="58"/>
-      <c r="D66" s="206">
+      <c r="D66" s="189">
+        <v>96800</v>
+      </c>
+      <c r="E66" s="126" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="212" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67" s="213"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="189">
         <v>38000</v>
       </c>
-      <c r="E66" s="126" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="211" t="s">
-        <v>214</v>
-      </c>
-      <c r="B67" s="212"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="206">
-        <v>360000</v>
-      </c>
       <c r="E67" s="126" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="209">
+      <c r="D68" s="189">
         <v>52000</v>
       </c>
-      <c r="E68" s="196" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E68" s="202" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B69" s="167"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="206">
+      <c r="D69" s="189">
         <v>53500</v>
       </c>
-      <c r="E69" s="196" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E69" s="202" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B70" s="167"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="206">
+      <c r="D70" s="189">
         <v>120000</v>
       </c>
-      <c r="E70" s="194" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="213" t="s">
-        <v>223</v>
-      </c>
-      <c r="B71" s="214"/>
+      <c r="E70" s="203" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="210" t="s">
+        <v>244</v>
+      </c>
+      <c r="B71" s="211"/>
       <c r="C71" s="5"/>
       <c r="D71" s="189">
-        <v>338800</v>
+        <v>111908.93</v>
       </c>
       <c r="E71" s="196" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="H71" s="168" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="212" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="213"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="189">
+        <v>240000</v>
+      </c>
+      <c r="E72" s="203" t="s">
+        <v>238</v>
+      </c>
+      <c r="H72" s="168" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="212" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" s="213"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="124">
+        <v>260000</v>
+      </c>
+      <c r="E73" s="194" t="s">
+        <v>225</v>
+      </c>
+      <c r="H73" s="168"/>
+    </row>
+    <row r="74" spans="1:8" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="212" t="s">
+        <v>216</v>
+      </c>
+      <c r="B74" s="213"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="124">
+        <v>240000</v>
+      </c>
+      <c r="E74" s="194" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="212" t="s">
+        <v>218</v>
+      </c>
+      <c r="B75" s="213"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="124">
+        <v>45000</v>
+      </c>
+      <c r="E75" s="194" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="212" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" s="213"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="124">
+        <v>130000</v>
+      </c>
+      <c r="E76" s="194" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="212" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" s="213"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="124">
+        <v>210000</v>
+      </c>
+      <c r="E77" s="194" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="212" t="s">
+        <v>210</v>
+      </c>
+      <c r="B78" s="213"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="124">
+        <v>115000</v>
+      </c>
+      <c r="E78" s="194" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="213"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="124">
+        <v>360000</v>
+      </c>
+      <c r="E79" s="194" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="208" t="s">
+        <v>240</v>
+      </c>
+      <c r="B80" s="201"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="124">
+        <v>710000</v>
+      </c>
+      <c r="E80" s="194" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="211" t="s">
+    <row r="81" spans="1:10" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="212" t="s">
+        <v>253</v>
+      </c>
+      <c r="B81" s="213"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="124">
+        <v>770000</v>
+      </c>
+      <c r="E81" s="194" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="212" t="s">
+        <v>226</v>
+      </c>
+      <c r="B82" s="213"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="124">
+        <v>120000</v>
+      </c>
+      <c r="E82" s="194" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="200" t="s">
         <v>246</v>
       </c>
-      <c r="B72" s="212"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="206">
-        <v>260000</v>
-      </c>
-      <c r="E72" s="203" t="s">
-        <v>245</v>
-      </c>
-      <c r="H72" s="168"/>
-    </row>
-    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="219" t="s">
-        <v>240</v>
-      </c>
-      <c r="B73" s="220"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="206">
-        <v>120000</v>
-      </c>
-      <c r="E73" s="194" t="s">
-        <v>211</v>
-      </c>
-      <c r="H73" s="168" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="219" t="s">
-        <v>235</v>
-      </c>
-      <c r="B74" s="220"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="152">
-        <v>305000</v>
-      </c>
-      <c r="E74" s="194" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="219" t="s">
-        <v>237</v>
-      </c>
-      <c r="B75" s="220"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="152">
-        <v>45000</v>
-      </c>
-      <c r="E75" s="203" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="219" t="s">
-        <v>238</v>
-      </c>
-      <c r="B76" s="220"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="152">
-        <v>130000</v>
-      </c>
-      <c r="E76" s="203" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="219" t="s">
-        <v>227</v>
-      </c>
-      <c r="B77" s="220"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="152">
-        <v>210000</v>
-      </c>
-      <c r="E77" s="203" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="219" t="s">
-        <v>226</v>
-      </c>
-      <c r="B78" s="220"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="152">
-        <v>115000</v>
-      </c>
-      <c r="E78" s="203" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="219" t="s">
-        <v>243</v>
-      </c>
-      <c r="B79" s="220"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="152">
-        <v>360000</v>
-      </c>
-      <c r="E79" s="203" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="219" t="s">
-        <v>247</v>
-      </c>
-      <c r="B80" s="220"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="152">
-        <v>770000</v>
-      </c>
-      <c r="E80" s="203" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="201" t="s">
-        <v>249</v>
-      </c>
-      <c r="B81" s="202"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="152">
-        <v>120000</v>
-      </c>
-      <c r="E81" s="203" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="201" t="s">
-        <v>232</v>
-      </c>
-      <c r="B82" s="202"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="152">
+      <c r="B83" s="201"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="124">
         <v>12000</v>
       </c>
-      <c r="E82" s="203" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="219" t="s">
-        <v>224</v>
-      </c>
-      <c r="B83" s="220"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="152">
+      <c r="E83" s="194" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="212" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="213"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="124">
         <f>1600+6400</f>
         <v>8000</v>
       </c>
-      <c r="E83" s="194" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="213" t="s">
-        <v>210</v>
-      </c>
-      <c r="B84" s="214"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="124">
-        <v>146900</v>
-      </c>
-      <c r="E84" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="I84" s="213"/>
-      <c r="J84" s="214"/>
-    </row>
-    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="30" t="s">
+      <c r="E84" s="194"/>
+    </row>
+    <row r="85" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="210"/>
+      <c r="B85" s="211"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="124"/>
+      <c r="E85" s="197"/>
+      <c r="I85" s="210"/>
+      <c r="J85" s="211"/>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B85" s="37"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="198">
-        <f>SUM(D65:D84)</f>
-        <v>3636800</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="37" t="s">
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="198">
+        <f>SUM(D65:D85)</f>
+        <v>4124808.9299999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B86" s="71"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="175"/>
-      <c r="E86" s="195"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
+      <c r="B87" s="71"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="175"/>
+      <c r="E87" s="195"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="189">
-        <f>37181.67+5673.24+21952.02+27190.88+9051.16+45454.76</f>
-        <v>146503.73000000001</v>
-      </c>
-      <c r="E87" s="199"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
       <c r="D88" s="189">
-        <v>46383.47</v>
-      </c>
-      <c r="E88" s="126"/>
-    </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="54" t="s">
+        <f>14894.24+10203+42365+10884.56+32649.71+17876.73+7400.53</f>
+        <v>136273.76999999999</v>
+      </c>
+      <c r="E88" s="199"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="189"/>
+      <c r="E89" s="126"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B89" s="54"/>
-      <c r="C89" s="54"/>
-      <c r="D89" s="127"/>
-      <c r="E89" s="121">
-        <f>SUM(D87:D88)</f>
-        <v>192887.2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="120"/>
-      <c r="E90" s="128"/>
-    </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="B91" s="32"/>
-      <c r="C91" s="32"/>
-      <c r="D91" s="129"/>
-      <c r="E91" s="130">
-        <v>1468681.28</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="1"/>
-      <c r="D92" s="131"/>
-      <c r="E92" s="132"/>
-      <c r="F92" s="46"/>
-    </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
+      <c r="B90" s="54"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="127"/>
+      <c r="E90" s="121">
+        <f>SUM(D88:D89)</f>
+        <v>136273.76999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="120"/>
+      <c r="E91" s="128"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="129"/>
+      <c r="E92" s="130"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="D93" s="131"/>
+      <c r="E93" s="132"/>
+      <c r="F93" s="46"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B93" s="10"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="133"/>
-      <c r="E93" s="134">
-        <f>(SUM(E31:E91))</f>
-        <v>13748124.789999997</v>
-      </c>
-      <c r="F93" s="163"/>
-      <c r="G93" s="46"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D94" s="131"/>
-      <c r="E94" s="131"/>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="10"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="133"/>
+      <c r="E94" s="134">
+        <f>(SUM(E31:E92))</f>
+        <v>12841476.049999999</v>
+      </c>
+      <c r="F94" s="163"/>
+      <c r="G94" s="46"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D95" s="131"/>
       <c r="E95" s="131"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="135"/>
-      <c r="E96" s="136"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="213"/>
-      <c r="B97" s="214"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="152"/>
-      <c r="E97" s="122"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="213"/>
-      <c r="B98" s="214"/>
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="131"/>
+      <c r="E96" s="131"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B97" s="12"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="135"/>
+      <c r="E97" s="136"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="210"/>
+      <c r="B98" s="211"/>
       <c r="C98" s="5"/>
-      <c r="D98" s="124"/>
+      <c r="D98" s="152"/>
       <c r="E98" s="122"/>
     </row>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="219"/>
-      <c r="B99" s="220"/>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="210"/>
+      <c r="B99" s="211"/>
       <c r="C99" s="5"/>
       <c r="D99" s="124"/>
       <c r="E99" s="122"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="123"/>
-      <c r="B100" s="125"/>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="212"/>
+      <c r="B100" s="213"/>
       <c r="C100" s="5"/>
       <c r="D100" s="124"/>
       <c r="E100" s="122"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="52"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61">
-        <f>SUM(D97:D100)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="32" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="123"/>
+      <c r="B101" s="125"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="124"/>
+      <c r="E101" s="122"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="52"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="61"/>
+      <c r="E102" s="61">
+        <f>SUM(D98:D101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B104" s="32"/>
-      <c r="C104" s="32"/>
-      <c r="D104" s="33"/>
-      <c r="E104" s="119"/>
-    </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="3" t="s">
+      <c r="B105" s="32"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="119"/>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B106" s="10"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="72">
-        <f>E101+E104</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="116" t="s">
+      <c r="B107" s="10"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="72">
+        <f>E102+E105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="B108" s="117">
-        <f>E93</f>
-        <v>13748124.789999997</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="116" t="s">
+      <c r="B109" s="117">
+        <f>E94</f>
+        <v>12841476.049999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="B109" s="117">
-        <f>E93-E91</f>
-        <v>12279443.509999998</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="116" t="s">
+      <c r="B110" s="117">
+        <f>E94-E92</f>
+        <v>12841476.049999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="B110" s="117">
-        <f>E106-E104</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="116" t="s">
+      <c r="B111" s="117">
+        <f>E107-E105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="B111" s="117">
-        <f>E106</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="221"/>
-      <c r="B114" s="221"/>
-      <c r="C114" s="221"/>
-      <c r="D114" s="221"/>
-      <c r="E114" s="221"/>
-    </row>
-    <row r="115" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="221"/>
-      <c r="B115" s="221"/>
-      <c r="C115" s="221"/>
-      <c r="D115" s="221"/>
-      <c r="E115" s="221"/>
-    </row>
-    <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="221"/>
-      <c r="B116" s="221"/>
-      <c r="C116" s="221"/>
-      <c r="D116" s="221"/>
-      <c r="E116" s="221"/>
-    </row>
-    <row r="118" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="23" t="s">
+      <c r="B112" s="117">
+        <f>E107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="242" t="s">
+        <v>254</v>
+      </c>
+      <c r="B113" s="243"/>
+    </row>
+    <row r="114" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="214"/>
+      <c r="B115" s="214"/>
+      <c r="C115" s="214"/>
+      <c r="D115" s="214"/>
+      <c r="E115" s="214"/>
+    </row>
+    <row r="116" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="214"/>
+      <c r="B116" s="214"/>
+      <c r="C116" s="214"/>
+      <c r="D116" s="214"/>
+      <c r="E116" s="214"/>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="214"/>
+      <c r="B117" s="214"/>
+      <c r="C117" s="214"/>
+      <c r="D117" s="214"/>
+      <c r="E117" s="214"/>
+    </row>
+    <row r="119" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B118" s="148"/>
-      <c r="C118" s="24"/>
-    </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="35"/>
-      <c r="B119" s="62">
-        <v>0</v>
-      </c>
-      <c r="C119" s="26"/>
-    </row>
-    <row r="120" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="25" t="s">
+      <c r="B119" s="148"/>
+      <c r="C119" s="24"/>
+    </row>
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="35"/>
+      <c r="B120" s="62">
+        <v>0</v>
+      </c>
+      <c r="C120" s="26"/>
+    </row>
+    <row r="121" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B120" s="42">
+      <c r="B121" s="42">
         <f>PRORRATEO!I81</f>
-        <v>11284159.269999998</v>
-      </c>
-      <c r="C120" s="24"/>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="25"/>
-      <c r="B121" s="42">
-        <v>0</v>
+        <v>10964795.799999999</v>
       </c>
       <c r="C121" s="24"/>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="25" t="s">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="42">
+        <v>0</v>
+      </c>
+      <c r="C122" s="24"/>
+    </row>
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B122" s="126">
-        <f>B144</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="24"/>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="28"/>
-      <c r="B123" s="50"/>
+      <c r="B123" s="126">
+        <f>B146</f>
+        <v>184089</v>
+      </c>
       <c r="C123" s="24"/>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="142" t="s">
-        <v>172</v>
-      </c>
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="28"/>
       <c r="B124" s="50"/>
       <c r="C124" s="24"/>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="41" t="s">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="142" t="s">
+        <v>171</v>
+      </c>
+      <c r="B125" s="50"/>
+      <c r="C125" s="24"/>
+    </row>
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B125" s="50">
-        <f>-B109</f>
-        <v>-12279443.509999998</v>
-      </c>
-      <c r="C125" s="24"/>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="28" t="s">
+      <c r="B126" s="50">
+        <f>-B110</f>
+        <v>-12841476.049999999</v>
+      </c>
+      <c r="C126" s="24"/>
+    </row>
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B126" s="50">
-        <f>-(B110)</f>
-        <v>0</v>
-      </c>
-      <c r="C126" s="24"/>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="34" t="s">
+      <c r="B127" s="50">
+        <f>-(B111)</f>
+        <v>0</v>
+      </c>
+      <c r="C127" s="24"/>
+    </row>
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B127" s="62">
-        <f>SUM(B119:B126)</f>
-        <v>-995284.24000000022</v>
-      </c>
-      <c r="C127" s="27"/>
-      <c r="D127" s="46"/>
-    </row>
-    <row r="128" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="43"/>
+      <c r="B128" s="62">
+        <f>SUM(B120:B127)</f>
+        <v>-1692591.25</v>
+      </c>
       <c r="C128" s="27"/>
       <c r="D128" s="46"/>
-      <c r="E128" s="149"/>
-      <c r="F128" s="150"/>
-    </row>
-    <row r="129" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="44"/>
+    </row>
+    <row r="129" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="43"/>
       <c r="C129" s="27"/>
-    </row>
-    <row r="130" spans="1:4" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130"/>
-      <c r="B130" s="43"/>
-      <c r="C130" s="39"/>
-    </row>
-    <row r="131" spans="1:4" s="40" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="154" t="s">
-        <v>190</v>
-      </c>
-      <c r="B131" s="155">
-        <v>66313.089999996126</v>
-      </c>
+      <c r="D129" s="46"/>
+      <c r="E129" s="149"/>
+      <c r="F129" s="150"/>
+    </row>
+    <row r="130" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="44"/>
+      <c r="C130" s="27"/>
+    </row>
+    <row r="131" spans="1:6" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131"/>
+      <c r="B131" s="43"/>
       <c r="C131" s="39"/>
-      <c r="D131" s="49"/>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="B132" s="159">
-        <f>-B109</f>
-        <v>-12279443.509999998</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:6" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="154" t="s">
+        <v>250</v>
+      </c>
+      <c r="B132" s="155">
+        <v>1422704.1999999937</v>
+      </c>
+      <c r="C132" s="39"/>
+      <c r="D132" s="49"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="57" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B133" s="159">
         <f>-B110</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-12841476.049999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="B134" s="160">
+        <v>192</v>
+      </c>
+      <c r="B134" s="159">
+        <f>-B111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" s="159">
+        <f>B146</f>
+        <v>184089</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B136" s="160">
         <f>PRORRATEO!I81</f>
-        <v>11284159.269999998</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="57"/>
-      <c r="B135" s="160"/>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="161" t="s">
-        <v>199</v>
-      </c>
-      <c r="B136" s="162">
-        <f>-(11743+7875)</f>
-        <v>-19618</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="157" t="s">
-        <v>184</v>
-      </c>
-      <c r="B137" s="158">
-        <f>SUM(B131:C136)</f>
-        <v>-948589.1500000041</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="156"/>
-      <c r="B138" s="156"/>
-    </row>
-    <row r="139" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="222" t="s">
+        <v>10964795.799999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="B137" s="206">
+        <v>-65000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="161" t="s">
+        <v>196</v>
+      </c>
+      <c r="B138" s="162"/>
+    </row>
+    <row r="139" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="157" t="s">
+        <v>183</v>
+      </c>
+      <c r="B139" s="158">
+        <f>SUM(B132:C138)</f>
+        <v>-334887.05000000633</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="156"/>
+      <c r="B140" s="156"/>
+    </row>
+    <row r="141" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="215" t="s">
         <v>55</v>
       </c>
-      <c r="B140" s="222"/>
-      <c r="C140" s="222"/>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="222"/>
-      <c r="B141" s="222"/>
-      <c r="C141" s="222"/>
-    </row>
-    <row r="142" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="139"/>
-      <c r="B142" s="38"/>
-      <c r="C142" s="38">
+      <c r="B142" s="215"/>
+      <c r="C142" s="215"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="215"/>
+      <c r="B143" s="215"/>
+      <c r="C143" s="215"/>
+    </row>
+    <row r="144" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="B144" s="38">
+        <v>184089</v>
+      </c>
+      <c r="C144" s="38">
         <v>40000</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="139"/>
-      <c r="B143" s="141"/>
-      <c r="C143" s="137"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="47" t="s">
+    <row r="145" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="139"/>
+      <c r="B145" s="141"/>
+      <c r="C145" s="137"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B144" s="140">
-        <f>SUM(B142:B143)</f>
-        <v>0</v>
-      </c>
-      <c r="C144" s="48"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M145" s="8"/>
-    </row>
-    <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="221"/>
-      <c r="B146" s="221"/>
-      <c r="C146" s="221"/>
-      <c r="D146" s="221"/>
-      <c r="E146" s="221"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A147" s="221"/>
-      <c r="B147" s="221"/>
-      <c r="C147" s="221"/>
-      <c r="D147" s="221"/>
-      <c r="E147" s="221"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A148" s="221"/>
-      <c r="B148" s="221"/>
-      <c r="C148" s="221"/>
-      <c r="D148" s="221"/>
-      <c r="E148" s="221"/>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A149" s="221"/>
-      <c r="B149" s="221"/>
-      <c r="C149" s="221"/>
-      <c r="D149" s="221"/>
-      <c r="E149" s="221"/>
+      <c r="B146" s="140">
+        <f>SUM(B144:B145)</f>
+        <v>184089</v>
+      </c>
+      <c r="C146" s="48"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M147" s="8"/>
+    </row>
+    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="214"/>
+      <c r="B148" s="214"/>
+      <c r="C148" s="214"/>
+      <c r="D148" s="214"/>
+      <c r="E148" s="214"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="214"/>
+      <c r="B149" s="214"/>
+      <c r="C149" s="214"/>
+      <c r="D149" s="214"/>
+      <c r="E149" s="214"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="214"/>
+      <c r="B150" s="214"/>
+      <c r="C150" s="214"/>
+      <c r="D150" s="214"/>
+      <c r="E150" s="214"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="214"/>
+      <c r="B151" s="214"/>
+      <c r="C151" s="214"/>
+      <c r="D151" s="214"/>
+      <c r="E151" s="214"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="I84:J84"/>
+  <mergeCells count="33">
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A82:B82"/>
     <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A146:E149"/>
-    <mergeCell ref="A140:C141"/>
-    <mergeCell ref="A114:E116"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="D62:E62"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="B9:C11"/>
@@ -3638,11 +3667,22 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="I85:J85"/>
     <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A148:E151"/>
+    <mergeCell ref="A142:C143"/>
+    <mergeCell ref="A115:E117"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A113:B113"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3653,52 +3693,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" customWidth="1"/>
-    <col min="4" max="4" width="4.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" customWidth="1"/>
-    <col min="13" max="13" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" customWidth="1"/>
-    <col min="15" max="15" width="8.44140625" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
-    <col min="19" max="19" width="0.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="13" max="13" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="0.42578125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="19" max="19" width="0.140625" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
-      <c r="P1" s="223"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3714,19 +3754,19 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="235">
-        <v>11376831.439999999</v>
-      </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
+      <c r="P2" s="239">
+        <v>12376831.439999999</v>
+      </c>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
       <c r="S2" s="22"/>
     </row>
-    <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3746,85 +3786,85 @@
       <c r="Q3" s="59"/>
       <c r="R3" s="63"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="239" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="226" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="143"/>
-      <c r="D4" s="228" t="s">
+      <c r="D4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="228" t="s">
+      <c r="E4" s="222" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="228" t="s">
+      <c r="F4" s="222" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="228" t="s">
+      <c r="G4" s="222" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="224" t="s">
-        <v>187</v>
-      </c>
-      <c r="I4" s="228" t="s">
+      <c r="H4" s="230" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="222" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="228" t="s">
+      <c r="J4" s="222" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="230" t="s">
+      <c r="K4" s="234" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="230" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="224" t="s">
+      <c r="M4" s="230" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="224" t="s">
+      <c r="N4" s="230" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="233" t="s">
+      <c r="O4" s="237" t="s">
         <v>63</v>
       </c>
       <c r="P4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="226" t="s">
+      <c r="Q4" s="232" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="236" t="s">
+      <c r="R4" s="240" t="s">
         <v>61</v>
       </c>
       <c r="U4" s="46"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="240"/>
-      <c r="B5" s="242"/>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="225"/>
+      <c r="B5" s="227"/>
       <c r="C5" s="144"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="232"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="234"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="231"/>
+      <c r="M5" s="236"/>
+      <c r="N5" s="231"/>
+      <c r="O5" s="238"/>
       <c r="P5" s="64" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q5" s="227"/>
-      <c r="R5" s="237"/>
-    </row>
-    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q5" s="233"/>
+      <c r="R5" s="241"/>
+    </row>
+    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3863,31 +3903,31 @@
       </c>
       <c r="N6" s="83">
         <f t="shared" ref="N6:N69" si="0">P$2*G6%</f>
-        <v>58374.522118640001</v>
+        <v>63505.522118640001</v>
       </c>
       <c r="O6" s="84">
         <v>0</v>
       </c>
       <c r="P6" s="85">
         <f>ROUND(SUM(K6:O6),0) + S6</f>
-        <v>58374.01</v>
+        <v>63505.01</v>
       </c>
       <c r="Q6" s="86">
         <f>ROUND(P6*6% + P6,0) + S6</f>
-        <v>61876.01</v>
+        <v>67315.009999999995</v>
       </c>
       <c r="R6" s="87">
         <f>ROUND(P6*3%,0) + P6</f>
-        <v>60125.01</v>
+        <v>65410.01</v>
       </c>
       <c r="S6" s="46">
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3927,22 +3967,22 @@
       </c>
       <c r="N7" s="83">
         <f t="shared" si="0"/>
-        <v>69614.831581360006</v>
+        <v>75733.831581360006</v>
       </c>
       <c r="O7" s="84">
         <v>0</v>
       </c>
       <c r="P7" s="85">
         <f t="shared" ref="P7:P70" si="3">ROUND(SUM(K7:O7),0) + S7</f>
-        <v>69615.02</v>
+        <v>75734.02</v>
       </c>
       <c r="Q7" s="86">
         <f t="shared" ref="Q7:Q70" si="4">ROUND(P7*6% + P7,0) + S7</f>
-        <v>73792.02</v>
+        <v>80278.02</v>
       </c>
       <c r="R7" s="87">
         <f t="shared" ref="R7:R70" si="5">ROUND(P7*3%,0) + P7</f>
-        <v>71703.02</v>
+        <v>78006.02</v>
       </c>
       <c r="S7" s="46">
         <f>S6+0.01</f>
@@ -3950,7 +3990,7 @@
       </c>
       <c r="T7" s="46"/>
     </row>
-    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3970,49 +4010,46 @@
         <v>0.61150000000000004</v>
       </c>
       <c r="H8" s="78">
-        <v>134959.03</v>
-      </c>
-      <c r="I8" s="169">
-        <f>351410-I9-I10</f>
-        <v>134958.91000000003</v>
-      </c>
+        <v>69569.03</v>
+      </c>
+      <c r="I8" s="169"/>
       <c r="J8" s="80"/>
       <c r="K8" s="81">
         <f t="shared" si="1"/>
-        <v>0.11999999996623956</v>
+        <v>69569.03</v>
       </c>
       <c r="L8" s="81">
         <f t="shared" si="2"/>
-        <v>3.5999999989871864E-3</v>
+        <v>2087.0708999999997</v>
       </c>
       <c r="M8" s="82">
         <v>0</v>
       </c>
       <c r="N8" s="83">
         <f t="shared" si="0"/>
-        <v>69569.324255600004</v>
+        <v>75684.324255600004</v>
       </c>
       <c r="O8" s="84">
         <v>0</v>
       </c>
       <c r="P8" s="85">
         <f t="shared" si="3"/>
-        <v>69569.03</v>
+        <v>147340.03</v>
       </c>
       <c r="Q8" s="86">
         <f t="shared" si="4"/>
-        <v>73743.03</v>
+        <v>156180.03</v>
       </c>
       <c r="R8" s="87">
         <f t="shared" si="5"/>
-        <v>71656.03</v>
+        <v>151760.03</v>
       </c>
       <c r="S8" s="46">
         <f t="shared" ref="S8:S71" si="7">S7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -4032,42 +4069,39 @@
         <v>0.50329999999999997</v>
       </c>
       <c r="H9" s="78">
-        <v>111079.03999999999</v>
-      </c>
-      <c r="I9" s="169">
-        <f>H9</f>
-        <v>111079.03999999999</v>
-      </c>
+        <v>57260.04</v>
+      </c>
+      <c r="I9" s="169"/>
       <c r="J9" s="80"/>
       <c r="K9" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>57260.04</v>
       </c>
       <c r="L9" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1717.8011999999999</v>
       </c>
       <c r="M9" s="82">
         <v>0</v>
       </c>
       <c r="N9" s="83">
         <f t="shared" si="0"/>
-        <v>57259.592637519992</v>
+        <v>62292.592637519985</v>
       </c>
       <c r="O9" s="84">
         <v>0</v>
       </c>
       <c r="P9" s="85">
         <f t="shared" si="3"/>
-        <v>57260.04</v>
+        <v>121270.04</v>
       </c>
       <c r="Q9" s="86">
         <f t="shared" si="4"/>
-        <v>60696.04</v>
+        <v>128546.04</v>
       </c>
       <c r="R9" s="87">
         <f t="shared" si="5"/>
-        <v>58978.04</v>
+        <v>124908.04</v>
       </c>
       <c r="S9" s="46">
         <f t="shared" si="7"/>
@@ -4075,7 +4109,7 @@
       </c>
       <c r="U9" s="46"/>
     </row>
-    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -4095,42 +4129,39 @@
         <v>0.50329999999999997</v>
       </c>
       <c r="H10" s="78">
-        <v>105372.05</v>
-      </c>
-      <c r="I10" s="169">
-        <f>H10</f>
-        <v>105372.05</v>
-      </c>
+        <v>57260.05</v>
+      </c>
+      <c r="I10" s="169"/>
       <c r="J10" s="80"/>
       <c r="K10" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>57260.05</v>
       </c>
       <c r="L10" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1717.8015</v>
       </c>
       <c r="M10" s="82">
         <v>0</v>
       </c>
       <c r="N10" s="83">
         <f t="shared" si="0"/>
-        <v>57259.592637519992</v>
+        <v>62292.592637519985</v>
       </c>
       <c r="O10" s="84">
         <v>0</v>
       </c>
       <c r="P10" s="85">
         <f t="shared" si="3"/>
-        <v>57260.05</v>
+        <v>121270.05</v>
       </c>
       <c r="Q10" s="86">
         <f t="shared" si="4"/>
-        <v>60696.05</v>
+        <v>128546.05</v>
       </c>
       <c r="R10" s="87">
         <f t="shared" si="5"/>
-        <v>58978.05</v>
+        <v>124908.05</v>
       </c>
       <c r="S10" s="46">
         <f t="shared" si="7"/>
@@ -4138,7 +4169,7 @@
       </c>
       <c r="U10" s="46"/>
     </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -4180,29 +4211,29 @@
       </c>
       <c r="N11" s="83">
         <f t="shared" si="0"/>
-        <v>85314.858968560002</v>
+        <v>92813.858968560002</v>
       </c>
       <c r="O11" s="84">
         <v>0</v>
       </c>
       <c r="P11" s="85">
         <f t="shared" si="3"/>
-        <v>85315.06</v>
+        <v>92814.06</v>
       </c>
       <c r="Q11" s="86">
         <f t="shared" si="4"/>
-        <v>90434.06</v>
+        <v>98383.06</v>
       </c>
       <c r="R11" s="87">
         <f t="shared" si="5"/>
-        <v>87874.06</v>
+        <v>95598.06</v>
       </c>
       <c r="S11" s="46">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -4244,29 +4275,29 @@
       </c>
       <c r="N12" s="83">
         <f t="shared" si="0"/>
-        <v>61719.310561999999</v>
+        <v>67144.310561999999</v>
       </c>
       <c r="O12" s="84">
         <v>0</v>
       </c>
       <c r="P12" s="85">
         <f t="shared" si="3"/>
-        <v>61719.07</v>
+        <v>67144.070000000007</v>
       </c>
       <c r="Q12" s="86">
         <f t="shared" si="4"/>
-        <v>65422.07</v>
+        <v>71173.070000000007</v>
       </c>
       <c r="R12" s="87">
         <f t="shared" si="5"/>
-        <v>63571.07</v>
+        <v>69158.070000000007</v>
       </c>
       <c r="S12" s="46">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -4306,29 +4337,29 @@
       </c>
       <c r="N13" s="83">
         <f t="shared" si="0"/>
-        <v>51616.684243279997</v>
+        <v>56153.684243280004</v>
       </c>
       <c r="O13" s="84">
         <v>0</v>
       </c>
       <c r="P13" s="85">
         <f t="shared" si="3"/>
-        <v>51617.08</v>
+        <v>56154.080000000002</v>
       </c>
       <c r="Q13" s="86">
         <f t="shared" si="4"/>
-        <v>54714.080000000002</v>
+        <v>59523.08</v>
       </c>
       <c r="R13" s="87">
         <f t="shared" si="5"/>
-        <v>53166.080000000002</v>
+        <v>57839.08</v>
       </c>
       <c r="S13" s="46">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -4343,56 +4374,59 @@
       <c r="E14" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="69"/>
+      <c r="F14" s="69" t="s">
+        <v>203</v>
+      </c>
       <c r="G14" s="77">
         <v>0.52439999999999998</v>
       </c>
       <c r="H14" s="78">
-        <v>115735.09</v>
+        <v>117417.09</v>
       </c>
       <c r="I14" s="169">
-        <v>59660.09</v>
+        <f>H14-59660</f>
+        <v>57757.09</v>
       </c>
       <c r="J14" s="80"/>
       <c r="K14" s="81">
         <f t="shared" si="1"/>
-        <v>56075</v>
+        <v>59660</v>
       </c>
       <c r="L14" s="81">
         <f t="shared" si="2"/>
-        <v>1682.25</v>
+        <v>1789.8</v>
       </c>
       <c r="M14" s="82">
         <v>0</v>
       </c>
       <c r="N14" s="83">
         <f t="shared" si="0"/>
-        <v>59660.104071359994</v>
+        <v>64904.104071359994</v>
       </c>
       <c r="O14" s="84">
         <v>0</v>
       </c>
       <c r="P14" s="85">
         <f t="shared" si="3"/>
-        <v>117417.09</v>
+        <v>126354.09</v>
       </c>
       <c r="Q14" s="86">
         <f t="shared" si="4"/>
-        <v>124462.09</v>
+        <v>133935.09</v>
       </c>
       <c r="R14" s="87">
         <f t="shared" si="5"/>
-        <v>120940.09</v>
+        <v>130145.09</v>
       </c>
       <c r="S14" s="46">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -4408,58 +4442,55 @@
         <v>77</v>
       </c>
       <c r="F15" s="69" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="G15" s="77">
         <v>0.42399999999999999</v>
       </c>
       <c r="H15" s="78">
-        <v>93577.1</v>
-      </c>
-      <c r="I15" s="169">
-        <f>48238.1+45339</f>
-        <v>93577.1</v>
-      </c>
+        <v>48238.1</v>
+      </c>
+      <c r="I15" s="169"/>
       <c r="J15" s="80"/>
       <c r="K15" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>48238.1</v>
       </c>
       <c r="L15" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1447.1429999999998</v>
       </c>
       <c r="M15" s="82">
         <v>0</v>
       </c>
       <c r="N15" s="83">
         <f t="shared" si="0"/>
-        <v>48237.765305599998</v>
+        <v>52477.765305599998</v>
       </c>
       <c r="O15" s="84">
         <v>0</v>
       </c>
       <c r="P15" s="85">
         <f t="shared" si="3"/>
-        <v>48238.1</v>
+        <v>102163.1</v>
       </c>
       <c r="Q15" s="86">
         <f t="shared" si="4"/>
-        <v>51132.1</v>
+        <v>108293.1</v>
       </c>
       <c r="R15" s="87">
         <f t="shared" si="5"/>
-        <v>49685.1</v>
+        <v>105228.1</v>
       </c>
       <c r="S15" s="46">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -4481,46 +4512,46 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H16" s="78">
-        <v>2546601.11</v>
+        <v>2885042.11</v>
       </c>
       <c r="I16" s="169"/>
       <c r="J16" s="80"/>
       <c r="K16" s="81">
         <f t="shared" si="1"/>
-        <v>2546601.11</v>
+        <v>2885042.11</v>
       </c>
       <c r="L16" s="81">
         <f t="shared" si="2"/>
-        <v>76398.033299999996</v>
+        <v>86551.263299999991</v>
       </c>
       <c r="M16" s="82">
         <v>0</v>
       </c>
       <c r="N16" s="83">
         <f t="shared" si="0"/>
-        <v>262042.55855752001</v>
+        <v>285075.55855751998</v>
       </c>
       <c r="O16" s="84">
         <v>0</v>
       </c>
       <c r="P16" s="85">
         <f t="shared" si="3"/>
-        <v>2885042.11</v>
+        <v>3256669.11</v>
       </c>
       <c r="Q16" s="86">
         <f t="shared" si="4"/>
-        <v>3058145.11</v>
+        <v>3452069.11</v>
       </c>
       <c r="R16" s="87">
         <f t="shared" si="5"/>
-        <v>2971593.11</v>
+        <v>3354369.11</v>
       </c>
       <c r="S16" s="46">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -4538,17 +4569,17 @@
         <v>123</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G17" s="77">
         <v>2.7492999999999999</v>
       </c>
       <c r="H17" s="78">
-        <v>312783.12</v>
+        <v>322166</v>
       </c>
       <c r="I17" s="169">
         <f>H17</f>
-        <v>312783.12</v>
+        <v>322166</v>
       </c>
       <c r="J17" s="80"/>
       <c r="K17" s="81">
@@ -4564,29 +4595,29 @@
       </c>
       <c r="N17" s="83">
         <f t="shared" si="0"/>
-        <v>312783.22677991999</v>
+        <v>340276.22677991999</v>
       </c>
       <c r="O17" s="84">
         <v>0</v>
       </c>
       <c r="P17" s="85">
         <f t="shared" si="3"/>
-        <v>312783.12</v>
+        <v>340276.12</v>
       </c>
       <c r="Q17" s="86">
         <f t="shared" si="4"/>
-        <v>331550.12</v>
+        <v>360693.12</v>
       </c>
       <c r="R17" s="87">
         <f t="shared" si="5"/>
-        <v>322166.12</v>
+        <v>350484.12</v>
       </c>
       <c r="S17" s="46">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -4630,29 +4661,29 @@
       </c>
       <c r="N18" s="83">
         <f t="shared" si="0"/>
-        <v>262042.55855752001</v>
+        <v>285075.55855751998</v>
       </c>
       <c r="O18" s="84">
         <v>0</v>
       </c>
       <c r="P18" s="85">
         <f t="shared" si="3"/>
-        <v>262043.13</v>
+        <v>285076.13</v>
       </c>
       <c r="Q18" s="86">
         <f t="shared" si="4"/>
-        <v>277766.13</v>
+        <v>302181.13</v>
       </c>
       <c r="R18" s="87">
         <f t="shared" si="5"/>
-        <v>269904.13</v>
+        <v>293628.13</v>
       </c>
       <c r="S18" s="46">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -4676,51 +4707,52 @@
         <v>2.6368</v>
       </c>
       <c r="H19" s="78">
-        <v>299984.14</v>
+        <v>567768.14</v>
       </c>
       <c r="I19" s="169">
-        <v>40000</v>
+        <f>40000+528000</f>
+        <v>568000</v>
       </c>
       <c r="J19" s="80"/>
       <c r="K19" s="81">
         <f t="shared" si="1"/>
-        <v>259984.14</v>
+        <v>-231.85999999998603</v>
       </c>
       <c r="L19" s="81">
         <f t="shared" si="2"/>
-        <v>7799.5241999999998</v>
+        <v>0</v>
       </c>
       <c r="M19" s="82">
         <v>0</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="0"/>
-        <v>299984.29140991997</v>
+        <v>326352.29140991997</v>
       </c>
       <c r="O19" s="84">
         <v>0</v>
       </c>
       <c r="P19" s="85">
         <f t="shared" si="3"/>
-        <v>567768.14</v>
+        <v>326120.14</v>
       </c>
       <c r="Q19" s="86">
         <f t="shared" si="4"/>
-        <v>601834.14</v>
+        <v>345687.14</v>
       </c>
       <c r="R19" s="87">
         <f t="shared" si="5"/>
-        <v>584801.14</v>
+        <v>335904.14</v>
       </c>
       <c r="S19" s="46">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -4742,11 +4774,11 @@
         <v>2.3536999999999999</v>
       </c>
       <c r="H20" s="78">
-        <v>268508.15000000002</v>
+        <v>267776.15000000002</v>
       </c>
       <c r="I20" s="169">
         <f>H20</f>
-        <v>268508.15000000002</v>
+        <v>267776.15000000002</v>
       </c>
       <c r="J20" s="80"/>
       <c r="K20" s="81">
@@ -4762,29 +4794,29 @@
       </c>
       <c r="N20" s="83">
         <f t="shared" si="0"/>
-        <v>267776.48160328</v>
+        <v>291313.48160328</v>
       </c>
       <c r="O20" s="84">
         <v>0</v>
       </c>
       <c r="P20" s="85">
         <f t="shared" si="3"/>
-        <v>267776.15000000002</v>
+        <v>291313.15000000002</v>
       </c>
       <c r="Q20" s="86">
         <f t="shared" si="4"/>
-        <v>283843.15000000002</v>
+        <v>308792.15000000002</v>
       </c>
       <c r="R20" s="87">
         <f t="shared" si="5"/>
-        <v>275809.15000000002</v>
+        <v>300052.15000000002</v>
       </c>
       <c r="S20" s="46">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -4802,7 +4834,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" s="77">
         <v>2.6476999999999999</v>
@@ -4828,22 +4860,22 @@
       </c>
       <c r="N21" s="83">
         <f t="shared" si="0"/>
-        <v>301224.36603688</v>
+        <v>327701.36603688</v>
       </c>
       <c r="O21" s="84">
         <v>0</v>
       </c>
       <c r="P21" s="85">
         <f t="shared" si="3"/>
-        <v>301224.15999999997</v>
+        <v>327701.15999999997</v>
       </c>
       <c r="Q21" s="86">
         <f t="shared" si="4"/>
-        <v>319298.15999999997</v>
+        <v>347363.16</v>
       </c>
       <c r="R21" s="87">
         <f t="shared" si="5"/>
-        <v>310261.15999999997</v>
+        <v>337532.15999999997</v>
       </c>
       <c r="S21" s="46">
         <f t="shared" si="7"/>
@@ -4851,7 +4883,7 @@
       </c>
       <c r="U21" s="45"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4869,7 +4901,7 @@
         <v>81</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G22" s="77">
         <v>2.3235000000000001</v>
@@ -4895,29 +4927,29 @@
       </c>
       <c r="N22" s="83">
         <f t="shared" si="0"/>
-        <v>264340.67850839999</v>
+        <v>287575.67850840004</v>
       </c>
       <c r="O22" s="84">
         <v>0</v>
       </c>
       <c r="P22" s="85">
         <f t="shared" si="3"/>
-        <v>264341.17</v>
+        <v>287576.17</v>
       </c>
       <c r="Q22" s="86">
         <f t="shared" si="4"/>
-        <v>280202.17</v>
+        <v>304831.17</v>
       </c>
       <c r="R22" s="87">
         <f t="shared" si="5"/>
-        <v>272271.17</v>
+        <v>296203.17</v>
       </c>
       <c r="S22" s="46">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4932,25 +4964,24 @@
         <v>18</v>
       </c>
       <c r="E23" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="F23" s="153" t="s">
         <v>182</v>
-      </c>
-      <c r="F23" s="153" t="s">
-        <v>183</v>
       </c>
       <c r="G23" s="77">
         <v>2.6880000000000002</v>
       </c>
       <c r="H23" s="78">
-        <v>296469.18</v>
+        <v>291809.18</v>
       </c>
       <c r="I23" s="169">
-        <f>150000+160469</f>
-        <v>310469</v>
+        <v>300500</v>
       </c>
       <c r="J23" s="80"/>
       <c r="K23" s="81">
         <f t="shared" si="1"/>
-        <v>-13999.820000000007</v>
+        <v>-8690.820000000007</v>
       </c>
       <c r="L23" s="81">
         <f t="shared" si="2"/>
@@ -4961,32 +4992,32 @@
       </c>
       <c r="N23" s="83">
         <f t="shared" si="0"/>
-        <v>305809.22910719999</v>
+        <v>332689.22910719999</v>
       </c>
       <c r="O23" s="84">
         <v>0</v>
       </c>
       <c r="P23" s="85">
         <f t="shared" si="3"/>
-        <v>291809.18</v>
+        <v>323998.18</v>
       </c>
       <c r="Q23" s="86">
         <f t="shared" si="4"/>
-        <v>309318.18</v>
+        <v>343438.18</v>
       </c>
       <c r="R23" s="87">
         <f t="shared" si="5"/>
-        <v>300563.18</v>
+        <v>333718.18</v>
       </c>
       <c r="S23" s="46">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="U23" s="164" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -5008,11 +5039,11 @@
         <v>2.36</v>
       </c>
       <c r="H24" s="78">
-        <v>168493.19</v>
+        <v>268493.19</v>
       </c>
       <c r="I24" s="169">
         <f>H24</f>
-        <v>168493.19</v>
+        <v>268493.19</v>
       </c>
       <c r="J24" s="80"/>
       <c r="K24" s="81">
@@ -5028,29 +5059,29 @@
       </c>
       <c r="N24" s="83">
         <f t="shared" si="0"/>
-        <v>268493.221984</v>
+        <v>292093.221984</v>
       </c>
       <c r="O24" s="84">
         <v>0</v>
       </c>
       <c r="P24" s="85">
         <f t="shared" si="3"/>
-        <v>268493.19</v>
+        <v>292093.19</v>
       </c>
       <c r="Q24" s="86">
         <f t="shared" si="4"/>
-        <v>284603.19</v>
+        <v>309619.19</v>
       </c>
       <c r="R24" s="87">
         <f t="shared" si="5"/>
-        <v>276548.19</v>
+        <v>300856.19</v>
       </c>
       <c r="S24" s="46">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -5072,15 +5103,15 @@
         <v>2.7183000000000002</v>
       </c>
       <c r="H25" s="78">
-        <v>318478.2</v>
+        <v>307735.2</v>
       </c>
       <c r="I25" s="169">
-        <v>320000</v>
+        <v>317000</v>
       </c>
       <c r="J25" s="80"/>
       <c r="K25" s="118">
         <f t="shared" si="1"/>
-        <v>-1521.7999999999884</v>
+        <v>-9264.7999999999884</v>
       </c>
       <c r="L25" s="81">
         <f t="shared" si="2"/>
@@ -5091,29 +5122,29 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="0"/>
-        <v>309256.40903352003</v>
+        <v>336439.40903352003</v>
       </c>
       <c r="O25" s="84">
         <v>0</v>
       </c>
       <c r="P25" s="85">
         <f t="shared" si="3"/>
-        <v>307735.2</v>
+        <v>327175.2</v>
       </c>
       <c r="Q25" s="86">
         <f t="shared" si="4"/>
-        <v>326199.2</v>
+        <v>346806.2</v>
       </c>
       <c r="R25" s="87">
         <f t="shared" si="5"/>
-        <v>316967.2</v>
+        <v>336990.2</v>
       </c>
       <c r="S25" s="46">
         <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -5135,11 +5166,11 @@
         <v>2.3033000000000001</v>
       </c>
       <c r="H26" s="78">
-        <v>255581.21</v>
+        <v>262043.21</v>
       </c>
       <c r="I26" s="169">
         <f>H26</f>
-        <v>255581.21</v>
+        <v>262043.21</v>
       </c>
       <c r="J26" s="80"/>
       <c r="K26" s="81">
@@ -5155,29 +5186,29 @@
       </c>
       <c r="N26" s="83">
         <f t="shared" si="0"/>
-        <v>262042.55855752001</v>
+        <v>285075.55855751998</v>
       </c>
       <c r="O26" s="84">
         <v>0</v>
       </c>
       <c r="P26" s="85">
         <f t="shared" si="3"/>
-        <v>262043.21</v>
+        <v>285076.21000000002</v>
       </c>
       <c r="Q26" s="86">
         <f t="shared" si="4"/>
-        <v>277766.21000000002</v>
+        <v>302181.21000000002</v>
       </c>
       <c r="R26" s="87">
         <f t="shared" si="5"/>
-        <v>269904.20999999996</v>
+        <v>293628.21000000002</v>
       </c>
       <c r="S26" s="46">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -5201,51 +5232,55 @@
         <v>2.6360000000000001</v>
       </c>
       <c r="H27" s="78">
-        <v>581768.22</v>
+        <v>772239.22</v>
       </c>
       <c r="I27" s="169">
-        <v>273665.21999999997</v>
+        <f>H27-454893</f>
+        <v>317346.21999999997</v>
       </c>
       <c r="J27" s="80"/>
       <c r="K27" s="81">
         <f t="shared" si="1"/>
-        <v>308103</v>
+        <v>454893</v>
       </c>
       <c r="L27" s="81">
         <f t="shared" si="2"/>
-        <v>9243.09</v>
+        <v>13646.789999999999</v>
       </c>
       <c r="M27" s="82">
         <v>0</v>
       </c>
       <c r="N27" s="83">
         <f t="shared" si="0"/>
-        <v>299893.27675840002</v>
-      </c>
-      <c r="O27" s="200">
-        <v>155000</v>
+        <v>326253.27675840002</v>
+      </c>
+      <c r="O27" s="207">
+        <v>65000</v>
       </c>
       <c r="P27" s="85">
         <f t="shared" si="3"/>
-        <v>772239.22</v>
+        <v>859793.22</v>
       </c>
       <c r="Q27" s="86">
         <f t="shared" si="4"/>
-        <v>818574.22</v>
+        <v>911381.22</v>
       </c>
       <c r="R27" s="87">
         <f t="shared" si="5"/>
-        <v>795406.22</v>
+        <v>885587.22</v>
       </c>
       <c r="S27" s="46">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
+      <c r="T27" s="69" t="s">
+        <v>203</v>
+      </c>
       <c r="U27" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -5287,29 +5322,29 @@
       </c>
       <c r="N28" s="83">
         <f t="shared" si="0"/>
-        <v>262042.55855752001</v>
+        <v>285075.55855751998</v>
       </c>
       <c r="O28" s="84">
         <v>0</v>
       </c>
       <c r="P28" s="85">
         <f t="shared" si="3"/>
-        <v>262043.23</v>
+        <v>285076.23</v>
       </c>
       <c r="Q28" s="86">
         <f t="shared" si="4"/>
-        <v>277766.23</v>
+        <v>302181.23</v>
       </c>
       <c r="R28" s="87">
         <f t="shared" si="5"/>
-        <v>269904.23</v>
+        <v>293628.23</v>
       </c>
       <c r="S28" s="46">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -5351,29 +5386,29 @@
       </c>
       <c r="N29" s="83">
         <f t="shared" si="0"/>
-        <v>297606.53363895998</v>
+        <v>323765.53363895998</v>
       </c>
       <c r="O29" s="84">
         <v>0</v>
       </c>
       <c r="P29" s="85">
         <f t="shared" si="3"/>
-        <v>297607.24</v>
+        <v>323766.24</v>
       </c>
       <c r="Q29" s="86">
         <f t="shared" si="4"/>
-        <v>315464.24</v>
+        <v>343192.24</v>
       </c>
       <c r="R29" s="87">
         <f t="shared" si="5"/>
-        <v>306535.24</v>
+        <v>333479.24</v>
       </c>
       <c r="S29" s="46">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -5415,29 +5450,29 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="0"/>
-        <v>267776.48160328</v>
+        <v>291313.48160328</v>
       </c>
       <c r="O30" s="84">
         <v>0</v>
       </c>
       <c r="P30" s="85">
         <f t="shared" si="3"/>
-        <v>267776.25</v>
+        <v>291313.25</v>
       </c>
       <c r="Q30" s="86">
         <f t="shared" si="4"/>
-        <v>283843.25</v>
+        <v>308792.25</v>
       </c>
       <c r="R30" s="87">
         <f t="shared" si="5"/>
-        <v>275809.25</v>
+        <v>300052.25</v>
       </c>
       <c r="S30" s="46">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -5481,29 +5516,29 @@
       </c>
       <c r="N31" s="83">
         <f t="shared" si="0"/>
-        <v>301133.35138536</v>
+        <v>327602.35138536</v>
       </c>
       <c r="O31" s="84">
         <v>0</v>
       </c>
       <c r="P31" s="85">
         <f t="shared" si="3"/>
-        <v>301133.26</v>
+        <v>327602.26</v>
       </c>
       <c r="Q31" s="86">
         <f t="shared" si="4"/>
-        <v>319201.26</v>
+        <v>347258.26</v>
       </c>
       <c r="R31" s="87">
         <f t="shared" si="5"/>
-        <v>310167.26</v>
+        <v>337430.26</v>
       </c>
       <c r="S31" s="46">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -5545,29 +5580,29 @@
       </c>
       <c r="N32" s="83">
         <f t="shared" si="0"/>
-        <v>267776.48160328</v>
+        <v>291313.48160328</v>
       </c>
       <c r="O32" s="84">
         <v>0</v>
       </c>
       <c r="P32" s="85">
         <f t="shared" si="3"/>
-        <v>267776.27</v>
+        <v>291313.27</v>
       </c>
       <c r="Q32" s="86">
         <f t="shared" si="4"/>
-        <v>283843.27</v>
+        <v>308792.27</v>
       </c>
       <c r="R32" s="87">
         <f t="shared" si="5"/>
-        <v>275809.27</v>
+        <v>300052.27</v>
       </c>
       <c r="S32" s="46">
         <f t="shared" si="7"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -5589,11 +5624,11 @@
         <v>2.6663000000000001</v>
       </c>
       <c r="H33" s="78">
-        <v>295310.28000000003</v>
+        <v>303340.28000000003</v>
       </c>
       <c r="I33" s="169">
         <f>H33</f>
-        <v>295310.28000000003</v>
+        <v>303340.28000000003</v>
       </c>
       <c r="J33" s="80"/>
       <c r="K33" s="81">
@@ -5609,29 +5644,29 @@
       </c>
       <c r="N33" s="83">
         <f t="shared" si="0"/>
-        <v>303340.45668472</v>
+        <v>330003.45668472</v>
       </c>
       <c r="O33" s="138">
         <v>0</v>
       </c>
       <c r="P33" s="85">
         <f t="shared" si="3"/>
-        <v>303340.28000000003</v>
+        <v>330003.28000000003</v>
       </c>
       <c r="Q33" s="86">
         <f t="shared" si="4"/>
-        <v>321541.28000000003</v>
+        <v>349803.28</v>
       </c>
       <c r="R33" s="87">
         <f t="shared" si="5"/>
-        <v>312440.28000000003</v>
+        <v>339903.28</v>
       </c>
       <c r="S33" s="46">
         <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>27</v>
       </c>
@@ -5655,11 +5690,11 @@
         <v>2.4476</v>
       </c>
       <c r="H34" s="78">
-        <v>286813.28999999998</v>
+        <v>278459.28999999998</v>
       </c>
       <c r="I34" s="169">
         <f>H34</f>
-        <v>286813.28999999998</v>
+        <v>278459.28999999998</v>
       </c>
       <c r="J34" s="80"/>
       <c r="K34" s="81">
@@ -5675,29 +5710,29 @@
       </c>
       <c r="N34" s="83">
         <f t="shared" si="0"/>
-        <v>278459.32632544002</v>
+        <v>302935.32632544002</v>
       </c>
       <c r="O34" s="84">
         <v>0</v>
       </c>
       <c r="P34" s="85">
         <f t="shared" si="3"/>
-        <v>278459.28999999998</v>
+        <v>302935.28999999998</v>
       </c>
       <c r="Q34" s="86">
         <f t="shared" si="4"/>
-        <v>295167.28999999998</v>
+        <v>321111.28999999998</v>
       </c>
       <c r="R34" s="87">
         <f t="shared" si="5"/>
-        <v>286813.28999999998</v>
+        <v>312023.28999999998</v>
       </c>
       <c r="S34" s="46">
         <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>27</v>
       </c>
@@ -5719,48 +5754,46 @@
         <v>2.7183000000000002</v>
       </c>
       <c r="H35" s="78">
-        <v>291204.3</v>
-      </c>
-      <c r="I35" s="169">
-        <v>299940</v>
-      </c>
+        <v>300521.3</v>
+      </c>
+      <c r="I35" s="169"/>
       <c r="J35" s="80"/>
       <c r="K35" s="81">
         <f t="shared" si="1"/>
-        <v>-8735.7000000000116</v>
+        <v>300521.3</v>
       </c>
       <c r="L35" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9015.6389999999992</v>
       </c>
       <c r="M35" s="82">
         <v>0</v>
       </c>
       <c r="N35" s="83">
         <f t="shared" si="0"/>
-        <v>309256.40903352003</v>
+        <v>336439.40903352003</v>
       </c>
       <c r="O35" s="84">
         <v>0</v>
       </c>
       <c r="P35" s="85">
         <f t="shared" si="3"/>
-        <v>300521.3</v>
+        <v>645976.30000000005</v>
       </c>
       <c r="Q35" s="86">
         <f t="shared" si="4"/>
-        <v>318553.3</v>
+        <v>684735.3</v>
       </c>
       <c r="R35" s="87">
         <f t="shared" si="5"/>
-        <v>309537.3</v>
+        <v>665355.30000000005</v>
       </c>
       <c r="S35" s="46">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>27</v>
       </c>
@@ -5784,48 +5817,49 @@
         <v>2.3026</v>
       </c>
       <c r="H36" s="79">
-        <v>261963.31</v>
+        <v>293522.31</v>
       </c>
       <c r="I36" s="169">
-        <v>231323.31</v>
+        <f>H36</f>
+        <v>293522.31</v>
       </c>
       <c r="J36" s="88"/>
       <c r="K36" s="81">
         <f t="shared" si="1"/>
-        <v>30640</v>
+        <v>0</v>
       </c>
       <c r="L36" s="81">
         <f t="shared" si="2"/>
-        <v>919.19999999999993</v>
+        <v>0</v>
       </c>
       <c r="M36" s="82">
         <v>0</v>
       </c>
       <c r="N36" s="151">
         <f t="shared" si="0"/>
-        <v>261962.92073744</v>
+        <v>284988.92073744</v>
       </c>
       <c r="O36" s="89">
         <v>0</v>
       </c>
       <c r="P36" s="85">
         <f t="shared" si="3"/>
-        <v>293522.31</v>
+        <v>284989.31</v>
       </c>
       <c r="Q36" s="86">
         <f t="shared" si="4"/>
-        <v>311134.31</v>
+        <v>302089.31</v>
       </c>
       <c r="R36" s="87">
         <f t="shared" si="5"/>
-        <v>302328.31</v>
+        <v>293539.31</v>
       </c>
       <c r="S36" s="46">
         <f t="shared" si="7"/>
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>27</v>
       </c>
@@ -5847,7 +5881,7 @@
         <v>2.6562000000000001</v>
       </c>
       <c r="H37" s="78">
-        <v>418649.32</v>
+        <v>422143.32</v>
       </c>
       <c r="I37" s="169">
         <v>302191.32</v>
@@ -5855,40 +5889,40 @@
       <c r="J37" s="80"/>
       <c r="K37" s="81">
         <f t="shared" si="1"/>
-        <v>116458</v>
+        <v>119952</v>
       </c>
       <c r="L37" s="81">
         <f t="shared" si="2"/>
-        <v>3493.74</v>
+        <v>3598.56</v>
       </c>
       <c r="M37" s="82">
         <v>0</v>
       </c>
       <c r="N37" s="83">
         <f t="shared" si="0"/>
-        <v>302191.39670928003</v>
+        <v>328753.39670928003</v>
       </c>
       <c r="O37" s="84">
         <v>0</v>
       </c>
       <c r="P37" s="85">
         <f t="shared" si="3"/>
-        <v>422143.32</v>
+        <v>452304.32</v>
       </c>
       <c r="Q37" s="86">
         <f t="shared" si="4"/>
-        <v>447472.32</v>
+        <v>479443.32</v>
       </c>
       <c r="R37" s="87">
         <f t="shared" si="5"/>
-        <v>434807.32</v>
+        <v>465873.32</v>
       </c>
       <c r="S37" s="46">
         <f t="shared" si="7"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>27</v>
       </c>
@@ -5913,7 +5947,7 @@
         <v>265569.33</v>
       </c>
       <c r="I38" s="169">
-        <f>H38</f>
+        <f t="shared" ref="I38:I43" si="9">H38</f>
         <v>265569.33</v>
       </c>
       <c r="J38" s="80"/>
@@ -5930,29 +5964,29 @@
       </c>
       <c r="N38" s="83">
         <f t="shared" si="0"/>
-        <v>265569.37630392</v>
+        <v>288912.37630392</v>
       </c>
       <c r="O38" s="84">
         <v>0</v>
       </c>
       <c r="P38" s="85">
         <f t="shared" si="3"/>
-        <v>265569.33</v>
+        <v>288912.33</v>
       </c>
       <c r="Q38" s="86">
         <f t="shared" si="4"/>
-        <v>281503.33</v>
+        <v>306247.33</v>
       </c>
       <c r="R38" s="87">
         <f t="shared" si="5"/>
-        <v>273536.33</v>
+        <v>297579.33</v>
       </c>
       <c r="S38" s="46">
         <f t="shared" si="7"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>27</v>
       </c>
@@ -5977,7 +6011,7 @@
         <v>298744.34000000003</v>
       </c>
       <c r="I39" s="169">
-        <f>H39</f>
+        <f t="shared" si="9"/>
         <v>298744.34000000003</v>
       </c>
       <c r="J39" s="80"/>
@@ -5994,29 +6028,29 @@
       </c>
       <c r="N39" s="83">
         <f t="shared" si="0"/>
-        <v>298744.21678295999</v>
+        <v>325003.21678295999</v>
       </c>
       <c r="O39" s="84">
         <v>0</v>
       </c>
       <c r="P39" s="85">
         <f t="shared" si="3"/>
-        <v>298744.34000000003</v>
+        <v>325003.34000000003</v>
       </c>
       <c r="Q39" s="86">
         <f t="shared" si="4"/>
-        <v>316669.34000000003</v>
+        <v>344504.34</v>
       </c>
       <c r="R39" s="87">
         <f t="shared" si="5"/>
-        <v>307706.34000000003</v>
+        <v>334753.34000000003</v>
       </c>
       <c r="S39" s="46">
         <f t="shared" si="7"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>27</v>
       </c>
@@ -6040,48 +6074,49 @@
         <v>1.0069999999999999</v>
       </c>
       <c r="H40" s="78">
-        <v>121329.35</v>
+        <v>118205.35</v>
       </c>
       <c r="I40" s="169">
-        <v>117795.35</v>
+        <f t="shared" si="9"/>
+        <v>118205.35</v>
       </c>
       <c r="J40" s="80"/>
       <c r="K40" s="81">
         <f t="shared" si="1"/>
-        <v>3534</v>
+        <v>0</v>
       </c>
       <c r="L40" s="81">
         <f t="shared" si="2"/>
-        <v>106.02</v>
+        <v>0</v>
       </c>
       <c r="M40" s="82">
         <v>0</v>
       </c>
       <c r="N40" s="83">
         <f t="shared" si="0"/>
-        <v>114564.69260079999</v>
+        <v>124634.69260079999</v>
       </c>
       <c r="O40" s="84">
         <v>0</v>
       </c>
       <c r="P40" s="85">
         <f t="shared" si="3"/>
-        <v>118205.35</v>
+        <v>124635.35</v>
       </c>
       <c r="Q40" s="86">
         <f t="shared" si="4"/>
-        <v>125298.35</v>
+        <v>132113.35</v>
       </c>
       <c r="R40" s="87">
         <f t="shared" si="5"/>
-        <v>121751.35</v>
+        <v>128374.35</v>
       </c>
       <c r="S40" s="46">
         <f t="shared" si="7"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
@@ -6099,7 +6134,7 @@
         <v>94</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G41" s="77">
         <v>0.78120000000000001</v>
@@ -6108,7 +6143,7 @@
         <v>88876.36</v>
       </c>
       <c r="I41" s="169">
-        <f>H41</f>
+        <f t="shared" si="9"/>
         <v>88876.36</v>
       </c>
       <c r="J41" s="80"/>
@@ -6125,32 +6160,32 @@
       </c>
       <c r="N41" s="83">
         <f t="shared" si="0"/>
-        <v>88875.807209279999</v>
+        <v>96687.807209279999</v>
       </c>
       <c r="O41" s="84">
         <v>0</v>
       </c>
       <c r="P41" s="85">
         <f t="shared" si="3"/>
-        <v>88876.36</v>
+        <v>96688.36</v>
       </c>
       <c r="Q41" s="86">
         <f t="shared" si="4"/>
-        <v>94209.36</v>
+        <v>102490.36</v>
       </c>
       <c r="R41" s="87">
         <f t="shared" si="5"/>
-        <v>91542.36</v>
+        <v>99589.36</v>
       </c>
       <c r="S41" s="46">
         <f t="shared" si="7"/>
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55"/>
       <c r="B42" s="67">
         <v>1</v>
@@ -6166,7 +6201,7 @@
         <v>94</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G42" s="91">
         <v>1.2153</v>
@@ -6175,7 +6210,7 @@
         <v>138263.37</v>
       </c>
       <c r="I42" s="169">
-        <f>H42</f>
+        <f t="shared" si="9"/>
         <v>138263.37</v>
       </c>
       <c r="J42" s="80"/>
@@ -6192,32 +6227,32 @@
       </c>
       <c r="N42" s="83">
         <f t="shared" si="0"/>
-        <v>138262.63249032001</v>
+        <v>150415.63249032001</v>
       </c>
       <c r="O42" s="84">
         <v>0</v>
       </c>
       <c r="P42" s="85">
         <f t="shared" si="3"/>
-        <v>138263.37</v>
+        <v>150416.37</v>
       </c>
       <c r="Q42" s="86">
         <f t="shared" si="4"/>
-        <v>146559.37</v>
+        <v>159441.37</v>
       </c>
       <c r="R42" s="87">
         <f t="shared" si="5"/>
-        <v>142411.37</v>
+        <v>154928.37</v>
       </c>
       <c r="S42" s="46">
         <f t="shared" si="7"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="68">
         <v>2</v>
       </c>
@@ -6238,11 +6273,11 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H43" s="78">
-        <v>111896.38</v>
+        <v>111896</v>
       </c>
       <c r="I43" s="169">
-        <f>H43</f>
-        <v>111896.38</v>
+        <f t="shared" si="9"/>
+        <v>111896</v>
       </c>
       <c r="J43" s="80"/>
       <c r="K43" s="81">
@@ -6258,29 +6293,29 @@
       </c>
       <c r="N43" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O43" s="84">
         <v>0</v>
       </c>
       <c r="P43" s="85">
         <f t="shared" si="3"/>
-        <v>108637.38</v>
+        <v>118186.38</v>
       </c>
       <c r="Q43" s="86">
         <f t="shared" si="4"/>
-        <v>115156.38</v>
+        <v>125278.38</v>
       </c>
       <c r="R43" s="87">
         <f t="shared" si="5"/>
-        <v>111896.38</v>
+        <v>121732.38</v>
       </c>
       <c r="S43" s="46">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="68">
         <v>2</v>
       </c>
@@ -6299,46 +6334,46 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H44" s="78">
-        <v>333756.39</v>
+        <v>429687.39</v>
       </c>
       <c r="I44" s="169"/>
       <c r="J44" s="80"/>
       <c r="K44" s="81">
         <f t="shared" si="1"/>
-        <v>333756.39</v>
+        <v>429687.39</v>
       </c>
       <c r="L44" s="81">
         <f t="shared" si="2"/>
-        <v>10012.691699999999</v>
+        <v>12890.6217</v>
       </c>
       <c r="M44" s="82">
         <v>0</v>
       </c>
       <c r="N44" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O44" s="84">
         <v>0</v>
       </c>
       <c r="P44" s="85">
         <f t="shared" si="3"/>
-        <v>429687.39</v>
+        <v>536048.39</v>
       </c>
       <c r="Q44" s="86">
         <f t="shared" si="4"/>
-        <v>455469.39</v>
+        <v>568211.39</v>
       </c>
       <c r="R44" s="87">
         <f t="shared" si="5"/>
-        <v>442578.39</v>
+        <v>552129.39</v>
       </c>
       <c r="S44" s="46">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="68">
         <v>2</v>
       </c>
@@ -6359,49 +6394,48 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H45" s="78">
-        <v>143962.4</v>
+        <v>131346.4</v>
       </c>
       <c r="I45" s="169">
-        <f>12616+131346</f>
-        <v>143962</v>
+        <v>135296.4</v>
       </c>
       <c r="J45" s="80"/>
       <c r="K45" s="81">
         <f t="shared" si="1"/>
-        <v>0.39999999999417923</v>
+        <v>-3950</v>
       </c>
       <c r="L45" s="81">
         <f t="shared" si="2"/>
-        <v>1.1999999999825376E-2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="82">
         <v>0</v>
       </c>
       <c r="N45" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O45" s="84">
         <v>0</v>
       </c>
       <c r="P45" s="85">
         <f t="shared" si="3"/>
-        <v>131346.4</v>
+        <v>138941.4</v>
       </c>
       <c r="Q45" s="86">
         <f t="shared" si="4"/>
-        <v>139227.4</v>
+        <v>147278.39999999999</v>
       </c>
       <c r="R45" s="87">
         <f t="shared" si="5"/>
-        <v>135286.39999999999</v>
+        <v>143109.4</v>
       </c>
       <c r="S45" s="46">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="68">
         <v>3</v>
       </c>
@@ -6422,7 +6456,7 @@
         <v>0.95489999999999997</v>
       </c>
       <c r="H46" s="78">
-        <v>111896.41</v>
+        <v>108637.41</v>
       </c>
       <c r="I46" s="169">
         <v>111896.41</v>
@@ -6430,7 +6464,7 @@
       <c r="J46" s="80"/>
       <c r="K46" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3259</v>
       </c>
       <c r="L46" s="81">
         <f t="shared" si="2"/>
@@ -6441,29 +6475,29 @@
       </c>
       <c r="N46" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O46" s="84">
         <v>0</v>
       </c>
       <c r="P46" s="85">
         <f t="shared" si="3"/>
-        <v>108637.41</v>
+        <v>114927.41</v>
       </c>
       <c r="Q46" s="86">
         <f t="shared" si="4"/>
-        <v>115156.41</v>
+        <v>121823.41</v>
       </c>
       <c r="R46" s="87">
         <f t="shared" si="5"/>
-        <v>111896.41</v>
+        <v>118375.41</v>
       </c>
       <c r="S46" s="46">
         <f t="shared" si="7"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="68">
         <v>3</v>
       </c>
@@ -6485,7 +6519,7 @@
         <v>85918.42</v>
       </c>
       <c r="I47" s="169">
-        <f t="shared" ref="I47" si="9">H47</f>
+        <f t="shared" ref="I47" si="10">H47</f>
         <v>85918.42</v>
       </c>
       <c r="J47" s="80"/>
@@ -6502,29 +6536,29 @@
       </c>
       <c r="N47" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O47" s="84">
         <v>0</v>
       </c>
       <c r="P47" s="85">
         <f t="shared" si="3"/>
-        <v>85918.42</v>
+        <v>93470.42</v>
       </c>
       <c r="Q47" s="86">
         <f t="shared" si="4"/>
-        <v>91074.42</v>
+        <v>99079.42</v>
       </c>
       <c r="R47" s="87">
         <f t="shared" si="5"/>
-        <v>88496.42</v>
+        <v>96274.42</v>
       </c>
       <c r="S47" s="46">
         <f t="shared" si="7"/>
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="68">
         <v>3</v>
       </c>
@@ -6546,7 +6580,7 @@
         <v>131346.43</v>
       </c>
       <c r="I48" s="169">
-        <f t="shared" ref="I48:I53" si="10">H48</f>
+        <f t="shared" ref="I48:I53" si="11">H48</f>
         <v>131346.43</v>
       </c>
       <c r="J48" s="80"/>
@@ -6563,29 +6597,29 @@
       </c>
       <c r="N48" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O48" s="84">
         <v>0</v>
       </c>
       <c r="P48" s="85">
         <f t="shared" si="3"/>
-        <v>131346.43</v>
+        <v>142891.43</v>
       </c>
       <c r="Q48" s="86">
         <f t="shared" si="4"/>
-        <v>139227.43</v>
+        <v>151465.43</v>
       </c>
       <c r="R48" s="87">
         <f t="shared" si="5"/>
-        <v>135286.43</v>
+        <v>147178.43</v>
       </c>
       <c r="S48" s="46">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="68">
         <v>4</v>
       </c>
@@ -6609,7 +6643,7 @@
         <v>108637.44</v>
       </c>
       <c r="I49" s="169">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108637.44</v>
       </c>
       <c r="J49" s="80"/>
@@ -6626,29 +6660,29 @@
       </c>
       <c r="N49" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O49" s="84">
         <v>0</v>
       </c>
       <c r="P49" s="85">
         <f t="shared" si="3"/>
-        <v>108637.44</v>
+        <v>118186.44</v>
       </c>
       <c r="Q49" s="86">
         <f t="shared" si="4"/>
-        <v>115156.44</v>
+        <v>125278.44</v>
       </c>
       <c r="R49" s="87">
         <f t="shared" si="5"/>
-        <v>111896.44</v>
+        <v>121732.44</v>
       </c>
       <c r="S49" s="46">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="68">
         <v>4</v>
       </c>
@@ -6660,7 +6694,7 @@
         <v>45</v>
       </c>
       <c r="E50" s="67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F50" s="67"/>
       <c r="G50" s="91">
@@ -6670,13 +6704,12 @@
         <v>85918.45</v>
       </c>
       <c r="I50" s="169">
-        <f t="shared" si="10"/>
-        <v>85918.45</v>
+        <v>85920</v>
       </c>
       <c r="J50" s="80"/>
       <c r="K50" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.5500000000029104</v>
       </c>
       <c r="L50" s="81">
         <f t="shared" si="2"/>
@@ -6687,32 +6720,32 @@
       </c>
       <c r="N50" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O50" s="84">
         <v>0</v>
       </c>
       <c r="P50" s="85">
         <f t="shared" si="3"/>
-        <v>85918.45</v>
+        <v>93468.45</v>
       </c>
       <c r="Q50" s="86">
         <f t="shared" si="4"/>
-        <v>91074.45</v>
+        <v>99077.45</v>
       </c>
       <c r="R50" s="87">
         <f t="shared" si="5"/>
-        <v>88496.45</v>
+        <v>96272.45</v>
       </c>
       <c r="S50" s="46">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="68">
         <v>4</v>
       </c>
@@ -6733,11 +6766,11 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H51" s="78">
-        <v>250728.46</v>
+        <v>131346.46</v>
       </c>
       <c r="I51" s="169">
-        <f t="shared" si="10"/>
-        <v>250728.46</v>
+        <f t="shared" si="11"/>
+        <v>131346.46</v>
       </c>
       <c r="J51" s="80"/>
       <c r="K51" s="81">
@@ -6753,29 +6786,29 @@
       </c>
       <c r="N51" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O51" s="84">
         <v>0</v>
       </c>
       <c r="P51" s="85">
         <f t="shared" si="3"/>
-        <v>131346.46</v>
+        <v>142891.46</v>
       </c>
       <c r="Q51" s="86">
         <f t="shared" si="4"/>
-        <v>139227.46</v>
+        <v>151465.46</v>
       </c>
       <c r="R51" s="87">
         <f t="shared" si="5"/>
-        <v>135286.46</v>
+        <v>147178.46</v>
       </c>
       <c r="S51" s="46">
         <f t="shared" si="7"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="68">
         <v>5</v>
       </c>
@@ -6790,7 +6823,7 @@
         <v>147</v>
       </c>
       <c r="F52" s="90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G52" s="91">
         <v>0.95489999999999997</v>
@@ -6799,7 +6832,7 @@
         <v>108637.47</v>
       </c>
       <c r="I52" s="169">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108637.47</v>
       </c>
       <c r="J52" s="80"/>
@@ -6816,29 +6849,29 @@
       </c>
       <c r="N52" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O52" s="84">
         <v>0</v>
       </c>
       <c r="P52" s="85">
         <f t="shared" si="3"/>
-        <v>108637.47</v>
+        <v>118186.47</v>
       </c>
       <c r="Q52" s="86">
         <f t="shared" si="4"/>
-        <v>115156.47</v>
+        <v>125278.47</v>
       </c>
       <c r="R52" s="87">
         <f t="shared" si="5"/>
-        <v>111896.47</v>
+        <v>121732.47</v>
       </c>
       <c r="S52" s="46">
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="68">
         <v>5</v>
       </c>
@@ -6853,7 +6886,7 @@
         <v>123</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G53" s="91">
         <v>0.75519999999999998</v>
@@ -6862,7 +6895,7 @@
         <v>85918.48</v>
       </c>
       <c r="I53" s="169">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>85918.48</v>
       </c>
       <c r="J53" s="80"/>
@@ -6879,29 +6912,29 @@
       </c>
       <c r="N53" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O53" s="84">
         <v>0</v>
       </c>
       <c r="P53" s="85">
         <f t="shared" si="3"/>
-        <v>85918.48</v>
+        <v>93470.48</v>
       </c>
       <c r="Q53" s="86">
         <f t="shared" si="4"/>
-        <v>91074.48</v>
+        <v>99079.48</v>
       </c>
       <c r="R53" s="87">
         <f t="shared" si="5"/>
-        <v>88496.48</v>
+        <v>96274.48</v>
       </c>
       <c r="S53" s="46">
         <f t="shared" si="7"/>
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="68">
         <v>5</v>
       </c>
@@ -6922,48 +6955,49 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H54" s="78">
-        <v>135286.49</v>
+        <v>135404.49</v>
       </c>
       <c r="I54" s="169">
-        <v>131346.49</v>
+        <f t="shared" ref="I54:I59" si="12">H54</f>
+        <v>135404.49</v>
       </c>
       <c r="J54" s="80"/>
       <c r="K54" s="81">
         <f t="shared" si="1"/>
-        <v>3940</v>
+        <v>0</v>
       </c>
       <c r="L54" s="81">
         <f t="shared" si="2"/>
-        <v>118.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="M54" s="82">
         <v>0</v>
       </c>
       <c r="N54" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O54" s="84">
         <v>0</v>
       </c>
       <c r="P54" s="85">
         <f t="shared" si="3"/>
-        <v>135404.49</v>
+        <v>142891.49</v>
       </c>
       <c r="Q54" s="86">
         <f t="shared" si="4"/>
-        <v>143529.49</v>
+        <v>151465.49</v>
       </c>
       <c r="R54" s="87">
         <f t="shared" si="5"/>
-        <v>139466.49</v>
+        <v>147178.49</v>
       </c>
       <c r="S54" s="46">
         <f t="shared" si="7"/>
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="68">
         <v>6</v>
       </c>
@@ -6985,7 +7019,7 @@
         <v>108637.5</v>
       </c>
       <c r="I55" s="169">
-        <f>H55</f>
+        <f t="shared" si="12"/>
         <v>108637.5</v>
       </c>
       <c r="J55" s="80"/>
@@ -7002,29 +7036,29 @@
       </c>
       <c r="N55" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O55" s="84">
         <v>0</v>
       </c>
       <c r="P55" s="85">
         <f t="shared" si="3"/>
-        <v>108637.5</v>
+        <v>118186.5</v>
       </c>
       <c r="Q55" s="86">
         <f t="shared" si="4"/>
-        <v>115156.5</v>
+        <v>125278.5</v>
       </c>
       <c r="R55" s="87">
         <f t="shared" si="5"/>
-        <v>111896.5</v>
+        <v>121732.5</v>
       </c>
       <c r="S55" s="46">
         <f t="shared" si="7"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="68">
         <v>6</v>
       </c>
@@ -7043,52 +7077,52 @@
         <v>0.75519999999999998</v>
       </c>
       <c r="H56" s="78">
-        <v>171638.51</v>
+        <v>88469.51</v>
       </c>
       <c r="I56" s="169">
-        <f>85918+83244</f>
-        <v>169162</v>
+        <f t="shared" si="12"/>
+        <v>88469.51</v>
       </c>
       <c r="J56" s="80"/>
       <c r="K56" s="81">
         <f t="shared" si="1"/>
-        <v>2476.5100000000093</v>
+        <v>0</v>
       </c>
       <c r="L56" s="81">
         <f t="shared" si="2"/>
-        <v>74.295300000000282</v>
+        <v>0</v>
       </c>
       <c r="M56" s="82">
         <v>0</v>
       </c>
       <c r="N56" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O56" s="84">
         <v>0</v>
       </c>
       <c r="P56" s="85">
         <f t="shared" si="3"/>
-        <v>88469.51</v>
+        <v>93470.51</v>
       </c>
       <c r="Q56" s="86">
         <f t="shared" si="4"/>
-        <v>93778.51</v>
+        <v>99079.51</v>
       </c>
       <c r="R56" s="87">
         <f t="shared" si="5"/>
-        <v>91123.51</v>
+        <v>96274.51</v>
       </c>
       <c r="S56" s="46">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="68">
         <v>6</v>
       </c>
@@ -7107,48 +7141,49 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H57" s="78">
-        <v>260331.51999999999</v>
+        <v>270502.52</v>
       </c>
       <c r="I57" s="169">
-        <v>125228.52</v>
+        <f t="shared" si="12"/>
+        <v>270502.52</v>
       </c>
       <c r="J57" s="80"/>
       <c r="K57" s="81">
         <f t="shared" si="1"/>
-        <v>135103</v>
+        <v>0</v>
       </c>
       <c r="L57" s="81">
         <f t="shared" si="2"/>
-        <v>4053.0899999999997</v>
+        <v>0</v>
       </c>
       <c r="M57" s="82">
         <v>0</v>
       </c>
       <c r="N57" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O57" s="84">
         <v>0</v>
       </c>
       <c r="P57" s="85">
         <f t="shared" si="3"/>
-        <v>270502.52</v>
+        <v>142891.51999999999</v>
       </c>
       <c r="Q57" s="86">
         <f t="shared" si="4"/>
-        <v>286733.52</v>
+        <v>151465.51999999999</v>
       </c>
       <c r="R57" s="87">
         <f t="shared" si="5"/>
-        <v>278617.52</v>
+        <v>147178.51999999999</v>
       </c>
       <c r="S57" s="46">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="68">
         <v>7</v>
       </c>
@@ -7170,7 +7205,7 @@
         <v>108637.53</v>
       </c>
       <c r="I58" s="169">
-        <f>H58</f>
+        <f t="shared" si="12"/>
         <v>108637.53</v>
       </c>
       <c r="J58" s="80"/>
@@ -7187,29 +7222,29 @@
       </c>
       <c r="N58" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O58" s="84">
         <v>0</v>
       </c>
       <c r="P58" s="85">
         <f t="shared" si="3"/>
-        <v>108637.53</v>
+        <v>118186.53</v>
       </c>
       <c r="Q58" s="86">
         <f t="shared" si="4"/>
-        <v>115156.53</v>
+        <v>125278.53</v>
       </c>
       <c r="R58" s="87">
         <f t="shared" si="5"/>
-        <v>111896.53</v>
+        <v>121732.53</v>
       </c>
       <c r="S58" s="46">
         <f t="shared" si="7"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="68">
         <v>7</v>
       </c>
@@ -7231,7 +7266,7 @@
         <v>85918.54</v>
       </c>
       <c r="I59" s="169">
-        <f>H59</f>
+        <f t="shared" si="12"/>
         <v>85918.54</v>
       </c>
       <c r="J59" s="80"/>
@@ -7248,29 +7283,29 @@
       </c>
       <c r="N59" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O59" s="84">
         <v>0</v>
       </c>
       <c r="P59" s="85">
         <f t="shared" si="3"/>
-        <v>85918.54</v>
+        <v>93470.54</v>
       </c>
       <c r="Q59" s="86">
         <f t="shared" si="4"/>
-        <v>91074.54</v>
+        <v>99079.54</v>
       </c>
       <c r="R59" s="87">
         <f t="shared" si="5"/>
-        <v>88496.54</v>
+        <v>96274.54</v>
       </c>
       <c r="S59" s="46">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="68">
         <v>7</v>
       </c>
@@ -7284,14 +7319,14 @@
       <c r="E60" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="F60" s="90" t="s">
-        <v>151</v>
+      <c r="F60" s="67" t="s">
+        <v>248</v>
       </c>
       <c r="G60" s="91">
         <v>1.1545000000000001</v>
       </c>
       <c r="H60" s="78">
-        <v>511521.55</v>
+        <v>534759.55000000005</v>
       </c>
       <c r="I60" s="169">
         <v>119858</v>
@@ -7299,40 +7334,40 @@
       <c r="J60" s="80"/>
       <c r="K60" s="81">
         <f t="shared" si="1"/>
-        <v>391663.55</v>
+        <v>414901.55000000005</v>
       </c>
       <c r="L60" s="81">
         <f t="shared" si="2"/>
-        <v>11749.906499999999</v>
+        <v>12447.0465</v>
       </c>
       <c r="M60" s="82">
         <v>0</v>
       </c>
       <c r="N60" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O60" s="84">
         <v>0</v>
       </c>
       <c r="P60" s="85">
         <f t="shared" si="3"/>
-        <v>534759.55000000005</v>
+        <v>570239.55000000005</v>
       </c>
       <c r="Q60" s="86">
         <f t="shared" si="4"/>
-        <v>566845.55000000005</v>
+        <v>604454.55000000005</v>
       </c>
       <c r="R60" s="87">
         <f t="shared" si="5"/>
-        <v>550802.55000000005</v>
+        <v>587346.55000000005</v>
       </c>
       <c r="S60" s="46">
         <f t="shared" si="7"/>
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="68">
         <v>8</v>
       </c>
@@ -7344,20 +7379,20 @@
         <v>56</v>
       </c>
       <c r="E61" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="F61" s="90" t="s">
         <v>152</v>
-      </c>
-      <c r="F61" s="90" t="s">
-        <v>153</v>
       </c>
       <c r="G61" s="91">
         <v>0.95489999999999997</v>
       </c>
       <c r="H61" s="78">
-        <v>98801.56</v>
+        <v>108637.56</v>
       </c>
       <c r="I61" s="169">
         <f>H61</f>
-        <v>98801.56</v>
+        <v>108637.56</v>
       </c>
       <c r="J61" s="80"/>
       <c r="K61" s="81">
@@ -7373,27 +7408,27 @@
       </c>
       <c r="N61" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O61" s="84"/>
       <c r="P61" s="85">
         <f t="shared" si="3"/>
-        <v>108637.56</v>
+        <v>118186.56</v>
       </c>
       <c r="Q61" s="86">
         <f t="shared" si="4"/>
-        <v>115156.56</v>
+        <v>125278.56</v>
       </c>
       <c r="R61" s="87">
         <f t="shared" si="5"/>
-        <v>111896.56</v>
+        <v>121732.56</v>
       </c>
       <c r="S61" s="46">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="68">
         <v>8</v>
       </c>
@@ -7405,10 +7440,10 @@
         <v>57</v>
       </c>
       <c r="E62" s="67" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F62" s="90" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G62" s="91">
         <v>0.75519999999999998</v>
@@ -7417,46 +7452,45 @@
         <v>85918.57</v>
       </c>
       <c r="I62" s="169">
-        <f>H62</f>
-        <v>85918.57</v>
+        <v>85496.57</v>
       </c>
       <c r="J62" s="80"/>
       <c r="K62" s="81">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="L62" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.66</v>
       </c>
       <c r="M62" s="82">
         <v>0</v>
       </c>
       <c r="N62" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O62" s="84">
         <v>0</v>
       </c>
       <c r="P62" s="85">
         <f t="shared" si="3"/>
-        <v>85918.57</v>
+        <v>93904.57</v>
       </c>
       <c r="Q62" s="86">
         <f t="shared" si="4"/>
-        <v>91074.57</v>
+        <v>99539.57</v>
       </c>
       <c r="R62" s="87">
         <f t="shared" si="5"/>
-        <v>88496.57</v>
+        <v>96721.57</v>
       </c>
       <c r="S62" s="46">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="68">
         <v>8</v>
       </c>
@@ -7495,29 +7529,29 @@
       </c>
       <c r="N63" s="83">
         <f>P$2*G63%</f>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O63" s="84">
         <v>0</v>
       </c>
       <c r="P63" s="85">
         <f t="shared" si="3"/>
-        <v>131346.57999999999</v>
+        <v>142891.57999999999</v>
       </c>
       <c r="Q63" s="86">
         <f t="shared" si="4"/>
-        <v>139227.57999999999</v>
+        <v>151465.57999999999</v>
       </c>
       <c r="R63" s="87">
         <f t="shared" si="5"/>
-        <v>135286.57999999999</v>
+        <v>147178.57999999999</v>
       </c>
       <c r="S63" s="46">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="68">
         <v>9</v>
       </c>
@@ -7529,55 +7563,57 @@
         <v>59</v>
       </c>
       <c r="E64" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="F64" s="67" t="s">
         <v>156</v>
-      </c>
-      <c r="F64" s="67" t="s">
-        <v>157</v>
       </c>
       <c r="G64" s="91">
         <v>0.95489999999999997</v>
       </c>
       <c r="H64" s="78">
-        <v>108637.59</v>
-      </c>
-      <c r="I64" s="169"/>
+        <v>220534.59</v>
+      </c>
+      <c r="I64" s="169">
+        <v>108637</v>
+      </c>
       <c r="J64" s="80"/>
       <c r="K64" s="81">
         <f t="shared" si="1"/>
-        <v>108637.59</v>
+        <v>111897.59</v>
       </c>
       <c r="L64" s="81">
         <f t="shared" si="2"/>
-        <v>3259.1276999999995</v>
+        <v>3356.9276999999997</v>
       </c>
       <c r="M64" s="82">
         <v>0</v>
       </c>
       <c r="N64" s="83">
         <f>P$2*G64%</f>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O64" s="84">
         <v>0</v>
       </c>
       <c r="P64" s="85">
         <f t="shared" si="3"/>
-        <v>220534.59</v>
+        <v>233441.59</v>
       </c>
       <c r="Q64" s="86">
         <f t="shared" si="4"/>
-        <v>233767.59</v>
+        <v>247448.59</v>
       </c>
       <c r="R64" s="87">
         <f t="shared" si="5"/>
-        <v>227150.59</v>
+        <v>240444.59</v>
       </c>
       <c r="S64" s="46">
         <f t="shared" si="7"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="68">
         <v>9</v>
       </c>
@@ -7589,58 +7625,58 @@
         <v>60</v>
       </c>
       <c r="E65" s="67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F65" s="90"/>
       <c r="G65" s="91">
         <v>0.75519999999999998</v>
       </c>
       <c r="H65" s="78">
-        <v>85918.6</v>
+        <v>88496</v>
       </c>
       <c r="I65" s="169">
-        <v>78403.600000000006</v>
+        <v>85918</v>
       </c>
       <c r="J65" s="80"/>
       <c r="K65" s="81">
         <f t="shared" si="1"/>
-        <v>7515</v>
+        <v>2578</v>
       </c>
       <c r="L65" s="81">
         <f t="shared" si="2"/>
-        <v>225.45</v>
+        <v>77.34</v>
       </c>
       <c r="M65" s="82">
         <v>0</v>
       </c>
       <c r="N65" s="83">
         <f>P$2*G65%</f>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O65" s="84">
         <v>0</v>
       </c>
       <c r="P65" s="85">
         <f t="shared" si="3"/>
-        <v>93658.6</v>
+        <v>96125.6</v>
       </c>
       <c r="Q65" s="86">
         <f t="shared" si="4"/>
-        <v>99278.6</v>
+        <v>101893.6</v>
       </c>
       <c r="R65" s="87">
         <f t="shared" si="5"/>
-        <v>96468.6</v>
+        <v>99009.600000000006</v>
       </c>
       <c r="S65" s="46">
         <f t="shared" si="7"/>
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="68">
         <v>9</v>
       </c>
@@ -7662,7 +7698,7 @@
         <v>131346.60999999999</v>
       </c>
       <c r="I66" s="169">
-        <f>119858.61+11488</f>
+        <f>H66</f>
         <v>131346.60999999999</v>
       </c>
       <c r="J66" s="80"/>
@@ -7679,32 +7715,32 @@
       </c>
       <c r="N66" s="83">
         <f>P$2*G66%</f>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O66" s="84">
         <v>0</v>
       </c>
       <c r="P66" s="85">
         <f t="shared" si="3"/>
-        <v>131346.60999999999</v>
+        <v>142891.60999999999</v>
       </c>
       <c r="Q66" s="86">
         <f t="shared" si="4"/>
-        <v>139227.60999999999</v>
+        <v>151465.60999999999</v>
       </c>
       <c r="R66" s="87">
         <f t="shared" si="5"/>
-        <v>135286.60999999999</v>
+        <v>147178.60999999999</v>
       </c>
       <c r="S66" s="46">
         <f t="shared" si="7"/>
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="68">
         <v>10</v>
       </c>
@@ -7716,61 +7752,61 @@
         <v>62</v>
       </c>
       <c r="E67" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="F67" s="90" t="s">
         <v>159</v>
-      </c>
-      <c r="F67" s="90" t="s">
-        <v>160</v>
       </c>
       <c r="G67" s="91">
         <v>0.95489999999999997</v>
       </c>
       <c r="H67" s="78">
-        <v>213060.62</v>
+        <v>108638.62</v>
       </c>
       <c r="I67" s="169">
-        <f>92690.35+108627+11743</f>
-        <v>213060.35</v>
+        <f>H67</f>
+        <v>108638.62</v>
       </c>
       <c r="J67" s="80"/>
       <c r="K67" s="81">
         <f t="shared" si="1"/>
-        <v>0.26999999998952262</v>
+        <v>0</v>
       </c>
       <c r="L67" s="81">
         <f t="shared" si="2"/>
-        <v>8.0999999996856781E-3</v>
+        <v>0</v>
       </c>
       <c r="M67" s="82">
         <v>0</v>
       </c>
       <c r="N67" s="83">
         <f t="shared" si="0"/>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O67" s="84">
         <v>0</v>
       </c>
       <c r="P67" s="85">
         <f t="shared" si="3"/>
-        <v>108638.62</v>
+        <v>118186.62</v>
       </c>
       <c r="Q67" s="86">
         <f t="shared" si="4"/>
-        <v>115157.62</v>
+        <v>125278.62</v>
       </c>
       <c r="R67" s="87">
         <f t="shared" si="5"/>
-        <v>111897.62</v>
+        <v>121732.62</v>
       </c>
       <c r="S67" s="46">
         <f t="shared" si="7"/>
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="68">
         <v>10</v>
       </c>
@@ -7785,13 +7821,13 @@
         <v>123</v>
       </c>
       <c r="F68" s="67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G68" s="91">
         <v>0.75519999999999998</v>
       </c>
       <c r="H68" s="78">
-        <v>88340.63</v>
+        <v>88412.63</v>
       </c>
       <c r="I68" s="169">
         <v>85918.63</v>
@@ -7799,40 +7835,40 @@
       <c r="J68" s="80"/>
       <c r="K68" s="81">
         <f t="shared" si="1"/>
-        <v>2422</v>
+        <v>2494</v>
       </c>
       <c r="L68" s="81">
         <f t="shared" si="2"/>
-        <v>72.66</v>
+        <v>74.819999999999993</v>
       </c>
       <c r="M68" s="82">
         <v>0</v>
       </c>
       <c r="N68" s="83">
         <f t="shared" si="0"/>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O68" s="84">
         <v>0</v>
       </c>
       <c r="P68" s="85">
         <f t="shared" si="3"/>
-        <v>88412.63</v>
+        <v>96039.63</v>
       </c>
       <c r="Q68" s="86">
         <f t="shared" si="4"/>
-        <v>93717.63</v>
+        <v>101802.63</v>
       </c>
       <c r="R68" s="87">
         <f t="shared" si="5"/>
-        <v>91064.63</v>
+        <v>98920.63</v>
       </c>
       <c r="S68" s="46">
         <f t="shared" si="7"/>
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="68">
         <v>10</v>
       </c>
@@ -7871,29 +7907,29 @@
       </c>
       <c r="N69" s="83">
         <f t="shared" si="0"/>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O69" s="84">
         <v>0</v>
       </c>
       <c r="P69" s="85">
         <f t="shared" si="3"/>
-        <v>131346.64000000001</v>
+        <v>142891.64000000001</v>
       </c>
       <c r="Q69" s="86">
         <f t="shared" si="4"/>
-        <v>139227.64000000001</v>
+        <v>151465.64000000001</v>
       </c>
       <c r="R69" s="87">
         <f t="shared" si="5"/>
-        <v>135286.64000000001</v>
+        <v>147178.64000000001</v>
       </c>
       <c r="S69" s="46">
         <f t="shared" si="7"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="68">
         <v>11</v>
       </c>
@@ -7931,30 +7967,30 @@
         <v>0</v>
       </c>
       <c r="N70" s="83">
-        <f t="shared" ref="N70" si="11">P$2*G70%</f>
-        <v>108637.36342056</v>
+        <f t="shared" ref="N70" si="13">P$2*G70%</f>
+        <v>118186.36342056</v>
       </c>
       <c r="O70" s="84">
         <v>0</v>
       </c>
       <c r="P70" s="85">
         <f t="shared" si="3"/>
-        <v>108637.65</v>
+        <v>118186.65</v>
       </c>
       <c r="Q70" s="86">
         <f t="shared" si="4"/>
-        <v>115156.65</v>
+        <v>125278.65</v>
       </c>
       <c r="R70" s="87">
         <f t="shared" si="5"/>
-        <v>111896.65</v>
+        <v>121732.65</v>
       </c>
       <c r="S70" s="46">
         <f t="shared" si="7"/>
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="68">
         <v>11</v>
       </c>
@@ -7969,25 +8005,24 @@
         <v>106</v>
       </c>
       <c r="F71" s="90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G71" s="91">
         <v>0.75519999999999998</v>
       </c>
       <c r="H71" s="78">
-        <v>88496.66</v>
+        <v>85918.66</v>
       </c>
       <c r="I71" s="169">
-        <f>H71</f>
         <v>88496.66</v>
       </c>
       <c r="J71" s="80"/>
       <c r="K71" s="81">
-        <f t="shared" ref="K71:K75" si="12">H71-I71</f>
-        <v>0</v>
+        <f t="shared" ref="K71:K75" si="14">H71-I71</f>
+        <v>-2578</v>
       </c>
       <c r="L71" s="81">
-        <f t="shared" ref="L71:L75" si="13">IF(K71&gt;0,K71*3%,0)</f>
+        <f t="shared" ref="L71:L75" si="15">IF(K71&gt;0,K71*3%,0)</f>
         <v>0</v>
       </c>
       <c r="M71" s="82">
@@ -7995,29 +8030,29 @@
       </c>
       <c r="N71" s="83">
         <f>P$2*G71%</f>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O71" s="84">
         <v>0</v>
       </c>
       <c r="P71" s="85">
-        <f t="shared" ref="P71:P75" si="14">ROUND(SUM(K71:O71),0) + S71</f>
-        <v>85918.66</v>
+        <f t="shared" ref="P71:P75" si="16">ROUND(SUM(K71:O71),0) + S71</f>
+        <v>90892.66</v>
       </c>
       <c r="Q71" s="86">
-        <f t="shared" ref="Q71:Q75" si="15">ROUND(P71*6% + P71,0) + S71</f>
-        <v>91074.66</v>
+        <f t="shared" ref="Q71:Q75" si="17">ROUND(P71*6% + P71,0) + S71</f>
+        <v>96346.66</v>
       </c>
       <c r="R71" s="87">
-        <f t="shared" ref="R71:R75" si="16">ROUND(P71*3%,0) + P71</f>
-        <v>88496.66</v>
+        <f t="shared" ref="R71:R75" si="18">ROUND(P71*3%,0) + P71</f>
+        <v>93619.66</v>
       </c>
       <c r="S71" s="46">
         <f t="shared" si="7"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="68">
         <v>11</v>
       </c>
@@ -8025,7 +8060,7 @@
         <v>115</v>
       </c>
       <c r="D72" s="68">
-        <f t="shared" ref="D72:D75" si="17">D71+1</f>
+        <f t="shared" ref="D72:D75" si="19">D71+1</f>
         <v>67</v>
       </c>
       <c r="E72" s="67" t="s">
@@ -8036,19 +8071,19 @@
         <v>1.1545000000000001</v>
       </c>
       <c r="H72" s="78">
-        <v>401726.67</v>
+        <v>131346.67000000001</v>
       </c>
       <c r="I72" s="169">
-        <f>262505.67+131346+7875</f>
-        <v>401726.67</v>
+        <f>H72</f>
+        <v>131346.67000000001</v>
       </c>
       <c r="J72" s="80"/>
       <c r="K72" s="81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L72" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M72" s="82">
@@ -8056,29 +8091,29 @@
       </c>
       <c r="N72" s="83">
         <f>P$2*G72%</f>
-        <v>131345.51897480001</v>
+        <v>142890.51897480001</v>
       </c>
       <c r="O72" s="84">
         <v>0</v>
       </c>
       <c r="P72" s="85">
-        <f t="shared" si="14"/>
-        <v>131346.67000000001</v>
+        <f t="shared" si="16"/>
+        <v>142891.67000000001</v>
       </c>
       <c r="Q72" s="86">
-        <f t="shared" si="15"/>
-        <v>139227.67000000001</v>
+        <f t="shared" si="17"/>
+        <v>151465.67000000001</v>
       </c>
       <c r="R72" s="87">
-        <f t="shared" si="16"/>
-        <v>135286.67000000001</v>
+        <f t="shared" si="18"/>
+        <v>147178.67000000001</v>
       </c>
       <c r="S72" s="46">
-        <f t="shared" ref="S72:S75" si="18">S71+0.01</f>
+        <f t="shared" ref="S72:S75" si="20">S71+0.01</f>
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="68">
         <v>12</v>
       </c>
@@ -8086,7 +8121,7 @@
         <v>113</v>
       </c>
       <c r="D73" s="68">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>68</v>
       </c>
       <c r="E73" s="94" t="s">
@@ -8100,16 +8135,16 @@
         <v>108637.68</v>
       </c>
       <c r="I73" s="169">
-        <f t="shared" ref="I73" si="19">H73</f>
+        <f t="shared" ref="I73" si="21">H73</f>
         <v>108637.68</v>
       </c>
       <c r="J73" s="98"/>
       <c r="K73" s="99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L73" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M73" s="82">
@@ -8117,29 +8152,29 @@
       </c>
       <c r="N73" s="100">
         <f>P$2*G73%</f>
-        <v>108637.36342056</v>
+        <v>118186.36342056</v>
       </c>
       <c r="O73" s="101">
         <v>0</v>
       </c>
       <c r="P73" s="85">
-        <f t="shared" si="14"/>
-        <v>108637.68</v>
+        <f t="shared" si="16"/>
+        <v>118186.68</v>
       </c>
       <c r="Q73" s="86">
-        <f t="shared" si="15"/>
-        <v>115156.68</v>
+        <f t="shared" si="17"/>
+        <v>125278.68</v>
       </c>
       <c r="R73" s="87">
-        <f t="shared" si="16"/>
-        <v>111896.68</v>
+        <f t="shared" si="18"/>
+        <v>121732.68</v>
       </c>
       <c r="S73" s="46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="68">
         <v>12</v>
       </c>
@@ -8147,7 +8182,7 @@
         <v>114</v>
       </c>
       <c r="D74" s="68">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>69</v>
       </c>
       <c r="E74" s="68" t="s">
@@ -8161,16 +8196,16 @@
         <v>85918.69</v>
       </c>
       <c r="I74" s="169">
-        <f>78403.69+7515</f>
+        <f>H74</f>
         <v>85918.69</v>
       </c>
       <c r="J74" s="98"/>
       <c r="K74" s="99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L74" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M74" s="82">
@@ -8178,29 +8213,29 @@
       </c>
       <c r="N74" s="100">
         <f>P$2*G74%</f>
-        <v>85917.831034879986</v>
+        <v>93469.831034879986</v>
       </c>
       <c r="O74" s="101">
         <v>0</v>
       </c>
       <c r="P74" s="85">
-        <f t="shared" si="14"/>
-        <v>85918.69</v>
+        <f t="shared" si="16"/>
+        <v>93470.69</v>
       </c>
       <c r="Q74" s="86">
-        <f t="shared" si="15"/>
-        <v>91074.69</v>
+        <f t="shared" si="17"/>
+        <v>99079.69</v>
       </c>
       <c r="R74" s="87">
-        <f t="shared" si="16"/>
-        <v>88496.69</v>
+        <f t="shared" si="18"/>
+        <v>96274.69</v>
       </c>
       <c r="S74" s="46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="68">
         <v>12</v>
       </c>
@@ -8208,7 +8243,7 @@
         <v>115</v>
       </c>
       <c r="D75" s="68">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>70</v>
       </c>
       <c r="E75" s="68" t="s">
@@ -8227,11 +8262,11 @@
       </c>
       <c r="J75" s="98"/>
       <c r="K75" s="99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L75" s="81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M75" s="82">
@@ -8239,38 +8274,36 @@
       </c>
       <c r="N75" s="100">
         <f>P$2*G75%</f>
-        <v>131391.02630055998</v>
+        <v>142940.02630055998</v>
       </c>
       <c r="O75" s="101">
         <v>0</v>
       </c>
       <c r="P75" s="85">
-        <f t="shared" si="14"/>
-        <v>131391.70000000001</v>
+        <f t="shared" si="16"/>
+        <v>142940.70000000001</v>
       </c>
       <c r="Q75" s="86">
-        <f t="shared" si="15"/>
-        <v>139275.70000000001</v>
+        <f t="shared" si="17"/>
+        <v>151517.70000000001</v>
       </c>
       <c r="R75" s="87">
-        <f t="shared" si="16"/>
-        <v>135333.70000000001</v>
+        <f t="shared" si="18"/>
+        <v>147228.70000000001</v>
       </c>
       <c r="S75" s="46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="68"/>
       <c r="C76" s="92"/>
       <c r="D76" s="92"/>
       <c r="E76" s="68"/>
       <c r="F76" s="69"/>
       <c r="G76" s="77"/>
-      <c r="H76" s="96">
-        <v>0</v>
-      </c>
+      <c r="H76" s="96"/>
       <c r="I76" s="97"/>
       <c r="J76" s="98"/>
       <c r="K76" s="99"/>
@@ -8283,7 +8316,7 @@
       <c r="R76" s="87"/>
       <c r="S76" s="46"/>
     </row>
-    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="68"/>
       <c r="C77" s="92"/>
       <c r="D77" s="92"/>
@@ -8303,7 +8336,7 @@
       <c r="R77" s="87"/>
       <c r="S77" s="46"/>
     </row>
-    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="68"/>
       <c r="C78" s="92"/>
       <c r="D78" s="92"/>
@@ -8323,7 +8356,7 @@
       <c r="R78" s="87"/>
       <c r="S78" s="46"/>
     </row>
-    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="103"/>
       <c r="C79" s="145"/>
       <c r="D79" s="93"/>
@@ -8343,7 +8376,7 @@
       <c r="R79" s="87"/>
       <c r="S79" s="46"/>
     </row>
-    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="68"/>
       <c r="C80" s="68"/>
       <c r="D80" s="68"/>
@@ -8363,7 +8396,7 @@
       <c r="R80" s="107"/>
       <c r="S80" s="46"/>
     </row>
-    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="108"/>
       <c r="C81" s="146"/>
       <c r="D81" s="109"/>
@@ -8375,145 +8408,137 @@
       </c>
       <c r="H81" s="56">
         <f>SUM(H6:H80)</f>
-        <v>15566811.85</v>
+        <v>15951195.749999998</v>
       </c>
       <c r="I81" s="65">
         <f>SUM(I6:I80)</f>
-        <v>11284159.269999998</v>
+        <v>10964795.799999999</v>
       </c>
       <c r="J81" s="56">
-        <f t="shared" ref="J81:Q81" si="20">SUM(J6:J80)</f>
+        <f t="shared" ref="J81:Q81" si="22">SUM(J6:J80)</f>
         <v>0</v>
       </c>
       <c r="K81" s="65">
         <f>SUM(K6:K80)</f>
-        <v>4282652.5799999991</v>
+        <v>4986399.95</v>
       </c>
       <c r="L81" s="65"/>
       <c r="M81" s="65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N81" s="65">
-        <f t="shared" si="20"/>
-        <v>11376831.43999999</v>
+        <f t="shared" si="22"/>
+        <v>12376831.439999986</v>
       </c>
       <c r="O81" s="65">
-        <f t="shared" si="20"/>
-        <v>155000</v>
+        <f t="shared" si="22"/>
+        <v>65000</v>
       </c>
       <c r="P81" s="112">
-        <f t="shared" si="20"/>
-        <v>15943716.85</v>
+        <f t="shared" si="22"/>
+        <v>17578685.849999998</v>
       </c>
       <c r="Q81" s="112">
-        <f t="shared" si="20"/>
-        <v>16900370.849999998</v>
+        <f t="shared" si="22"/>
+        <v>18633433.850000001</v>
       </c>
       <c r="R81" s="112"/>
     </row>
-    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E82" s="53"/>
       <c r="F82" s="53"/>
     </row>
-    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="221" t="str">
+    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E84" s="214" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="221"/>
-      <c r="G84" s="221"/>
-      <c r="H84" s="221"/>
-      <c r="I84" s="221"/>
-      <c r="J84" s="221"/>
-      <c r="K84" s="221"/>
-      <c r="L84" s="221"/>
-      <c r="M84" s="221"/>
-      <c r="N84" s="221"/>
-      <c r="O84" s="221"/>
-      <c r="P84" s="221"/>
-    </row>
-    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E85" s="221"/>
-      <c r="F85" s="221"/>
-      <c r="G85" s="221"/>
-      <c r="H85" s="221"/>
-      <c r="I85" s="221"/>
-      <c r="J85" s="221"/>
-      <c r="K85" s="221"/>
-      <c r="L85" s="221"/>
-      <c r="M85" s="221"/>
-      <c r="N85" s="221"/>
-      <c r="O85" s="221"/>
-      <c r="P85" s="221"/>
-    </row>
-    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E86" s="221"/>
-      <c r="F86" s="221"/>
-      <c r="G86" s="221"/>
-      <c r="H86" s="221"/>
-      <c r="I86" s="221"/>
-      <c r="J86" s="221"/>
-      <c r="K86" s="221"/>
-      <c r="L86" s="221"/>
-      <c r="M86" s="221"/>
-      <c r="N86" s="221"/>
-      <c r="O86" s="221"/>
-      <c r="P86" s="221"/>
-    </row>
-    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="221"/>
-      <c r="F87" s="221"/>
-      <c r="G87" s="221"/>
-      <c r="H87" s="221"/>
-      <c r="I87" s="221"/>
-      <c r="J87" s="221"/>
-      <c r="K87" s="221"/>
-      <c r="L87" s="221"/>
-      <c r="M87" s="221"/>
-      <c r="N87" s="221"/>
-      <c r="O87" s="221"/>
-      <c r="P87" s="221"/>
-    </row>
-    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E88" s="221"/>
-      <c r="F88" s="221"/>
-      <c r="G88" s="221"/>
-      <c r="H88" s="221"/>
-      <c r="I88" s="221"/>
-      <c r="J88" s="221"/>
-      <c r="K88" s="221"/>
-      <c r="L88" s="221"/>
-      <c r="M88" s="221"/>
-      <c r="N88" s="221"/>
-      <c r="O88" s="221"/>
-      <c r="P88" s="221"/>
-    </row>
-    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="221"/>
-      <c r="F89" s="221"/>
-      <c r="G89" s="221"/>
-      <c r="H89" s="221"/>
-      <c r="I89" s="221"/>
-      <c r="J89" s="221"/>
-      <c r="K89" s="221"/>
-      <c r="L89" s="221"/>
-      <c r="M89" s="221"/>
-      <c r="N89" s="221"/>
-      <c r="O89" s="221"/>
-      <c r="P89" s="221"/>
+      <c r="F84" s="214"/>
+      <c r="G84" s="214"/>
+      <c r="H84" s="214"/>
+      <c r="I84" s="214"/>
+      <c r="J84" s="214"/>
+      <c r="K84" s="214"/>
+      <c r="L84" s="214"/>
+      <c r="M84" s="214"/>
+      <c r="N84" s="214"/>
+      <c r="O84" s="214"/>
+      <c r="P84" s="214"/>
+    </row>
+    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E85" s="214"/>
+      <c r="F85" s="214"/>
+      <c r="G85" s="214"/>
+      <c r="H85" s="214"/>
+      <c r="I85" s="214"/>
+      <c r="J85" s="214"/>
+      <c r="K85" s="214"/>
+      <c r="L85" s="214"/>
+      <c r="M85" s="214"/>
+      <c r="N85" s="214"/>
+      <c r="O85" s="214"/>
+      <c r="P85" s="214"/>
+    </row>
+    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E86" s="214"/>
+      <c r="F86" s="214"/>
+      <c r="G86" s="214"/>
+      <c r="H86" s="214"/>
+      <c r="I86" s="214"/>
+      <c r="J86" s="214"/>
+      <c r="K86" s="214"/>
+      <c r="L86" s="214"/>
+      <c r="M86" s="214"/>
+      <c r="N86" s="214"/>
+      <c r="O86" s="214"/>
+      <c r="P86" s="214"/>
+    </row>
+    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E87" s="214"/>
+      <c r="F87" s="214"/>
+      <c r="G87" s="214"/>
+      <c r="H87" s="214"/>
+      <c r="I87" s="214"/>
+      <c r="J87" s="214"/>
+      <c r="K87" s="214"/>
+      <c r="L87" s="214"/>
+      <c r="M87" s="214"/>
+      <c r="N87" s="214"/>
+      <c r="O87" s="214"/>
+      <c r="P87" s="214"/>
+    </row>
+    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E88" s="214"/>
+      <c r="F88" s="214"/>
+      <c r="G88" s="214"/>
+      <c r="H88" s="214"/>
+      <c r="I88" s="214"/>
+      <c r="J88" s="214"/>
+      <c r="K88" s="214"/>
+      <c r="L88" s="214"/>
+      <c r="M88" s="214"/>
+      <c r="N88" s="214"/>
+      <c r="O88" s="214"/>
+      <c r="P88" s="214"/>
+    </row>
+    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E89" s="214"/>
+      <c r="F89" s="214"/>
+      <c r="G89" s="214"/>
+      <c r="H89" s="214"/>
+      <c r="I89" s="214"/>
+      <c r="J89" s="214"/>
+      <c r="K89" s="214"/>
+      <c r="L89" s="214"/>
+      <c r="M89" s="214"/>
+      <c r="N89" s="214"/>
+      <c r="O89" s="214"/>
+      <c r="P89" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="H4:H5"/>
@@ -8525,6 +8550,14 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="R4:R5"/>
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/GORRITI/Mayo/GORRITI-MAYO.xlsx
+++ b/GORRITI/Mayo/GORRITI-MAYO.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A86D8D6-5DC9-4BF4-A245-A61732C051ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4583763-8CF9-49FC-969B-5095573AF4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="256">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -414,9 +415,6 @@
     <t>BORTZ ESTHER</t>
   </si>
   <si>
-    <t>Daniel</t>
-  </si>
-  <si>
     <t>CARRIZO RAÚL</t>
   </si>
   <si>
@@ -790,6 +788,12 @@
   </si>
   <si>
     <t xml:space="preserve">SE PRORRATEA UN MONTO MENOS A EL GASTO REAL EFECTUADO ($12.841.476,05) </t>
+  </si>
+  <si>
+    <t>Daniel / Luciana</t>
+  </si>
+  <si>
+    <t>LUCIANA TIENE TODO PAGO, CORREGIR ESO</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1014,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1080,6 +1084,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1496,7 +1506,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1801,23 +1811,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1837,26 +1841,17 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1872,6 +1867,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1897,12 +1898,25 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2334,7 +2348,7 @@
         <v>71</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="75" t="s">
@@ -2354,49 +2368,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="219" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" s="219"/>
+      <c r="B9" s="217" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="217"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="219"/>
-      <c r="C11" s="219"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="218" t="s">
+      <c r="A14" s="216" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="218"/>
-      <c r="C14" s="218"/>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
+      <c r="B14" s="216"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="218"/>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
+      <c r="A15" s="216"/>
+      <c r="B15" s="216"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
-      <c r="B16" s="218"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
+      <c r="A16" s="216"/>
+      <c r="B16" s="216"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="218"/>
-      <c r="B17" s="218"/>
-      <c r="C17" s="218"/>
-      <c r="D17" s="218"/>
-      <c r="E17" s="218"/>
+      <c r="A17" s="216"/>
+      <c r="B17" s="216"/>
+      <c r="C17" s="216"/>
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2423,7 +2437,7 @@
     </row>
     <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2431,7 +2445,7 @@
         <v>1227647</v>
       </c>
       <c r="E23" s="164" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2485,7 +2499,7 @@
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2493,7 +2507,7 @@
         <v>1076104</v>
       </c>
       <c r="E29" s="164" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2588,30 +2602,30 @@
       <c r="E39" s="178"/>
     </row>
     <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="220" t="s">
-        <v>237</v>
-      </c>
-      <c r="B40" s="221"/>
+      <c r="A40" s="218" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="219"/>
       <c r="C40" s="205"/>
       <c r="D40" s="170">
         <f>2*56000</f>
         <v>112000</v>
       </c>
       <c r="E40" s="204" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="212" t="s">
-        <v>207</v>
-      </c>
-      <c r="B41" s="213"/>
+      <c r="A41" s="210" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" s="211"/>
       <c r="C41" s="55"/>
       <c r="D41" s="170">
         <v>249000</v>
       </c>
       <c r="E41" s="204" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H41" s="147"/>
     </row>
@@ -2637,21 +2651,21 @@
       <c r="E43" s="182"/>
     </row>
     <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="210" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="211"/>
+      <c r="A44" s="212" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="213"/>
       <c r="C44" s="57"/>
       <c r="D44" s="183">
         <v>120977</v>
       </c>
       <c r="E44" s="184" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="210"/>
-      <c r="B45" s="211"/>
+      <c r="A45" s="212"/>
+      <c r="B45" s="213"/>
       <c r="C45" s="57"/>
       <c r="D45" s="185"/>
       <c r="E45" s="184"/>
@@ -2679,7 +2693,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="55"/>
@@ -2687,13 +2701,13 @@
         <v>1644550.83</v>
       </c>
       <c r="E48" s="188" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G48" s="147"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>38</v>
@@ -2703,7 +2717,7 @@
         <v>129055.15</v>
       </c>
       <c r="E49" s="190" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2763,7 +2777,7 @@
     </row>
     <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2771,12 +2785,12 @@
         <v>814908.33</v>
       </c>
       <c r="E54" s="202" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2790,7 +2804,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2804,7 +2818,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2812,12 +2826,12 @@
         <v>11961.98</v>
       </c>
       <c r="E57" s="202" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2825,12 +2839,12 @@
         <v>9656.9599999999991</v>
       </c>
       <c r="E58" s="193" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2838,12 +2852,12 @@
         <v>571919</v>
       </c>
       <c r="E59" s="193" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2851,28 +2865,28 @@
         <v>22050.01</v>
       </c>
       <c r="E60" s="194" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="210" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" s="211"/>
+      <c r="A61" s="212" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" s="213"/>
       <c r="C61" s="5"/>
       <c r="D61" s="189">
         <v>2302294.3199999998</v>
       </c>
       <c r="E61" s="193" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="210"/>
-      <c r="B62" s="211"/>
+      <c r="A62" s="212"/>
+      <c r="B62" s="213"/>
       <c r="C62" s="166"/>
-      <c r="D62" s="216"/>
-      <c r="E62" s="217"/>
+      <c r="D62" s="214"/>
+      <c r="E62" s="215"/>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
@@ -2896,48 +2910,48 @@
       <c r="E64" s="195"/>
     </row>
     <row r="65" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="212" t="s">
-        <v>232</v>
-      </c>
-      <c r="B65" s="213"/>
+      <c r="A65" s="210" t="s">
+        <v>231</v>
+      </c>
+      <c r="B65" s="211"/>
       <c r="C65" s="58"/>
       <c r="D65" s="189">
         <f>72600+360000</f>
         <v>432600</v>
       </c>
       <c r="E65" s="126" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="212" t="s">
-        <v>231</v>
-      </c>
-      <c r="B66" s="213"/>
+      <c r="A66" s="210" t="s">
+        <v>230</v>
+      </c>
+      <c r="B66" s="211"/>
       <c r="C66" s="58"/>
       <c r="D66" s="189">
         <v>96800</v>
       </c>
       <c r="E66" s="126" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="212" t="s">
-        <v>235</v>
-      </c>
-      <c r="B67" s="213"/>
+      <c r="A67" s="210" t="s">
+        <v>234</v>
+      </c>
+      <c r="B67" s="211"/>
       <c r="C67" s="58"/>
       <c r="D67" s="189">
         <v>38000</v>
       </c>
       <c r="E67" s="126" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2945,12 +2959,12 @@
         <v>52000</v>
       </c>
       <c r="E68" s="202" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B69" s="167"/>
       <c r="C69" s="5"/>
@@ -2958,12 +2972,12 @@
         <v>53500</v>
       </c>
       <c r="E69" s="202" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="167"/>
       <c r="C70" s="5"/>
@@ -2971,136 +2985,136 @@
         <v>120000</v>
       </c>
       <c r="E70" s="203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="210" t="s">
-        <v>244</v>
-      </c>
-      <c r="B71" s="211"/>
+      <c r="A71" s="212" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="213"/>
       <c r="C71" s="5"/>
       <c r="D71" s="189">
         <v>111908.93</v>
       </c>
       <c r="E71" s="196" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H71" s="168" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="212" t="s">
-        <v>242</v>
-      </c>
-      <c r="B72" s="213"/>
+      <c r="A72" s="210" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" s="211"/>
       <c r="C72" s="5"/>
       <c r="D72" s="189">
         <v>240000</v>
       </c>
       <c r="E72" s="203" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H72" s="168" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="212" t="s">
-        <v>243</v>
-      </c>
-      <c r="B73" s="213"/>
+      <c r="A73" s="210" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" s="211"/>
       <c r="C73" s="5"/>
       <c r="D73" s="124">
         <v>260000</v>
       </c>
       <c r="E73" s="194" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H73" s="168"/>
     </row>
     <row r="74" spans="1:8" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="212" t="s">
-        <v>216</v>
-      </c>
-      <c r="B74" s="213"/>
+      <c r="A74" s="210" t="s">
+        <v>215</v>
+      </c>
+      <c r="B74" s="211"/>
       <c r="C74" s="5"/>
       <c r="D74" s="124">
         <v>240000</v>
       </c>
       <c r="E74" s="194" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="212" t="s">
-        <v>218</v>
-      </c>
-      <c r="B75" s="213"/>
+      <c r="A75" s="210" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="211"/>
       <c r="C75" s="5"/>
       <c r="D75" s="124">
         <v>45000</v>
       </c>
       <c r="E75" s="194" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="212" t="s">
-        <v>219</v>
-      </c>
-      <c r="B76" s="213"/>
+      <c r="A76" s="210" t="s">
+        <v>218</v>
+      </c>
+      <c r="B76" s="211"/>
       <c r="C76" s="5"/>
       <c r="D76" s="124">
         <v>130000</v>
       </c>
       <c r="E76" s="194" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="212" t="s">
-        <v>211</v>
-      </c>
-      <c r="B77" s="213"/>
+      <c r="A77" s="210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B77" s="211"/>
       <c r="C77" s="5"/>
       <c r="D77" s="124">
         <v>210000</v>
       </c>
       <c r="E77" s="194" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="210" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="212" t="s">
-        <v>210</v>
-      </c>
-      <c r="B78" s="213"/>
+      <c r="B78" s="211"/>
       <c r="C78" s="5"/>
       <c r="D78" s="124">
         <v>115000</v>
       </c>
       <c r="E78" s="194" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="212" t="s">
-        <v>234</v>
-      </c>
-      <c r="B79" s="213"/>
+      <c r="A79" s="210" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" s="211"/>
       <c r="C79" s="5"/>
       <c r="D79" s="124">
         <v>360000</v>
       </c>
       <c r="E79" s="194" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="208" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B80" s="201"/>
       <c r="C80" s="5"/>
@@ -3108,38 +3122,38 @@
         <v>710000</v>
       </c>
       <c r="E80" s="194" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="212" t="s">
-        <v>253</v>
-      </c>
-      <c r="B81" s="213"/>
+      <c r="A81" s="210" t="s">
+        <v>252</v>
+      </c>
+      <c r="B81" s="211"/>
       <c r="C81" s="5"/>
       <c r="D81" s="124">
         <v>770000</v>
       </c>
       <c r="E81" s="194" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="210" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="212" t="s">
-        <v>226</v>
-      </c>
-      <c r="B82" s="213"/>
+      <c r="B82" s="211"/>
       <c r="C82" s="5"/>
       <c r="D82" s="124">
         <v>120000</v>
       </c>
       <c r="E82" s="194" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="200" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B83" s="201"/>
       <c r="C83" s="5"/>
@@ -3147,14 +3161,14 @@
         <v>12000</v>
       </c>
       <c r="E83" s="194" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="212" t="s">
-        <v>208</v>
-      </c>
-      <c r="B84" s="213"/>
+      <c r="A84" s="210" t="s">
+        <v>207</v>
+      </c>
+      <c r="B84" s="211"/>
       <c r="C84" s="5"/>
       <c r="D84" s="124">
         <f>1600+6400</f>
@@ -3163,13 +3177,13 @@
       <c r="E84" s="194"/>
     </row>
     <row r="85" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="210"/>
-      <c r="B85" s="211"/>
+      <c r="A85" s="212"/>
+      <c r="B85" s="213"/>
       <c r="C85" s="5"/>
       <c r="D85" s="124"/>
       <c r="E85" s="197"/>
-      <c r="I85" s="210"/>
-      <c r="J85" s="211"/>
+      <c r="I85" s="212"/>
+      <c r="J85" s="213"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="30" t="s">
@@ -3206,7 +3220,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3234,7 +3248,7 @@
     </row>
     <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B92" s="32"/>
       <c r="C92" s="32"/>
@@ -3271,7 +3285,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B97" s="12"/>
       <c r="C97" s="13"/>
@@ -3279,22 +3293,22 @@
       <c r="E97" s="136"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="210"/>
-      <c r="B98" s="211"/>
+      <c r="A98" s="212"/>
+      <c r="B98" s="213"/>
       <c r="C98" s="5"/>
       <c r="D98" s="152"/>
       <c r="E98" s="122"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="210"/>
-      <c r="B99" s="211"/>
+      <c r="A99" s="212"/>
+      <c r="B99" s="213"/>
       <c r="C99" s="5"/>
       <c r="D99" s="124"/>
       <c r="E99" s="122"/>
     </row>
     <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="212"/>
-      <c r="B100" s="213"/>
+      <c r="A100" s="210"/>
+      <c r="B100" s="211"/>
       <c r="C100" s="5"/>
       <c r="D100" s="124"/>
       <c r="E100" s="122"/>
@@ -3378,32 +3392,32 @@
       </c>
     </row>
     <row r="113" spans="1:5" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="242" t="s">
-        <v>254</v>
-      </c>
-      <c r="B113" s="243"/>
+      <c r="A113" s="222" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="223"/>
     </row>
     <row r="114" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="214"/>
-      <c r="B115" s="214"/>
-      <c r="C115" s="214"/>
-      <c r="D115" s="214"/>
-      <c r="E115" s="214"/>
+      <c r="A115" s="220"/>
+      <c r="B115" s="220"/>
+      <c r="C115" s="220"/>
+      <c r="D115" s="220"/>
+      <c r="E115" s="220"/>
     </row>
     <row r="116" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="214"/>
-      <c r="B116" s="214"/>
-      <c r="C116" s="214"/>
-      <c r="D116" s="214"/>
-      <c r="E116" s="214"/>
+      <c r="A116" s="220"/>
+      <c r="B116" s="220"/>
+      <c r="C116" s="220"/>
+      <c r="D116" s="220"/>
+      <c r="E116" s="220"/>
     </row>
     <row r="117" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="214"/>
-      <c r="B117" s="214"/>
-      <c r="C117" s="214"/>
-      <c r="D117" s="214"/>
-      <c r="E117" s="214"/>
+      <c r="A117" s="220"/>
+      <c r="B117" s="220"/>
+      <c r="C117" s="220"/>
+      <c r="D117" s="220"/>
+      <c r="E117" s="220"/>
     </row>
     <row r="119" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
@@ -3453,7 +3467,7 @@
     </row>
     <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="142" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B125" s="50"/>
       <c r="C125" s="24"/>
@@ -3507,7 +3521,7 @@
     </row>
     <row r="132" spans="1:6" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="154" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B132" s="155">
         <v>1422704.1999999937</v>
@@ -3517,7 +3531,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B133" s="159">
         <f>-B110</f>
@@ -3526,7 +3540,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B134" s="159">
         <f>-B111</f>
@@ -3535,7 +3549,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="57" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B135" s="159">
         <f>B146</f>
@@ -3544,7 +3558,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B136" s="160">
         <f>PRORRATEO!I81</f>
@@ -3553,7 +3567,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B137" s="206">
         <v>-65000</v>
@@ -3561,13 +3575,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="161" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B138" s="162"/>
     </row>
     <row r="139" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="157" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B139" s="158">
         <f>SUM(B132:C138)</f>
@@ -3580,20 +3594,20 @@
     </row>
     <row r="141" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="215" t="s">
+      <c r="A142" s="221" t="s">
         <v>55</v>
       </c>
-      <c r="B142" s="215"/>
-      <c r="C142" s="215"/>
+      <c r="B142" s="221"/>
+      <c r="C142" s="221"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="215"/>
-      <c r="B143" s="215"/>
-      <c r="C143" s="215"/>
+      <c r="A143" s="221"/>
+      <c r="B143" s="221"/>
+      <c r="C143" s="221"/>
     </row>
     <row r="144" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="139" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B144" s="38">
         <v>184089</v>
@@ -3621,52 +3635,35 @@
       <c r="M147" s="8"/>
     </row>
     <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="214"/>
-      <c r="B148" s="214"/>
-      <c r="C148" s="214"/>
-      <c r="D148" s="214"/>
-      <c r="E148" s="214"/>
+      <c r="A148" s="220"/>
+      <c r="B148" s="220"/>
+      <c r="C148" s="220"/>
+      <c r="D148" s="220"/>
+      <c r="E148" s="220"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A149" s="214"/>
-      <c r="B149" s="214"/>
-      <c r="C149" s="214"/>
-      <c r="D149" s="214"/>
-      <c r="E149" s="214"/>
+      <c r="A149" s="220"/>
+      <c r="B149" s="220"/>
+      <c r="C149" s="220"/>
+      <c r="D149" s="220"/>
+      <c r="E149" s="220"/>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A150" s="214"/>
-      <c r="B150" s="214"/>
-      <c r="C150" s="214"/>
-      <c r="D150" s="214"/>
-      <c r="E150" s="214"/>
+      <c r="A150" s="220"/>
+      <c r="B150" s="220"/>
+      <c r="C150" s="220"/>
+      <c r="D150" s="220"/>
+      <c r="E150" s="220"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="214"/>
-      <c r="B151" s="214"/>
-      <c r="C151" s="214"/>
-      <c r="D151" s="214"/>
-      <c r="E151" s="214"/>
+      <c r="A151" s="220"/>
+      <c r="B151" s="220"/>
+      <c r="C151" s="220"/>
+      <c r="D151" s="220"/>
+      <c r="E151" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A62:B62"/>
     <mergeCell ref="I85:J85"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A148:E151"/>
@@ -3683,6 +3680,23 @@
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A113:B113"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3725,16 +3739,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3754,16 +3768,16 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="239">
+      <c r="P2" s="236">
         <v>12376831.439999999</v>
       </c>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="239"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3787,82 +3801,82 @@
       <c r="R3" s="63"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="224" t="s">
+      <c r="A4" s="240" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="242" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="143"/>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="229" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="222" t="s">
+      <c r="F4" s="229" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="222" t="s">
+      <c r="G4" s="229" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="230" t="s">
-        <v>186</v>
-      </c>
-      <c r="I4" s="222" t="s">
+      <c r="H4" s="225" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="229" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="234" t="s">
+      <c r="K4" s="231" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="225" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="230" t="s">
+      <c r="M4" s="225" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="230" t="s">
+      <c r="N4" s="225" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="237" t="s">
+      <c r="O4" s="234" t="s">
         <v>63</v>
       </c>
       <c r="P4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="232" t="s">
+      <c r="Q4" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="240" t="s">
+      <c r="R4" s="237" t="s">
         <v>61</v>
       </c>
       <c r="U4" s="46"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="225"/>
-      <c r="B5" s="227"/>
+      <c r="A5" s="241"/>
+      <c r="B5" s="243"/>
       <c r="C5" s="144"/>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="231"/>
-      <c r="I5" s="228"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="236"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="238"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="233"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="235"/>
       <c r="P5" s="64" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="241"/>
+      <c r="Q5" s="228"/>
+      <c r="R5" s="238"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3924,7 +3938,7 @@
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4374,8 +4388,8 @@
       <c r="E14" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="69" t="s">
-        <v>203</v>
+      <c r="F14" s="244" t="s">
+        <v>202</v>
       </c>
       <c r="G14" s="77">
         <v>0.52439999999999998</v>
@@ -4423,7 +4437,7 @@
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4441,8 +4455,8 @@
       <c r="E15" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="69" t="s">
-        <v>203</v>
+      <c r="F15" s="244" t="s">
+        <v>202</v>
       </c>
       <c r="G15" s="77">
         <v>0.42399999999999999</v>
@@ -4487,7 +4501,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4569,7 +4583,7 @@
         <v>123</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G17" s="77">
         <v>2.7492999999999999</v>
@@ -4749,7 +4763,7 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4834,7 +4848,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="77">
         <v>2.6476999999999999</v>
@@ -4901,7 +4915,7 @@
         <v>81</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G22" s="77">
         <v>2.3235000000000001</v>
@@ -4964,10 +4978,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="153" t="s">
         <v>181</v>
-      </c>
-      <c r="F23" s="153" t="s">
-        <v>182</v>
       </c>
       <c r="G23" s="77">
         <v>2.6880000000000002</v>
@@ -5014,7 +5028,7 @@
         <v>0.18000000000000002</v>
       </c>
       <c r="U23" s="164" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5225,8 +5239,8 @@
       <c r="E27" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="69" t="s">
-        <v>129</v>
+      <c r="F27" s="244" t="s">
+        <v>254</v>
       </c>
       <c r="G27" s="77">
         <v>2.6360000000000001</v>
@@ -5274,10 +5288,10 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="69" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5487,10 +5501,10 @@
         <v>26</v>
       </c>
       <c r="E31" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="68" t="s">
         <v>130</v>
-      </c>
-      <c r="F31" s="68" t="s">
-        <v>131</v>
       </c>
       <c r="G31" s="77">
         <v>2.6469</v>
@@ -5681,10 +5695,10 @@
         <v>29</v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G34" s="77">
         <v>2.4476</v>
@@ -5808,10 +5822,10 @@
         <v>31</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G36" s="77">
         <v>2.3026</v>
@@ -6065,10 +6079,10 @@
         <v>35</v>
       </c>
       <c r="E40" s="68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G40" s="77">
         <v>1.0069999999999999</v>
@@ -6134,7 +6148,7 @@
         <v>94</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G41" s="77">
         <v>0.78120000000000001</v>
@@ -6182,7 +6196,7 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6201,7 +6215,7 @@
         <v>94</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G42" s="91">
         <v>1.2153</v>
@@ -6249,7 +6263,7 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6264,10 +6278,10 @@
         <v>38</v>
       </c>
       <c r="E43" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G43" s="91">
         <v>0.95489999999999997</v>
@@ -6388,7 +6402,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G45" s="91">
         <v>1.1545000000000001</v>
@@ -6447,10 +6461,10 @@
         <v>41</v>
       </c>
       <c r="E46" s="67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F46" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G46" s="91">
         <v>0.95489999999999997</v>
@@ -6631,10 +6645,10 @@
         <v>44</v>
       </c>
       <c r="E49" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F49" s="90" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G49" s="91">
         <v>0.95489999999999997</v>
@@ -6694,7 +6708,7 @@
         <v>45</v>
       </c>
       <c r="E50" s="67" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F50" s="67"/>
       <c r="G50" s="91">
@@ -6742,7 +6756,7 @@
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6757,10 +6771,10 @@
         <v>46</v>
       </c>
       <c r="E51" s="67" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F51" s="67" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G51" s="91">
         <v>1.1545000000000001</v>
@@ -6820,10 +6834,10 @@
         <v>47</v>
       </c>
       <c r="E52" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F52" s="90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G52" s="91">
         <v>0.95489999999999997</v>
@@ -6886,7 +6900,7 @@
         <v>123</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G53" s="91">
         <v>0.75519999999999998</v>
@@ -6946,10 +6960,10 @@
         <v>49</v>
       </c>
       <c r="E54" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="67" t="s">
         <v>148</v>
-      </c>
-      <c r="F54" s="67" t="s">
-        <v>149</v>
       </c>
       <c r="G54" s="91">
         <v>1.1545000000000001</v>
@@ -7119,7 +7133,7 @@
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7317,10 +7331,10 @@
         <v>55</v>
       </c>
       <c r="E60" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F60" s="67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G60" s="91">
         <v>1.1545000000000001</v>
@@ -7379,10 +7393,10 @@
         <v>56</v>
       </c>
       <c r="E61" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" s="90" t="s">
         <v>151</v>
-      </c>
-      <c r="F61" s="90" t="s">
-        <v>152</v>
       </c>
       <c r="G61" s="91">
         <v>0.95489999999999997</v>
@@ -7440,10 +7454,10 @@
         <v>57</v>
       </c>
       <c r="E62" s="67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F62" s="90" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G62" s="91">
         <v>0.75519999999999998</v>
@@ -7563,10 +7577,10 @@
         <v>59</v>
       </c>
       <c r="E64" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F64" s="67" t="s">
         <v>155</v>
-      </c>
-      <c r="F64" s="67" t="s">
-        <v>156</v>
       </c>
       <c r="G64" s="91">
         <v>0.95489999999999997</v>
@@ -7625,7 +7639,7 @@
         <v>60</v>
       </c>
       <c r="E65" s="67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F65" s="90"/>
       <c r="G65" s="91">
@@ -7673,7 +7687,7 @@
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7737,7 +7751,7 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7752,10 +7766,10 @@
         <v>62</v>
       </c>
       <c r="E67" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="F67" s="90" t="s">
         <v>158</v>
-      </c>
-      <c r="F67" s="90" t="s">
-        <v>159</v>
       </c>
       <c r="G67" s="91">
         <v>0.95489999999999997</v>
@@ -7803,7 +7817,7 @@
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7821,7 +7835,7 @@
         <v>123</v>
       </c>
       <c r="F68" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G68" s="91">
         <v>0.75519999999999998</v>
@@ -8005,7 +8019,7 @@
         <v>106</v>
       </c>
       <c r="F71" s="90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G71" s="91">
         <v>0.75519999999999998</v>
@@ -8451,94 +8465,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="214" t="str">
+      <c r="E84" s="220" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="214"/>
-      <c r="G84" s="214"/>
-      <c r="H84" s="214"/>
-      <c r="I84" s="214"/>
-      <c r="J84" s="214"/>
-      <c r="K84" s="214"/>
-      <c r="L84" s="214"/>
-      <c r="M84" s="214"/>
-      <c r="N84" s="214"/>
-      <c r="O84" s="214"/>
-      <c r="P84" s="214"/>
+      <c r="F84" s="220"/>
+      <c r="G84" s="220"/>
+      <c r="H84" s="220"/>
+      <c r="I84" s="220"/>
+      <c r="J84" s="220"/>
+      <c r="K84" s="220"/>
+      <c r="L84" s="220"/>
+      <c r="M84" s="220"/>
+      <c r="N84" s="220"/>
+      <c r="O84" s="220"/>
+      <c r="P84" s="220"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="214"/>
-      <c r="F85" s="214"/>
-      <c r="G85" s="214"/>
-      <c r="H85" s="214"/>
-      <c r="I85" s="214"/>
-      <c r="J85" s="214"/>
-      <c r="K85" s="214"/>
-      <c r="L85" s="214"/>
-      <c r="M85" s="214"/>
-      <c r="N85" s="214"/>
-      <c r="O85" s="214"/>
-      <c r="P85" s="214"/>
+      <c r="E85" s="220"/>
+      <c r="F85" s="220"/>
+      <c r="G85" s="220"/>
+      <c r="H85" s="220"/>
+      <c r="I85" s="220"/>
+      <c r="J85" s="220"/>
+      <c r="K85" s="220"/>
+      <c r="L85" s="220"/>
+      <c r="M85" s="220"/>
+      <c r="N85" s="220"/>
+      <c r="O85" s="220"/>
+      <c r="P85" s="220"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="214"/>
-      <c r="F86" s="214"/>
-      <c r="G86" s="214"/>
-      <c r="H86" s="214"/>
-      <c r="I86" s="214"/>
-      <c r="J86" s="214"/>
-      <c r="K86" s="214"/>
-      <c r="L86" s="214"/>
-      <c r="M86" s="214"/>
-      <c r="N86" s="214"/>
-      <c r="O86" s="214"/>
-      <c r="P86" s="214"/>
+      <c r="E86" s="220"/>
+      <c r="F86" s="220"/>
+      <c r="G86" s="220"/>
+      <c r="H86" s="220"/>
+      <c r="I86" s="220"/>
+      <c r="J86" s="220"/>
+      <c r="K86" s="220"/>
+      <c r="L86" s="220"/>
+      <c r="M86" s="220"/>
+      <c r="N86" s="220"/>
+      <c r="O86" s="220"/>
+      <c r="P86" s="220"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="214"/>
-      <c r="F87" s="214"/>
-      <c r="G87" s="214"/>
-      <c r="H87" s="214"/>
-      <c r="I87" s="214"/>
-      <c r="J87" s="214"/>
-      <c r="K87" s="214"/>
-      <c r="L87" s="214"/>
-      <c r="M87" s="214"/>
-      <c r="N87" s="214"/>
-      <c r="O87" s="214"/>
-      <c r="P87" s="214"/>
+      <c r="E87" s="220"/>
+      <c r="F87" s="220"/>
+      <c r="G87" s="220"/>
+      <c r="H87" s="220"/>
+      <c r="I87" s="220"/>
+      <c r="J87" s="220"/>
+      <c r="K87" s="220"/>
+      <c r="L87" s="220"/>
+      <c r="M87" s="220"/>
+      <c r="N87" s="220"/>
+      <c r="O87" s="220"/>
+      <c r="P87" s="220"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="214"/>
-      <c r="F88" s="214"/>
-      <c r="G88" s="214"/>
-      <c r="H88" s="214"/>
-      <c r="I88" s="214"/>
-      <c r="J88" s="214"/>
-      <c r="K88" s="214"/>
-      <c r="L88" s="214"/>
-      <c r="M88" s="214"/>
-      <c r="N88" s="214"/>
-      <c r="O88" s="214"/>
-      <c r="P88" s="214"/>
+      <c r="E88" s="220"/>
+      <c r="F88" s="220"/>
+      <c r="G88" s="220"/>
+      <c r="H88" s="220"/>
+      <c r="I88" s="220"/>
+      <c r="J88" s="220"/>
+      <c r="K88" s="220"/>
+      <c r="L88" s="220"/>
+      <c r="M88" s="220"/>
+      <c r="N88" s="220"/>
+      <c r="O88" s="220"/>
+      <c r="P88" s="220"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="214"/>
-      <c r="F89" s="214"/>
-      <c r="G89" s="214"/>
-      <c r="H89" s="214"/>
-      <c r="I89" s="214"/>
-      <c r="J89" s="214"/>
-      <c r="K89" s="214"/>
-      <c r="L89" s="214"/>
-      <c r="M89" s="214"/>
-      <c r="N89" s="214"/>
-      <c r="O89" s="214"/>
-      <c r="P89" s="214"/>
+      <c r="E89" s="220"/>
+      <c r="F89" s="220"/>
+      <c r="G89" s="220"/>
+      <c r="H89" s="220"/>
+      <c r="I89" s="220"/>
+      <c r="J89" s="220"/>
+      <c r="K89" s="220"/>
+      <c r="L89" s="220"/>
+      <c r="M89" s="220"/>
+      <c r="N89" s="220"/>
+      <c r="O89" s="220"/>
+      <c r="P89" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="H4:H5"/>
@@ -8550,16 +8572,23 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="R4:R5"/>
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17617F6D-8FDE-49AD-847F-18A3793B5686}">
+  <dimension ref="C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="245" t="s">
+        <v>255</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>